--- a/materials/templates/orionmano-valuation-template-v1.xlsx
+++ b/materials/templates/orionmano-valuation-template-v1.xlsx
@@ -142,8 +142,9 @@
     <definedName name="sens_terminal_g_count">'Inputs'!$D$123</definedName>
     <definedName name="sens_revenue_g_step">'Inputs'!$D$124</definedName>
     <definedName name="sens_ebitda_margin_step">'Inputs'!$D$125</definedName>
-    <definedName name="cocos_table">'Inputs'!$A$129:$K$158</definedName>
+    <definedName name="cocos_table">'Inputs'!$A$129:$L$158</definedName>
     <definedName name="precedents_table">'Inputs'!$A$162:$I$176</definedName>
+    <definedName name="segments_table">'Inputs'!$A$181:$M$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2190,20 +2191,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2243,35 +2245,40 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
+          <t>Business description</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>Accounting standard</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>Market cap (USD mm)</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>D/E ratio</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>Raw levered beta</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t>Unlevered beta (calculated)</t>
         </is>
@@ -2319,7 +2326,11 @@
         <v/>
       </c>
       <c r="K6" s="33">
-        <f>IFERROR(Inputs!I127/(1+(1-Inputs!J127)*Inputs!H127),"")</f>
+        <f>Inputs!K127</f>
+        <v/>
+      </c>
+      <c r="L6" s="33">
+        <f>IFERROR(Inputs!J127/(1+(1-Inputs!K127)*Inputs!I127),"")</f>
         <v/>
       </c>
     </row>
@@ -2365,7 +2376,11 @@
         <v/>
       </c>
       <c r="K7" s="33">
-        <f>IFERROR(Inputs!I128/(1+(1-Inputs!J128)*Inputs!H128),"")</f>
+        <f>Inputs!K128</f>
+        <v/>
+      </c>
+      <c r="L7" s="33">
+        <f>IFERROR(Inputs!J128/(1+(1-Inputs!K128)*Inputs!I128),"")</f>
         <v/>
       </c>
     </row>
@@ -2411,7 +2426,11 @@
         <v/>
       </c>
       <c r="K8" s="33">
-        <f>IFERROR(Inputs!I129/(1+(1-Inputs!J129)*Inputs!H129),"")</f>
+        <f>Inputs!K129</f>
+        <v/>
+      </c>
+      <c r="L8" s="33">
+        <f>IFERROR(Inputs!J129/(1+(1-Inputs!K129)*Inputs!I129),"")</f>
         <v/>
       </c>
     </row>
@@ -2457,7 +2476,11 @@
         <v/>
       </c>
       <c r="K9" s="33">
-        <f>IFERROR(Inputs!I130/(1+(1-Inputs!J130)*Inputs!H130),"")</f>
+        <f>Inputs!K130</f>
+        <v/>
+      </c>
+      <c r="L9" s="33">
+        <f>IFERROR(Inputs!J130/(1+(1-Inputs!K130)*Inputs!I130),"")</f>
         <v/>
       </c>
     </row>
@@ -2503,7 +2526,11 @@
         <v/>
       </c>
       <c r="K10" s="33">
-        <f>IFERROR(Inputs!I131/(1+(1-Inputs!J131)*Inputs!H131),"")</f>
+        <f>Inputs!K131</f>
+        <v/>
+      </c>
+      <c r="L10" s="33">
+        <f>IFERROR(Inputs!J131/(1+(1-Inputs!K131)*Inputs!I131),"")</f>
         <v/>
       </c>
     </row>
@@ -2549,7 +2576,11 @@
         <v/>
       </c>
       <c r="K11" s="33">
-        <f>IFERROR(Inputs!I132/(1+(1-Inputs!J132)*Inputs!H132),"")</f>
+        <f>Inputs!K132</f>
+        <v/>
+      </c>
+      <c r="L11" s="33">
+        <f>IFERROR(Inputs!J132/(1+(1-Inputs!K132)*Inputs!I132),"")</f>
         <v/>
       </c>
     </row>
@@ -2595,7 +2626,11 @@
         <v/>
       </c>
       <c r="K12" s="33">
-        <f>IFERROR(Inputs!I133/(1+(1-Inputs!J133)*Inputs!H133),"")</f>
+        <f>Inputs!K133</f>
+        <v/>
+      </c>
+      <c r="L12" s="33">
+        <f>IFERROR(Inputs!J133/(1+(1-Inputs!K133)*Inputs!I133),"")</f>
         <v/>
       </c>
     </row>
@@ -2641,7 +2676,11 @@
         <v/>
       </c>
       <c r="K13" s="33">
-        <f>IFERROR(Inputs!I134/(1+(1-Inputs!J134)*Inputs!H134),"")</f>
+        <f>Inputs!K134</f>
+        <v/>
+      </c>
+      <c r="L13" s="33">
+        <f>IFERROR(Inputs!J134/(1+(1-Inputs!K134)*Inputs!I134),"")</f>
         <v/>
       </c>
     </row>
@@ -2687,7 +2726,11 @@
         <v/>
       </c>
       <c r="K14" s="33">
-        <f>IFERROR(Inputs!I135/(1+(1-Inputs!J135)*Inputs!H135),"")</f>
+        <f>Inputs!K135</f>
+        <v/>
+      </c>
+      <c r="L14" s="33">
+        <f>IFERROR(Inputs!J135/(1+(1-Inputs!K135)*Inputs!I135),"")</f>
         <v/>
       </c>
     </row>
@@ -2733,7 +2776,11 @@
         <v/>
       </c>
       <c r="K15" s="33">
-        <f>IFERROR(Inputs!I136/(1+(1-Inputs!J136)*Inputs!H136),"")</f>
+        <f>Inputs!K136</f>
+        <v/>
+      </c>
+      <c r="L15" s="33">
+        <f>IFERROR(Inputs!J136/(1+(1-Inputs!K136)*Inputs!I136),"")</f>
         <v/>
       </c>
     </row>
@@ -2779,7 +2826,11 @@
         <v/>
       </c>
       <c r="K16" s="33">
-        <f>IFERROR(Inputs!I137/(1+(1-Inputs!J137)*Inputs!H137),"")</f>
+        <f>Inputs!K137</f>
+        <v/>
+      </c>
+      <c r="L16" s="33">
+        <f>IFERROR(Inputs!J137/(1+(1-Inputs!K137)*Inputs!I137),"")</f>
         <v/>
       </c>
     </row>
@@ -2825,7 +2876,11 @@
         <v/>
       </c>
       <c r="K17" s="33">
-        <f>IFERROR(Inputs!I138/(1+(1-Inputs!J138)*Inputs!H138),"")</f>
+        <f>Inputs!K138</f>
+        <v/>
+      </c>
+      <c r="L17" s="33">
+        <f>IFERROR(Inputs!J138/(1+(1-Inputs!K138)*Inputs!I138),"")</f>
         <v/>
       </c>
     </row>
@@ -2871,7 +2926,11 @@
         <v/>
       </c>
       <c r="K18" s="33">
-        <f>IFERROR(Inputs!I139/(1+(1-Inputs!J139)*Inputs!H139),"")</f>
+        <f>Inputs!K139</f>
+        <v/>
+      </c>
+      <c r="L18" s="33">
+        <f>IFERROR(Inputs!J139/(1+(1-Inputs!K139)*Inputs!I139),"")</f>
         <v/>
       </c>
     </row>
@@ -2917,7 +2976,11 @@
         <v/>
       </c>
       <c r="K19" s="33">
-        <f>IFERROR(Inputs!I140/(1+(1-Inputs!J140)*Inputs!H140),"")</f>
+        <f>Inputs!K140</f>
+        <v/>
+      </c>
+      <c r="L19" s="33">
+        <f>IFERROR(Inputs!J140/(1+(1-Inputs!K140)*Inputs!I140),"")</f>
         <v/>
       </c>
     </row>
@@ -2963,7 +3026,11 @@
         <v/>
       </c>
       <c r="K20" s="33">
-        <f>IFERROR(Inputs!I141/(1+(1-Inputs!J141)*Inputs!H141),"")</f>
+        <f>Inputs!K141</f>
+        <v/>
+      </c>
+      <c r="L20" s="33">
+        <f>IFERROR(Inputs!J141/(1+(1-Inputs!K141)*Inputs!I141),"")</f>
         <v/>
       </c>
     </row>
@@ -3009,7 +3076,11 @@
         <v/>
       </c>
       <c r="K21" s="33">
-        <f>IFERROR(Inputs!I142/(1+(1-Inputs!J142)*Inputs!H142),"")</f>
+        <f>Inputs!K142</f>
+        <v/>
+      </c>
+      <c r="L21" s="33">
+        <f>IFERROR(Inputs!J142/(1+(1-Inputs!K142)*Inputs!I142),"")</f>
         <v/>
       </c>
     </row>
@@ -3055,7 +3126,11 @@
         <v/>
       </c>
       <c r="K22" s="33">
-        <f>IFERROR(Inputs!I143/(1+(1-Inputs!J143)*Inputs!H143),"")</f>
+        <f>Inputs!K143</f>
+        <v/>
+      </c>
+      <c r="L22" s="33">
+        <f>IFERROR(Inputs!J143/(1+(1-Inputs!K143)*Inputs!I143),"")</f>
         <v/>
       </c>
     </row>
@@ -3101,7 +3176,11 @@
         <v/>
       </c>
       <c r="K23" s="33">
-        <f>IFERROR(Inputs!I144/(1+(1-Inputs!J144)*Inputs!H144),"")</f>
+        <f>Inputs!K144</f>
+        <v/>
+      </c>
+      <c r="L23" s="33">
+        <f>IFERROR(Inputs!J144/(1+(1-Inputs!K144)*Inputs!I144),"")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3226,11 @@
         <v/>
       </c>
       <c r="K24" s="33">
-        <f>IFERROR(Inputs!I145/(1+(1-Inputs!J145)*Inputs!H145),"")</f>
+        <f>Inputs!K145</f>
+        <v/>
+      </c>
+      <c r="L24" s="33">
+        <f>IFERROR(Inputs!J145/(1+(1-Inputs!K145)*Inputs!I145),"")</f>
         <v/>
       </c>
     </row>
@@ -3193,7 +3276,11 @@
         <v/>
       </c>
       <c r="K25" s="33">
-        <f>IFERROR(Inputs!I146/(1+(1-Inputs!J146)*Inputs!H146),"")</f>
+        <f>Inputs!K146</f>
+        <v/>
+      </c>
+      <c r="L25" s="33">
+        <f>IFERROR(Inputs!J146/(1+(1-Inputs!K146)*Inputs!I146),"")</f>
         <v/>
       </c>
     </row>
@@ -3239,7 +3326,11 @@
         <v/>
       </c>
       <c r="K26" s="33">
-        <f>IFERROR(Inputs!I147/(1+(1-Inputs!J147)*Inputs!H147),"")</f>
+        <f>Inputs!K147</f>
+        <v/>
+      </c>
+      <c r="L26" s="33">
+        <f>IFERROR(Inputs!J147/(1+(1-Inputs!K147)*Inputs!I147),"")</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3376,11 @@
         <v/>
       </c>
       <c r="K27" s="33">
-        <f>IFERROR(Inputs!I148/(1+(1-Inputs!J148)*Inputs!H148),"")</f>
+        <f>Inputs!K148</f>
+        <v/>
+      </c>
+      <c r="L27" s="33">
+        <f>IFERROR(Inputs!J148/(1+(1-Inputs!K148)*Inputs!I148),"")</f>
         <v/>
       </c>
     </row>
@@ -3331,7 +3426,11 @@
         <v/>
       </c>
       <c r="K28" s="33">
-        <f>IFERROR(Inputs!I149/(1+(1-Inputs!J149)*Inputs!H149),"")</f>
+        <f>Inputs!K149</f>
+        <v/>
+      </c>
+      <c r="L28" s="33">
+        <f>IFERROR(Inputs!J149/(1+(1-Inputs!K149)*Inputs!I149),"")</f>
         <v/>
       </c>
     </row>
@@ -3377,7 +3476,11 @@
         <v/>
       </c>
       <c r="K29" s="33">
-        <f>IFERROR(Inputs!I150/(1+(1-Inputs!J150)*Inputs!H150),"")</f>
+        <f>Inputs!K150</f>
+        <v/>
+      </c>
+      <c r="L29" s="33">
+        <f>IFERROR(Inputs!J150/(1+(1-Inputs!K150)*Inputs!I150),"")</f>
         <v/>
       </c>
     </row>
@@ -3423,7 +3526,11 @@
         <v/>
       </c>
       <c r="K30" s="33">
-        <f>IFERROR(Inputs!I151/(1+(1-Inputs!J151)*Inputs!H151),"")</f>
+        <f>Inputs!K151</f>
+        <v/>
+      </c>
+      <c r="L30" s="33">
+        <f>IFERROR(Inputs!J151/(1+(1-Inputs!K151)*Inputs!I151),"")</f>
         <v/>
       </c>
     </row>
@@ -3469,7 +3576,11 @@
         <v/>
       </c>
       <c r="K31" s="33">
-        <f>IFERROR(Inputs!I152/(1+(1-Inputs!J152)*Inputs!H152),"")</f>
+        <f>Inputs!K152</f>
+        <v/>
+      </c>
+      <c r="L31" s="33">
+        <f>IFERROR(Inputs!J152/(1+(1-Inputs!K152)*Inputs!I152),"")</f>
         <v/>
       </c>
     </row>
@@ -3515,7 +3626,11 @@
         <v/>
       </c>
       <c r="K32" s="33">
-        <f>IFERROR(Inputs!I153/(1+(1-Inputs!J153)*Inputs!H153),"")</f>
+        <f>Inputs!K153</f>
+        <v/>
+      </c>
+      <c r="L32" s="33">
+        <f>IFERROR(Inputs!J153/(1+(1-Inputs!K153)*Inputs!I153),"")</f>
         <v/>
       </c>
     </row>
@@ -3561,7 +3676,11 @@
         <v/>
       </c>
       <c r="K33" s="33">
-        <f>IFERROR(Inputs!I154/(1+(1-Inputs!J154)*Inputs!H154),"")</f>
+        <f>Inputs!K154</f>
+        <v/>
+      </c>
+      <c r="L33" s="33">
+        <f>IFERROR(Inputs!J154/(1+(1-Inputs!K154)*Inputs!I154),"")</f>
         <v/>
       </c>
     </row>
@@ -3607,7 +3726,11 @@
         <v/>
       </c>
       <c r="K34" s="33">
-        <f>IFERROR(Inputs!I155/(1+(1-Inputs!J155)*Inputs!H155),"")</f>
+        <f>Inputs!K155</f>
+        <v/>
+      </c>
+      <c r="L34" s="33">
+        <f>IFERROR(Inputs!J155/(1+(1-Inputs!K155)*Inputs!I155),"")</f>
         <v/>
       </c>
     </row>
@@ -3653,13 +3776,17 @@
         <v/>
       </c>
       <c r="K35" s="33">
-        <f>IFERROR(Inputs!I156/(1+(1-Inputs!J156)*Inputs!H156),"")</f>
+        <f>Inputs!K156</f>
+        <v/>
+      </c>
+      <c r="L35" s="33">
+        <f>IFERROR(Inputs!J156/(1+(1-Inputs!K156)*Inputs!I156),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12260,7 +12387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -14695,35 +14822,40 @@
       </c>
       <c r="E128" s="21" t="inlineStr">
         <is>
+          <t>Business description</t>
+        </is>
+      </c>
+      <c r="F128" s="21" t="inlineStr">
+        <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F128" s="21" t="inlineStr">
+      <c r="G128" s="21" t="inlineStr">
         <is>
           <t>Accounting standard</t>
         </is>
       </c>
-      <c r="G128" s="21" t="inlineStr">
+      <c r="H128" s="21" t="inlineStr">
         <is>
           <t>Market cap (USD mm)</t>
         </is>
       </c>
-      <c r="H128" s="21" t="inlineStr">
+      <c r="I128" s="21" t="inlineStr">
         <is>
           <t>D/E ratio</t>
         </is>
       </c>
-      <c r="I128" s="21" t="inlineStr">
+      <c r="J128" s="21" t="inlineStr">
         <is>
           <t>Raw levered beta</t>
         </is>
       </c>
-      <c r="J128" s="21" t="inlineStr">
+      <c r="K128" s="21" t="inlineStr">
         <is>
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="K128" s="21" t="inlineStr">
+      <c r="L128" s="21" t="inlineStr">
         <is>
           <t>Unlevered beta (calculated)</t>
         </is>
@@ -14741,6 +14873,7 @@
       <c r="I129" s="33" t="n"/>
       <c r="J129" s="33" t="n"/>
       <c r="K129" s="33" t="n"/>
+      <c r="L129" s="33" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="33" t="n"/>
@@ -14754,6 +14887,7 @@
       <c r="I130" s="33" t="n"/>
       <c r="J130" s="33" t="n"/>
       <c r="K130" s="33" t="n"/>
+      <c r="L130" s="33" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="33" t="n"/>
@@ -14767,6 +14901,7 @@
       <c r="I131" s="33" t="n"/>
       <c r="J131" s="33" t="n"/>
       <c r="K131" s="33" t="n"/>
+      <c r="L131" s="33" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="33" t="n"/>
@@ -14780,6 +14915,7 @@
       <c r="I132" s="33" t="n"/>
       <c r="J132" s="33" t="n"/>
       <c r="K132" s="33" t="n"/>
+      <c r="L132" s="33" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="33" t="n"/>
@@ -14793,6 +14929,7 @@
       <c r="I133" s="33" t="n"/>
       <c r="J133" s="33" t="n"/>
       <c r="K133" s="33" t="n"/>
+      <c r="L133" s="33" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="33" t="n"/>
@@ -14806,6 +14943,7 @@
       <c r="I134" s="33" t="n"/>
       <c r="J134" s="33" t="n"/>
       <c r="K134" s="33" t="n"/>
+      <c r="L134" s="33" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="33" t="n"/>
@@ -14819,6 +14957,7 @@
       <c r="I135" s="33" t="n"/>
       <c r="J135" s="33" t="n"/>
       <c r="K135" s="33" t="n"/>
+      <c r="L135" s="33" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="33" t="n"/>
@@ -14832,6 +14971,7 @@
       <c r="I136" s="33" t="n"/>
       <c r="J136" s="33" t="n"/>
       <c r="K136" s="33" t="n"/>
+      <c r="L136" s="33" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="33" t="n"/>
@@ -14845,6 +14985,7 @@
       <c r="I137" s="33" t="n"/>
       <c r="J137" s="33" t="n"/>
       <c r="K137" s="33" t="n"/>
+      <c r="L137" s="33" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="33" t="n"/>
@@ -14858,6 +14999,7 @@
       <c r="I138" s="33" t="n"/>
       <c r="J138" s="33" t="n"/>
       <c r="K138" s="33" t="n"/>
+      <c r="L138" s="33" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="33" t="n"/>
@@ -14871,6 +15013,7 @@
       <c r="I139" s="33" t="n"/>
       <c r="J139" s="33" t="n"/>
       <c r="K139" s="33" t="n"/>
+      <c r="L139" s="33" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="33" t="n"/>
@@ -14884,6 +15027,7 @@
       <c r="I140" s="33" t="n"/>
       <c r="J140" s="33" t="n"/>
       <c r="K140" s="33" t="n"/>
+      <c r="L140" s="33" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="33" t="n"/>
@@ -14897,6 +15041,7 @@
       <c r="I141" s="33" t="n"/>
       <c r="J141" s="33" t="n"/>
       <c r="K141" s="33" t="n"/>
+      <c r="L141" s="33" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="33" t="n"/>
@@ -14910,6 +15055,7 @@
       <c r="I142" s="33" t="n"/>
       <c r="J142" s="33" t="n"/>
       <c r="K142" s="33" t="n"/>
+      <c r="L142" s="33" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="33" t="n"/>
@@ -14923,6 +15069,7 @@
       <c r="I143" s="33" t="n"/>
       <c r="J143" s="33" t="n"/>
       <c r="K143" s="33" t="n"/>
+      <c r="L143" s="33" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="33" t="n"/>
@@ -14936,6 +15083,7 @@
       <c r="I144" s="33" t="n"/>
       <c r="J144" s="33" t="n"/>
       <c r="K144" s="33" t="n"/>
+      <c r="L144" s="33" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="33" t="n"/>
@@ -14949,6 +15097,7 @@
       <c r="I145" s="33" t="n"/>
       <c r="J145" s="33" t="n"/>
       <c r="K145" s="33" t="n"/>
+      <c r="L145" s="33" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="33" t="n"/>
@@ -14962,6 +15111,7 @@
       <c r="I146" s="33" t="n"/>
       <c r="J146" s="33" t="n"/>
       <c r="K146" s="33" t="n"/>
+      <c r="L146" s="33" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="33" t="n"/>
@@ -14975,6 +15125,7 @@
       <c r="I147" s="33" t="n"/>
       <c r="J147" s="33" t="n"/>
       <c r="K147" s="33" t="n"/>
+      <c r="L147" s="33" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="33" t="n"/>
@@ -14988,6 +15139,7 @@
       <c r="I148" s="33" t="n"/>
       <c r="J148" s="33" t="n"/>
       <c r="K148" s="33" t="n"/>
+      <c r="L148" s="33" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="33" t="n"/>
@@ -15001,6 +15153,7 @@
       <c r="I149" s="33" t="n"/>
       <c r="J149" s="33" t="n"/>
       <c r="K149" s="33" t="n"/>
+      <c r="L149" s="33" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="33" t="n"/>
@@ -15014,6 +15167,7 @@
       <c r="I150" s="33" t="n"/>
       <c r="J150" s="33" t="n"/>
       <c r="K150" s="33" t="n"/>
+      <c r="L150" s="33" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="33" t="n"/>
@@ -15027,6 +15181,7 @@
       <c r="I151" s="33" t="n"/>
       <c r="J151" s="33" t="n"/>
       <c r="K151" s="33" t="n"/>
+      <c r="L151" s="33" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="33" t="n"/>
@@ -15040,6 +15195,7 @@
       <c r="I152" s="33" t="n"/>
       <c r="J152" s="33" t="n"/>
       <c r="K152" s="33" t="n"/>
+      <c r="L152" s="33" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="33" t="n"/>
@@ -15053,6 +15209,7 @@
       <c r="I153" s="33" t="n"/>
       <c r="J153" s="33" t="n"/>
       <c r="K153" s="33" t="n"/>
+      <c r="L153" s="33" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="33" t="n"/>
@@ -15066,6 +15223,7 @@
       <c r="I154" s="33" t="n"/>
       <c r="J154" s="33" t="n"/>
       <c r="K154" s="33" t="n"/>
+      <c r="L154" s="33" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="33" t="n"/>
@@ -15079,6 +15237,7 @@
       <c r="I155" s="33" t="n"/>
       <c r="J155" s="33" t="n"/>
       <c r="K155" s="33" t="n"/>
+      <c r="L155" s="33" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="33" t="n"/>
@@ -15092,6 +15251,7 @@
       <c r="I156" s="33" t="n"/>
       <c r="J156" s="33" t="n"/>
       <c r="K156" s="33" t="n"/>
+      <c r="L156" s="33" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="33" t="n"/>
@@ -15105,6 +15265,7 @@
       <c r="I157" s="33" t="n"/>
       <c r="J157" s="33" t="n"/>
       <c r="K157" s="33" t="n"/>
+      <c r="L157" s="33" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="33" t="n"/>
@@ -15118,6 +15279,7 @@
       <c r="I158" s="33" t="n"/>
       <c r="J158" s="33" t="n"/>
       <c r="K158" s="33" t="n"/>
+      <c r="L158" s="33" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="37" t="inlineStr">
@@ -15338,10 +15500,167 @@
       <c r="H176" s="33" t="n"/>
       <c r="I176" s="33" t="n"/>
     </row>
+    <row r="178">
+      <c r="A178" s="37" t="inlineStr">
+        <is>
+          <t>Section I — Revenue segments  (Optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Optional segmented breakdown. Fill rows below + re-upload to override top-level revenue_growth / gross_margin with a segment aggregate. start_year=0 means the segment already exists in Y0; start_year&gt;0 introduces a new revenue line at that projection year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="21" t="inlineStr">
+        <is>
+          <t>Segment name</t>
+        </is>
+      </c>
+      <c r="B180" s="21" t="inlineStr">
+        <is>
+          <t>Start year</t>
+        </is>
+      </c>
+      <c r="C180" s="21" t="inlineStr">
+        <is>
+          <t>Initial revenue</t>
+        </is>
+      </c>
+      <c r="D180" s="21" t="inlineStr">
+        <is>
+          <t>Growth Y1</t>
+        </is>
+      </c>
+      <c r="E180" s="21" t="inlineStr">
+        <is>
+          <t>Growth Y2</t>
+        </is>
+      </c>
+      <c r="F180" s="21" t="inlineStr">
+        <is>
+          <t>Growth Y3</t>
+        </is>
+      </c>
+      <c r="G180" s="21" t="inlineStr">
+        <is>
+          <t>Growth Y4</t>
+        </is>
+      </c>
+      <c r="H180" s="21" t="inlineStr">
+        <is>
+          <t>Growth Y5</t>
+        </is>
+      </c>
+      <c r="I180" s="21" t="inlineStr">
+        <is>
+          <t>GM Y1</t>
+        </is>
+      </c>
+      <c r="J180" s="21" t="inlineStr">
+        <is>
+          <t>GM Y2</t>
+        </is>
+      </c>
+      <c r="K180" s="21" t="inlineStr">
+        <is>
+          <t>GM Y3</t>
+        </is>
+      </c>
+      <c r="L180" s="21" t="inlineStr">
+        <is>
+          <t>GM Y4</t>
+        </is>
+      </c>
+      <c r="M180" s="21" t="inlineStr">
+        <is>
+          <t>GM Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="33" t="n"/>
+      <c r="B181" s="33" t="n"/>
+      <c r="C181" s="33" t="n"/>
+      <c r="D181" s="33" t="n"/>
+      <c r="E181" s="33" t="n"/>
+      <c r="F181" s="33" t="n"/>
+      <c r="G181" s="33" t="n"/>
+      <c r="H181" s="33" t="n"/>
+      <c r="I181" s="33" t="n"/>
+      <c r="J181" s="33" t="n"/>
+      <c r="K181" s="33" t="n"/>
+      <c r="L181" s="33" t="n"/>
+      <c r="M181" s="33" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="33" t="n"/>
+      <c r="B182" s="33" t="n"/>
+      <c r="C182" s="33" t="n"/>
+      <c r="D182" s="33" t="n"/>
+      <c r="E182" s="33" t="n"/>
+      <c r="F182" s="33" t="n"/>
+      <c r="G182" s="33" t="n"/>
+      <c r="H182" s="33" t="n"/>
+      <c r="I182" s="33" t="n"/>
+      <c r="J182" s="33" t="n"/>
+      <c r="K182" s="33" t="n"/>
+      <c r="L182" s="33" t="n"/>
+      <c r="M182" s="33" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="33" t="n"/>
+      <c r="B183" s="33" t="n"/>
+      <c r="C183" s="33" t="n"/>
+      <c r="D183" s="33" t="n"/>
+      <c r="E183" s="33" t="n"/>
+      <c r="F183" s="33" t="n"/>
+      <c r="G183" s="33" t="n"/>
+      <c r="H183" s="33" t="n"/>
+      <c r="I183" s="33" t="n"/>
+      <c r="J183" s="33" t="n"/>
+      <c r="K183" s="33" t="n"/>
+      <c r="L183" s="33" t="n"/>
+      <c r="M183" s="33" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="33" t="n"/>
+      <c r="B184" s="33" t="n"/>
+      <c r="C184" s="33" t="n"/>
+      <c r="D184" s="33" t="n"/>
+      <c r="E184" s="33" t="n"/>
+      <c r="F184" s="33" t="n"/>
+      <c r="G184" s="33" t="n"/>
+      <c r="H184" s="33" t="n"/>
+      <c r="I184" s="33" t="n"/>
+      <c r="J184" s="33" t="n"/>
+      <c r="K184" s="33" t="n"/>
+      <c r="L184" s="33" t="n"/>
+      <c r="M184" s="33" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="33" t="n"/>
+      <c r="B185" s="33" t="n"/>
+      <c r="C185" s="33" t="n"/>
+      <c r="D185" s="33" t="n"/>
+      <c r="E185" s="33" t="n"/>
+      <c r="F185" s="33" t="n"/>
+      <c r="G185" s="33" t="n"/>
+      <c r="H185" s="33" t="n"/>
+      <c r="I185" s="33" t="n"/>
+      <c r="J185" s="33" t="n"/>
+      <c r="K185" s="33" t="n"/>
+      <c r="L185" s="33" t="n"/>
+      <c r="M185" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A92:H92"/>
     <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A178:M178"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A104:H104"/>
@@ -15349,6 +15668,7 @@
     <mergeCell ref="A119:H119"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A179:M179"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A75:H75"/>
     <mergeCell ref="A110:H110"/>

--- a/materials/templates/orionmano-valuation-template-v1.xlsx
+++ b/materials/templates/orionmano-valuation-template-v1.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Historical FS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Projections" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DCF (Independent)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Comps" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Football Field" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="WACC" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="CoCo Selection" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="CoCo Multiples" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="CoCo Margins" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="CoCo Ratios" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="CIQ Data Timeline" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Country ERP" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Industry Averages" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Adjustments" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Sensitivity" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Valuation Summary" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="_dropdowns" sheetId="21" state="hidden" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical FS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projections" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF (Independent)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Football Field" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Selection" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Multiples" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Margins" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Ratios" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CIQ Data Timeline" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country ERP" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industry Averages" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjustments" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_dropdowns" sheetId="21" state="hidden" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="company_name">'Inputs'!$D$7</definedName>
@@ -55,96 +55,100 @@
     <definedName name="revenue_growth_method">'Inputs'!$D$35</definedName>
     <definedName name="revenue_y0">'Inputs'!$D$36</definedName>
     <definedName name="nwc_y0">'Inputs'!$D$37</definedName>
-    <definedName name="revenue_growth_y1">'Inputs'!$D$38</definedName>
-    <definedName name="revenue_growth_y2">'Inputs'!$D$39</definedName>
-    <definedName name="revenue_growth_y3">'Inputs'!$D$40</definedName>
-    <definedName name="revenue_growth_y4">'Inputs'!$D$41</definedName>
-    <definedName name="revenue_growth_y5">'Inputs'!$D$42</definedName>
-    <definedName name="gross_margin_y1">'Inputs'!$D$43</definedName>
-    <definedName name="gross_margin_y2">'Inputs'!$D$44</definedName>
-    <definedName name="gross_margin_y3">'Inputs'!$D$45</definedName>
-    <definedName name="gross_margin_y4">'Inputs'!$D$46</definedName>
-    <definedName name="gross_margin_y5">'Inputs'!$D$47</definedName>
-    <definedName name="opex_pct_revenue_y1">'Inputs'!$D$48</definedName>
-    <definedName name="opex_pct_revenue_y2">'Inputs'!$D$49</definedName>
-    <definedName name="opex_pct_revenue_y3">'Inputs'!$D$50</definedName>
-    <definedName name="opex_pct_revenue_y4">'Inputs'!$D$51</definedName>
-    <definedName name="opex_pct_revenue_y5">'Inputs'!$D$52</definedName>
-    <definedName name="capex_pct_revenue_y1">'Inputs'!$D$53</definedName>
-    <definedName name="capex_pct_revenue_y2">'Inputs'!$D$54</definedName>
-    <definedName name="capex_pct_revenue_y3">'Inputs'!$D$55</definedName>
-    <definedName name="capex_pct_revenue_y4">'Inputs'!$D$56</definedName>
-    <definedName name="capex_pct_revenue_y5">'Inputs'!$D$57</definedName>
-    <definedName name="dep_pct_revenue_y1">'Inputs'!$D$58</definedName>
-    <definedName name="dep_pct_revenue_y2">'Inputs'!$D$59</definedName>
-    <definedName name="dep_pct_revenue_y3">'Inputs'!$D$60</definedName>
-    <definedName name="dep_pct_revenue_y4">'Inputs'!$D$61</definedName>
-    <definedName name="dep_pct_revenue_y5">'Inputs'!$D$62</definedName>
-    <definedName name="nwc_pct_sales_y1">'Inputs'!$D$63</definedName>
-    <definedName name="nwc_pct_sales_y2">'Inputs'!$D$64</definedName>
-    <definedName name="nwc_pct_sales_y3">'Inputs'!$D$65</definedName>
-    <definedName name="nwc_pct_sales_y4">'Inputs'!$D$66</definedName>
-    <definedName name="nwc_pct_sales_y5">'Inputs'!$D$67</definedName>
-    <definedName name="terminal_method">'Inputs'!$D$70</definedName>
-    <definedName name="terminal_growth_rate">'Inputs'!$D$71</definedName>
-    <definedName name="terminal_exit_multiple_type">'Inputs'!$D$72</definedName>
-    <definedName name="terminal_exit_multiple_value">'Inputs'!$D$73</definedName>
-    <definedName name="risk_free_rate">'Inputs'!$D$76</definedName>
-    <definedName name="risk_free_rate_source">'Inputs'!$D$77</definedName>
-    <definedName name="equity_risk_premium">'Inputs'!$D$78</definedName>
-    <definedName name="country_risk_premium">'Inputs'!$D$79</definedName>
-    <definedName name="unlevered_beta_per_mgmt">'Inputs'!$D$80</definedName>
-    <definedName name="unlevered_beta_indep">'Inputs'!$E$80</definedName>
-    <definedName name="target_debt_to_equity_per_mgmt">'Inputs'!$D$81</definedName>
-    <definedName name="target_debt_to_equity_indep">'Inputs'!$E$81</definedName>
-    <definedName name="levered_beta_per_mgmt">'Inputs'!$D$82</definedName>
-    <definedName name="levered_beta_indep">'Inputs'!$E$82</definedName>
-    <definedName name="size_premium_per_mgmt">'Inputs'!$D$83</definedName>
-    <definedName name="size_premium_indep">'Inputs'!$E$83</definedName>
-    <definedName name="specific_risk_premium_per_mgmt">'Inputs'!$D$84</definedName>
-    <definedName name="specific_risk_premium_indep">'Inputs'!$E$84</definedName>
-    <definedName name="cost_of_equity_per_mgmt">'Inputs'!$D$85</definedName>
-    <definedName name="cost_of_equity_indep">'Inputs'!$E$85</definedName>
-    <definedName name="pretax_cost_of_debt_per_mgmt">'Inputs'!$D$86</definedName>
-    <definedName name="pretax_cost_of_debt_indep">'Inputs'!$E$86</definedName>
-    <definedName name="aftertax_cost_of_debt_per_mgmt">'Inputs'!$D$87</definedName>
-    <definedName name="aftertax_cost_of_debt_indep">'Inputs'!$E$87</definedName>
-    <definedName name="target_debt_weight_per_mgmt">'Inputs'!$D$88</definedName>
-    <definedName name="target_debt_weight_indep">'Inputs'!$E$88</definedName>
-    <definedName name="target_equity_weight_per_mgmt">'Inputs'!$D$89</definedName>
-    <definedName name="target_equity_weight_indep">'Inputs'!$E$89</definedName>
-    <definedName name="wacc_per_mgmt">'Inputs'!$D$90</definedName>
-    <definedName name="wacc_indep">'Inputs'!$E$90</definedName>
-    <definedName name="surplus_assets">'Inputs'!$D$93</definedName>
-    <definedName name="net_debt_override">'Inputs'!$D$94</definedName>
-    <definedName name="minority_interests">'Inputs'!$D$95</definedName>
-    <definedName name="non_operating_assets">'Inputs'!$D$96</definedName>
-    <definedName name="dlom_pct">'Inputs'!$D$97</definedName>
-    <definedName name="dloc_pct">'Inputs'!$D$98</definedName>
-    <definedName name="equity_interest_pct">'Inputs'!$D$99</definedName>
-    <definedName name="shares_outstanding">'Inputs'!$D$100</definedName>
-    <definedName name="shares_outstanding_diluted">'Inputs'!$D$101</definedName>
-    <definedName name="pre_money_pct">'Inputs'!$D$102</definedName>
-    <definedName name="capitalize_rd">'Inputs'!$D$105</definedName>
-    <definedName name="rd_amortization_years">'Inputs'!$D$106</definedName>
-    <definedName name="convert_operating_leases">'Inputs'!$D$107</definedName>
-    <definedName name="lease_discount_rate">'Inputs'!$D$108</definedName>
-    <definedName name="weight_dcf">'Inputs'!$D$111</definedName>
-    <definedName name="weight_comps">'Inputs'!$D$112</definedName>
-    <definedName name="weight_precedent">'Inputs'!$D$113</definedName>
-    <definedName name="weight_nav">'Inputs'!$D$114</definedName>
-    <definedName name="selected_low">'Inputs'!$D$115</definedName>
-    <definedName name="selected_mid">'Inputs'!$D$116</definedName>
-    <definedName name="selected_high">'Inputs'!$D$117</definedName>
-    <definedName name="sens_wacc_step">'Inputs'!$D$120</definedName>
-    <definedName name="sens_wacc_count">'Inputs'!$D$121</definedName>
-    <definedName name="sens_terminal_g_step">'Inputs'!$D$122</definedName>
-    <definedName name="sens_terminal_g_count">'Inputs'!$D$123</definedName>
-    <definedName name="sens_revenue_g_step">'Inputs'!$D$124</definedName>
-    <definedName name="sens_ebitda_margin_step">'Inputs'!$D$125</definedName>
-    <definedName name="cocos_table">'Inputs'!$A$129:$L$158</definedName>
-    <definedName name="precedents_table">'Inputs'!$A$162:$I$176</definedName>
-    <definedName name="segments_table">'Inputs'!$A$181:$M$185</definedName>
+    <definedName name="gross_profit_y0">'Inputs'!$D$38</definedName>
+    <definedName name="opex_y0">'Inputs'!$D$39</definedName>
+    <definedName name="ebitda_y0">'Inputs'!$D$40</definedName>
+    <definedName name="ebit_y0">'Inputs'!$D$41</definedName>
+    <definedName name="revenue_growth_y1">'Inputs'!$D$42</definedName>
+    <definedName name="revenue_growth_y2">'Inputs'!$D$43</definedName>
+    <definedName name="revenue_growth_y3">'Inputs'!$D$44</definedName>
+    <definedName name="revenue_growth_y4">'Inputs'!$D$45</definedName>
+    <definedName name="revenue_growth_y5">'Inputs'!$D$46</definedName>
+    <definedName name="gross_margin_y1">'Inputs'!$D$47</definedName>
+    <definedName name="gross_margin_y2">'Inputs'!$D$48</definedName>
+    <definedName name="gross_margin_y3">'Inputs'!$D$49</definedName>
+    <definedName name="gross_margin_y4">'Inputs'!$D$50</definedName>
+    <definedName name="gross_margin_y5">'Inputs'!$D$51</definedName>
+    <definedName name="opex_pct_revenue_y1">'Inputs'!$D$52</definedName>
+    <definedName name="opex_pct_revenue_y2">'Inputs'!$D$53</definedName>
+    <definedName name="opex_pct_revenue_y3">'Inputs'!$D$54</definedName>
+    <definedName name="opex_pct_revenue_y4">'Inputs'!$D$55</definedName>
+    <definedName name="opex_pct_revenue_y5">'Inputs'!$D$56</definedName>
+    <definedName name="capex_pct_revenue_y1">'Inputs'!$D$57</definedName>
+    <definedName name="capex_pct_revenue_y2">'Inputs'!$D$58</definedName>
+    <definedName name="capex_pct_revenue_y3">'Inputs'!$D$59</definedName>
+    <definedName name="capex_pct_revenue_y4">'Inputs'!$D$60</definedName>
+    <definedName name="capex_pct_revenue_y5">'Inputs'!$D$61</definedName>
+    <definedName name="dep_pct_revenue_y1">'Inputs'!$D$62</definedName>
+    <definedName name="dep_pct_revenue_y2">'Inputs'!$D$63</definedName>
+    <definedName name="dep_pct_revenue_y3">'Inputs'!$D$64</definedName>
+    <definedName name="dep_pct_revenue_y4">'Inputs'!$D$65</definedName>
+    <definedName name="dep_pct_revenue_y5">'Inputs'!$D$66</definedName>
+    <definedName name="nwc_pct_sales_y1">'Inputs'!$D$67</definedName>
+    <definedName name="nwc_pct_sales_y2">'Inputs'!$D$68</definedName>
+    <definedName name="nwc_pct_sales_y3">'Inputs'!$D$69</definedName>
+    <definedName name="nwc_pct_sales_y4">'Inputs'!$D$70</definedName>
+    <definedName name="nwc_pct_sales_y5">'Inputs'!$D$71</definedName>
+    <definedName name="terminal_method">'Inputs'!$D$74</definedName>
+    <definedName name="terminal_growth_rate">'Inputs'!$D$75</definedName>
+    <definedName name="terminal_exit_multiple_type">'Inputs'!$D$76</definedName>
+    <definedName name="terminal_exit_multiple_value">'Inputs'!$D$77</definedName>
+    <definedName name="risk_free_rate">'Inputs'!$D$80</definedName>
+    <definedName name="risk_free_rate_source">'Inputs'!$D$81</definedName>
+    <definedName name="equity_risk_premium">'Inputs'!$D$82</definedName>
+    <definedName name="country_risk_premium">'Inputs'!$D$83</definedName>
+    <definedName name="unlevered_beta_per_mgmt">'Inputs'!$D$84</definedName>
+    <definedName name="unlevered_beta_indep">'Inputs'!$E$84</definedName>
+    <definedName name="target_debt_to_equity_per_mgmt">'Inputs'!$D$85</definedName>
+    <definedName name="target_debt_to_equity_indep">'Inputs'!$E$85</definedName>
+    <definedName name="levered_beta_per_mgmt">'Inputs'!$D$86</definedName>
+    <definedName name="levered_beta_indep">'Inputs'!$E$86</definedName>
+    <definedName name="size_premium_per_mgmt">'Inputs'!$D$87</definedName>
+    <definedName name="size_premium_indep">'Inputs'!$E$87</definedName>
+    <definedName name="specific_risk_premium_per_mgmt">'Inputs'!$D$88</definedName>
+    <definedName name="specific_risk_premium_indep">'Inputs'!$E$88</definedName>
+    <definedName name="cost_of_equity_per_mgmt">'Inputs'!$D$89</definedName>
+    <definedName name="cost_of_equity_indep">'Inputs'!$E$89</definedName>
+    <definedName name="pretax_cost_of_debt_per_mgmt">'Inputs'!$D$90</definedName>
+    <definedName name="pretax_cost_of_debt_indep">'Inputs'!$E$90</definedName>
+    <definedName name="aftertax_cost_of_debt_per_mgmt">'Inputs'!$D$91</definedName>
+    <definedName name="aftertax_cost_of_debt_indep">'Inputs'!$E$91</definedName>
+    <definedName name="target_debt_weight_per_mgmt">'Inputs'!$D$92</definedName>
+    <definedName name="target_debt_weight_indep">'Inputs'!$E$92</definedName>
+    <definedName name="target_equity_weight_per_mgmt">'Inputs'!$D$93</definedName>
+    <definedName name="target_equity_weight_indep">'Inputs'!$E$93</definedName>
+    <definedName name="wacc_per_mgmt">'Inputs'!$D$94</definedName>
+    <definedName name="wacc_indep">'Inputs'!$E$94</definedName>
+    <definedName name="surplus_assets">'Inputs'!$D$97</definedName>
+    <definedName name="net_debt_override">'Inputs'!$D$98</definedName>
+    <definedName name="minority_interests">'Inputs'!$D$99</definedName>
+    <definedName name="non_operating_assets">'Inputs'!$D$100</definedName>
+    <definedName name="dlom_pct">'Inputs'!$D$101</definedName>
+    <definedName name="dloc_pct">'Inputs'!$D$102</definedName>
+    <definedName name="equity_interest_pct">'Inputs'!$D$103</definedName>
+    <definedName name="shares_outstanding">'Inputs'!$D$104</definedName>
+    <definedName name="shares_outstanding_diluted">'Inputs'!$D$105</definedName>
+    <definedName name="pre_money_pct">'Inputs'!$D$106</definedName>
+    <definedName name="capitalize_rd">'Inputs'!$D$109</definedName>
+    <definedName name="rd_amortization_years">'Inputs'!$D$110</definedName>
+    <definedName name="convert_operating_leases">'Inputs'!$D$111</definedName>
+    <definedName name="lease_discount_rate">'Inputs'!$D$112</definedName>
+    <definedName name="weight_dcf">'Inputs'!$D$115</definedName>
+    <definedName name="weight_comps">'Inputs'!$D$116</definedName>
+    <definedName name="weight_precedent">'Inputs'!$D$117</definedName>
+    <definedName name="weight_nav">'Inputs'!$D$118</definedName>
+    <definedName name="selected_low">'Inputs'!$D$119</definedName>
+    <definedName name="selected_mid">'Inputs'!$D$120</definedName>
+    <definedName name="selected_high">'Inputs'!$D$121</definedName>
+    <definedName name="sens_wacc_step">'Inputs'!$D$124</definedName>
+    <definedName name="sens_wacc_count">'Inputs'!$D$125</definedName>
+    <definedName name="sens_terminal_g_step">'Inputs'!$D$126</definedName>
+    <definedName name="sens_terminal_g_count">'Inputs'!$D$127</definedName>
+    <definedName name="sens_revenue_g_step">'Inputs'!$D$128</definedName>
+    <definedName name="sens_ebitda_margin_step">'Inputs'!$D$129</definedName>
+    <definedName name="cocos_table">'Inputs'!$A$133:$L$162</definedName>
+    <definedName name="precedents_table">'Inputs'!$A$166:$I$180</definedName>
+    <definedName name="segments_table">'Inputs'!$A$185:$M$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12387,7 +12391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13053,100 +13057,116 @@
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y1</t>
+          <t>gross_profit_y0</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y1)</t>
+          <t>Gross profit (Y0)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D38" s="32" t="n"/>
       <c r="E38" s="32" t="n"/>
       <c r="F38" s="33" t="n"/>
       <c r="G38" s="33" t="n"/>
-      <c r="H38" s="33" t="n"/>
+      <c r="H38" s="34" t="inlineStr">
+        <is>
+          <t>Audited Y0 gross profit; populates Projections!C12</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y2</t>
+          <t>opex_y0</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y2)</t>
+          <t>Operating expenses (Y0)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D39" s="32" t="n"/>
       <c r="E39" s="32" t="n"/>
       <c r="F39" s="33" t="n"/>
       <c r="G39" s="33" t="n"/>
-      <c r="H39" s="33" t="n"/>
+      <c r="H39" s="34" t="inlineStr">
+        <is>
+          <t>Audited Y0 opex (negative); populates Projections!C14</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y3</t>
+          <t>ebitda_y0</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y3)</t>
+          <t>EBITDA (Y0)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D40" s="32" t="n"/>
       <c r="E40" s="32" t="n"/>
       <c r="F40" s="33" t="n"/>
       <c r="G40" s="33" t="n"/>
-      <c r="H40" s="33" t="n"/>
+      <c r="H40" s="34" t="inlineStr">
+        <is>
+          <t>Audited Y0 EBITDA; populates Projections!C15</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y4</t>
+          <t>ebit_y0</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y4)</t>
+          <t>EBIT (Y0)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D41" s="32" t="n"/>
       <c r="E41" s="32" t="n"/>
       <c r="F41" s="33" t="n"/>
       <c r="G41" s="33" t="n"/>
-      <c r="H41" s="33" t="n"/>
+      <c r="H41" s="34" t="inlineStr">
+        <is>
+          <t>Audited Y0 EBIT; populates Projections!C18</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y5</t>
+          <t>revenue_growth_y1</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y5)</t>
+          <t>Revenue growth (Y1)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -13163,12 +13183,12 @@
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y1</t>
+          <t>revenue_growth_y2</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y1)</t>
+          <t>Revenue growth (Y2)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -13185,12 +13205,12 @@
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y2</t>
+          <t>revenue_growth_y3</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y2)</t>
+          <t>Revenue growth (Y3)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -13207,12 +13227,12 @@
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y3</t>
+          <t>revenue_growth_y4</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y3)</t>
+          <t>Revenue growth (Y4)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -13229,12 +13249,12 @@
     <row r="46">
       <c r="A46" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y4</t>
+          <t>revenue_growth_y5</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y4)</t>
+          <t>Revenue growth (Y5)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -13251,12 +13271,12 @@
     <row r="47">
       <c r="A47" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y5</t>
+          <t>gross_margin_y1</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y5)</t>
+          <t>Gross margin (Y1)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -13273,12 +13293,12 @@
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y1</t>
+          <t>gross_margin_y2</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y1)</t>
+          <t>Gross margin (Y2)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13295,12 +13315,12 @@
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y2</t>
+          <t>gross_margin_y3</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y2)</t>
+          <t>Gross margin (Y3)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -13317,12 +13337,12 @@
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y3</t>
+          <t>gross_margin_y4</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y3)</t>
+          <t>Gross margin (Y4)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -13339,12 +13359,12 @@
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y4</t>
+          <t>gross_margin_y5</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y4)</t>
+          <t>Gross margin (Y5)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -13361,12 +13381,12 @@
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y5</t>
+          <t>opex_pct_revenue_y1</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y5)</t>
+          <t>Opex % of revenue (Y1)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -13383,12 +13403,12 @@
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y1</t>
+          <t>opex_pct_revenue_y2</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y1)</t>
+          <t>Opex % of revenue (Y2)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -13405,12 +13425,12 @@
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y2</t>
+          <t>opex_pct_revenue_y3</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y2)</t>
+          <t>Opex % of revenue (Y3)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13427,12 +13447,12 @@
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y3</t>
+          <t>opex_pct_revenue_y4</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y3)</t>
+          <t>Opex % of revenue (Y4)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13449,12 +13469,12 @@
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y4</t>
+          <t>opex_pct_revenue_y5</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y4)</t>
+          <t>Opex % of revenue (Y5)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13471,12 +13491,12 @@
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y5</t>
+          <t>capex_pct_revenue_y1</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y5)</t>
+          <t>Capex % of revenue (Y1)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13493,12 +13513,12 @@
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y1</t>
+          <t>capex_pct_revenue_y2</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y1)</t>
+          <t>Capex % of revenue (Y2)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13515,12 +13535,12 @@
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y2</t>
+          <t>capex_pct_revenue_y3</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y2)</t>
+          <t>Capex % of revenue (Y3)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13537,12 +13557,12 @@
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y3</t>
+          <t>capex_pct_revenue_y4</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y3)</t>
+          <t>Capex % of revenue (Y4)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -13559,12 +13579,12 @@
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y4</t>
+          <t>capex_pct_revenue_y5</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y4)</t>
+          <t>Capex % of revenue (Y5)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -13581,12 +13601,12 @@
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y5</t>
+          <t>dep_pct_revenue_y1</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y5)</t>
+          <t>Depreciation % of revenue (Y1)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -13603,12 +13623,12 @@
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y1</t>
+          <t>dep_pct_revenue_y2</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y1)</t>
+          <t>Depreciation % of revenue (Y2)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -13625,12 +13645,12 @@
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y2</t>
+          <t>dep_pct_revenue_y3</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y2)</t>
+          <t>Depreciation % of revenue (Y3)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13647,12 +13667,12 @@
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y3</t>
+          <t>dep_pct_revenue_y4</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y3)</t>
+          <t>Depreciation % of revenue (Y4)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13669,12 +13689,12 @@
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y4</t>
+          <t>dep_pct_revenue_y5</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y4)</t>
+          <t>Depreciation % of revenue (Y5)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -13691,12 +13711,12 @@
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y5</t>
+          <t>nwc_pct_sales_y1</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y5)</t>
+          <t>Working capital % of sales (Y1)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -13710,48 +13730,81 @@
       <c r="G67" s="33" t="n"/>
       <c r="H67" s="33" t="n"/>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Section E — Terminal value  (Core)</t>
-        </is>
-      </c>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>nwc_pct_sales_y2</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Working capital % of sales (Y2)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="n"/>
+      <c r="E68" s="32" t="n"/>
+      <c r="F68" s="33" t="n"/>
+      <c r="G68" s="33" t="n"/>
+      <c r="H68" s="33" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>nwc_pct_sales_y3</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Working capital % of sales (Y3)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="n"/>
+      <c r="E69" s="32" t="n"/>
+      <c r="F69" s="33" t="n"/>
+      <c r="G69" s="33" t="n"/>
+      <c r="H69" s="33" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>terminal_method</t>
+          <t>nwc_pct_sales_y4</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Terminal value method</t>
+          <t>Working capital % of sales (Y4)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D70" s="32" t="n"/>
       <c r="E70" s="32" t="n"/>
       <c r="F70" s="33" t="n"/>
       <c r="G70" s="33" t="n"/>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>gordon_growth | exit_multiple</t>
-        </is>
-      </c>
+      <c r="H70" s="33" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>terminal_growth_rate</t>
+          <t>nwc_pct_sales_y5</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth rate</t>
+          <t>Working capital % of sales (Y5)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -13765,71 +13818,75 @@
       <c r="G71" s="33" t="n"/>
       <c r="H71" s="33" t="n"/>
     </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>terminal_exit_multiple_type</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Exit multiple metric</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Section E — Terminal value  (Core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>terminal_method</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Terminal value method</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="D72" s="32" t="n"/>
-      <c r="E72" s="32" t="n"/>
-      <c r="F72" s="33" t="n"/>
-      <c r="G72" s="33" t="n"/>
-      <c r="H72" s="33" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>terminal_exit_multiple_value</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Exit multiple value</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="n"/>
-      <c r="E73" s="32" t="n"/>
-      <c r="F73" s="33" t="n"/>
-      <c r="G73" s="33" t="n"/>
-      <c r="H73" s="33" t="n"/>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Section F — WACC inputs  (Core)</t>
-        </is>
-      </c>
+      <c r="D74" s="32" t="n"/>
+      <c r="E74" s="32" t="n"/>
+      <c r="F74" s="33" t="n"/>
+      <c r="G74" s="33" t="n"/>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>gordon_growth | exit_multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>terminal_growth_rate</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Terminal growth rate</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="n"/>
+      <c r="E75" s="32" t="n"/>
+      <c r="F75" s="33" t="n"/>
+      <c r="G75" s="33" t="n"/>
+      <c r="H75" s="33" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>risk_free_rate</t>
+          <t>terminal_exit_multiple_type</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Risk-free rate</t>
+          <t>Exit multiple metric</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="D76" s="32" t="n"/>
@@ -13841,17 +13898,17 @@
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>risk_free_rate_source</t>
+          <t>terminal_exit_multiple_value</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Risk-free rate source descriptor</t>
+          <t>Exit multiple value</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D77" s="32" t="n"/>
@@ -13860,64 +13917,27 @@
       <c r="G77" s="33" t="n"/>
       <c r="H77" s="33" t="n"/>
     </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>equity_risk_premium</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Equity risk premium (ERP)</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="n"/>
-      <c r="E78" s="32" t="n"/>
-      <c r="F78" s="33" t="n"/>
-      <c r="G78" s="33" t="n"/>
-      <c r="H78" s="33" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>country_risk_premium</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Country risk premium</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="n"/>
-      <c r="E79" s="32" t="n"/>
-      <c r="F79" s="33" t="n"/>
-      <c r="G79" s="33" t="n"/>
-      <c r="H79" s="33" t="n"/>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Section F — WACC inputs  (Core)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>unlevered_beta</t>
+          <t>risk_free_rate</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Unlevered beta</t>
+          <t>Risk-free rate</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D80" s="32" t="n"/>
@@ -13929,17 +13949,17 @@
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>target_debt_to_equity</t>
+          <t>risk_free_rate_source</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Target D/E ratio</t>
+          <t>Risk-free rate source descriptor</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D81" s="32" t="n"/>
@@ -13951,27 +13971,21 @@
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>levered_beta</t>
+          <t>equity_risk_premium</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Levered beta (calculated)</t>
+          <t>Equity risk premium (ERP)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D82" s="35">
-        <f>WACC!E10</f>
-        <v/>
-      </c>
-      <c r="E82" s="35">
-        <f>WACC!F10</f>
-        <v/>
-      </c>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="n"/>
+      <c r="E82" s="32" t="n"/>
       <c r="F82" s="33" t="n"/>
       <c r="G82" s="33" t="n"/>
       <c r="H82" s="33" t="n"/>
@@ -13979,12 +13993,12 @@
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
         <is>
-          <t>size_premium</t>
+          <t>country_risk_premium</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Size premium</t>
+          <t>Country risk premium</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -14001,17 +14015,17 @@
     <row r="84">
       <c r="A84" s="31" t="inlineStr">
         <is>
-          <t>specific_risk_premium</t>
+          <t>unlevered_beta</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Specific risk premium</t>
+          <t>Unlevered beta</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D84" s="32" t="n"/>
@@ -14023,12 +14037,12 @@
     <row r="85">
       <c r="A85" s="31" t="inlineStr">
         <is>
-          <t>cost_of_equity</t>
+          <t>target_debt_to_equity</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity (calculated)</t>
+          <t>Target D/E ratio</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -14036,14 +14050,8 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D85" s="36">
-        <f>WACC!E16</f>
-        <v/>
-      </c>
-      <c r="E85" s="36">
-        <f>WACC!F16</f>
-        <v/>
-      </c>
+      <c r="D85" s="32" t="n"/>
+      <c r="E85" s="32" t="n"/>
       <c r="F85" s="33" t="n"/>
       <c r="G85" s="33" t="n"/>
       <c r="H85" s="33" t="n"/>
@@ -14051,21 +14059,27 @@
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>pretax_cost_of_debt</t>
+          <t>levered_beta</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt</t>
+          <t>Levered beta (calculated)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D86" s="32" t="n"/>
-      <c r="E86" s="32" t="n"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D86" s="35">
+        <f>WACC!E10</f>
+        <v/>
+      </c>
+      <c r="E86" s="35">
+        <f>WACC!F10</f>
+        <v/>
+      </c>
       <c r="F86" s="33" t="n"/>
       <c r="G86" s="33" t="n"/>
       <c r="H86" s="33" t="n"/>
@@ -14073,12 +14087,12 @@
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
         <is>
-          <t>aftertax_cost_of_debt</t>
+          <t>size_premium</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>After-tax cost of debt (calculated)</t>
+          <t>Size premium</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -14086,14 +14100,8 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D87" s="36">
-        <f>WACC!E20</f>
-        <v/>
-      </c>
-      <c r="E87" s="36">
-        <f>WACC!F20</f>
-        <v/>
-      </c>
+      <c r="D87" s="32" t="n"/>
+      <c r="E87" s="32" t="n"/>
       <c r="F87" s="33" t="n"/>
       <c r="G87" s="33" t="n"/>
       <c r="H87" s="33" t="n"/>
@@ -14101,12 +14109,12 @@
     <row r="88">
       <c r="A88" s="31" t="inlineStr">
         <is>
-          <t>target_debt_weight</t>
+          <t>specific_risk_premium</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>D/V (debt weight)</t>
+          <t>Specific risk premium</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -14123,12 +14131,12 @@
     <row r="89">
       <c r="A89" s="31" t="inlineStr">
         <is>
-          <t>target_equity_weight</t>
+          <t>cost_of_equity</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>E/V (equity weight)</t>
+          <t>Cost of equity (calculated)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -14136,8 +14144,14 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D89" s="32" t="n"/>
-      <c r="E89" s="32" t="n"/>
+      <c r="D89" s="36">
+        <f>WACC!E16</f>
+        <v/>
+      </c>
+      <c r="E89" s="36">
+        <f>WACC!F16</f>
+        <v/>
+      </c>
       <c r="F89" s="33" t="n"/>
       <c r="G89" s="33" t="n"/>
       <c r="H89" s="33" t="n"/>
@@ -14145,12 +14159,12 @@
     <row r="90">
       <c r="A90" s="31" t="inlineStr">
         <is>
-          <t>wacc</t>
+          <t>pretax_cost_of_debt</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>WACC (calculated)</t>
+          <t>Pre-tax cost of debt</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -14158,39 +14172,76 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D90" s="36">
-        <f>WACC!E25</f>
-        <v/>
-      </c>
-      <c r="E90" s="36">
-        <f>WACC!F25</f>
-        <v/>
-      </c>
+      <c r="D90" s="32" t="n"/>
+      <c r="E90" s="32" t="n"/>
       <c r="F90" s="33" t="n"/>
       <c r="G90" s="33" t="n"/>
       <c r="H90" s="33" t="n"/>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Section I — EV -&gt; Equity bridge  (Core)</t>
-        </is>
-      </c>
+    <row r="91">
+      <c r="A91" s="31" t="inlineStr">
+        <is>
+          <t>aftertax_cost_of_debt</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>After-tax cost of debt (calculated)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D91" s="36">
+        <f>WACC!E20</f>
+        <v/>
+      </c>
+      <c r="E91" s="36">
+        <f>WACC!F20</f>
+        <v/>
+      </c>
+      <c r="F91" s="33" t="n"/>
+      <c r="G91" s="33" t="n"/>
+      <c r="H91" s="33" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="31" t="inlineStr">
+        <is>
+          <t>target_debt_weight</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>D/V (debt weight)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="n"/>
+      <c r="E92" s="32" t="n"/>
+      <c r="F92" s="33" t="n"/>
+      <c r="G92" s="33" t="n"/>
+      <c r="H92" s="33" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="31" t="inlineStr">
         <is>
-          <t>surplus_assets</t>
+          <t>target_equity_weight</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Surplus / non-operating assets</t>
+          <t>E/V (equity weight)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D93" s="32" t="n"/>
@@ -14202,83 +14253,52 @@
     <row r="94">
       <c r="A94" s="31" t="inlineStr">
         <is>
-          <t>net_debt_override</t>
+          <t>wacc</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Net debt (override)</t>
+          <t>WACC (calculated)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D94" s="32" t="n"/>
-      <c r="E94" s="32" t="n"/>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D94" s="36">
+        <f>WACC!E25</f>
+        <v/>
+      </c>
+      <c r="E94" s="36">
+        <f>WACC!F25</f>
+        <v/>
+      </c>
       <c r="F94" s="33" t="n"/>
       <c r="G94" s="33" t="n"/>
       <c r="H94" s="33" t="n"/>
     </row>
-    <row r="95">
-      <c r="A95" s="31" t="inlineStr">
-        <is>
-          <t>minority_interests</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Minority interests</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D95" s="32" t="n"/>
-      <c r="E95" s="32" t="n"/>
-      <c r="F95" s="33" t="n"/>
-      <c r="G95" s="33" t="n"/>
-      <c r="H95" s="33" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="31" t="inlineStr">
-        <is>
-          <t>non_operating_assets</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Non-operating assets</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D96" s="32" t="n"/>
-      <c r="E96" s="32" t="n"/>
-      <c r="F96" s="33" t="n"/>
-      <c r="G96" s="33" t="n"/>
-      <c r="H96" s="33" t="n"/>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Section I — EV -&gt; Equity bridge  (Core)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="31" t="inlineStr">
         <is>
-          <t>dlom_pct</t>
+          <t>surplus_assets</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>DLOM rate</t>
+          <t>Surplus / non-operating assets</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D97" s="32" t="n"/>
@@ -14290,17 +14310,17 @@
     <row r="98">
       <c r="A98" s="31" t="inlineStr">
         <is>
-          <t>dloc_pct</t>
+          <t>net_debt_override</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>DLOC rate</t>
+          <t>Net debt (override)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D98" s="32" t="n"/>
@@ -14312,17 +14332,17 @@
     <row r="99">
       <c r="A99" s="31" t="inlineStr">
         <is>
-          <t>equity_interest_pct</t>
+          <t>minority_interests</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Client's % equity interest</t>
+          <t>Minority interests</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D99" s="32" t="n"/>
@@ -14334,17 +14354,17 @@
     <row r="100">
       <c r="A100" s="31" t="inlineStr">
         <is>
-          <t>shares_outstanding</t>
+          <t>non_operating_assets</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Shares outstanding (basic)</t>
+          <t>Non-operating assets</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D100" s="32" t="n"/>
@@ -14356,17 +14376,17 @@
     <row r="101">
       <c r="A101" s="31" t="inlineStr">
         <is>
-          <t>shares_outstanding_diluted</t>
+          <t>dlom_pct</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Shares outstanding (diluted)</t>
+          <t>DLOM rate</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D101" s="32" t="n"/>
@@ -14378,12 +14398,12 @@
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>pre_money_pct</t>
+          <t>dloc_pct</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Pre-money equity %</t>
+          <t>DLOC rate</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -14397,27 +14417,64 @@
       <c r="G102" s="33" t="n"/>
       <c r="H102" s="33" t="n"/>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="37" t="inlineStr">
-        <is>
-          <t>Section J — Adjustment toggles  (Extended)</t>
-        </is>
-      </c>
+    <row r="103">
+      <c r="A103" s="31" t="inlineStr">
+        <is>
+          <t>equity_interest_pct</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Client's % equity interest</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D103" s="32" t="n"/>
+      <c r="E103" s="32" t="n"/>
+      <c r="F103" s="33" t="n"/>
+      <c r="G103" s="33" t="n"/>
+      <c r="H103" s="33" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="31" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Shares outstanding (basic)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D104" s="32" t="n"/>
+      <c r="E104" s="32" t="n"/>
+      <c r="F104" s="33" t="n"/>
+      <c r="G104" s="33" t="n"/>
+      <c r="H104" s="33" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="31" t="inlineStr">
         <is>
-          <t>capitalize_rd</t>
+          <t>shares_outstanding_diluted</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Capitalize R&amp;D?</t>
+          <t>Shares outstanding (diluted)</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D105" s="32" t="n"/>
@@ -14429,17 +14486,17 @@
     <row r="106">
       <c r="A106" s="31" t="inlineStr">
         <is>
-          <t>rd_amortization_years</t>
+          <t>pre_money_pct</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D amortization period (years)</t>
+          <t>Pre-money equity %</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D106" s="32" t="n"/>
@@ -14448,71 +14505,71 @@
       <c r="G106" s="33" t="n"/>
       <c r="H106" s="33" t="n"/>
     </row>
-    <row r="107">
-      <c r="A107" s="31" t="inlineStr">
-        <is>
-          <t>convert_operating_leases</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Convert operating leases to debt?</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="37" t="inlineStr">
+        <is>
+          <t>Section J — Adjustment toggles  (Extended)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="31" t="inlineStr">
+        <is>
+          <t>capitalize_rd</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Capitalize R&amp;D?</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="D107" s="32" t="n"/>
-      <c r="E107" s="32" t="n"/>
-      <c r="F107" s="33" t="n"/>
-      <c r="G107" s="33" t="n"/>
-      <c r="H107" s="33" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="31" t="inlineStr">
-        <is>
-          <t>lease_discount_rate</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Lease discount rate</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D108" s="32" t="n"/>
-      <c r="E108" s="32" t="n"/>
-      <c r="F108" s="33" t="n"/>
-      <c r="G108" s="33" t="n"/>
-      <c r="H108" s="33" t="n"/>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="37" t="inlineStr">
-        <is>
-          <t>Section K — Football field weights  (Extended)</t>
-        </is>
-      </c>
+      <c r="D109" s="32" t="n"/>
+      <c r="E109" s="32" t="n"/>
+      <c r="F109" s="33" t="n"/>
+      <c r="G109" s="33" t="n"/>
+      <c r="H109" s="33" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="31" t="inlineStr">
+        <is>
+          <t>rd_amortization_years</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>R&amp;D amortization period (years)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D110" s="32" t="n"/>
+      <c r="E110" s="32" t="n"/>
+      <c r="F110" s="33" t="n"/>
+      <c r="G110" s="33" t="n"/>
+      <c r="H110" s="33" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="31" t="inlineStr">
         <is>
-          <t>weight_dcf</t>
+          <t>convert_operating_leases</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>DCF weight</t>
+          <t>Convert operating leases to debt?</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D111" s="32" t="n"/>
@@ -14524,12 +14581,12 @@
     <row r="112">
       <c r="A112" s="31" t="inlineStr">
         <is>
-          <t>weight_comps</t>
+          <t>lease_discount_rate</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Comparable companies weight</t>
+          <t>Lease discount rate</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -14543,64 +14600,27 @@
       <c r="G112" s="33" t="n"/>
       <c r="H112" s="33" t="n"/>
     </row>
-    <row r="113">
-      <c r="A113" s="31" t="inlineStr">
-        <is>
-          <t>weight_precedent</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Precedent transactions weight</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D113" s="32" t="n"/>
-      <c r="E113" s="32" t="n"/>
-      <c r="F113" s="33" t="n"/>
-      <c r="G113" s="33" t="n"/>
-      <c r="H113" s="33" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="31" t="inlineStr">
-        <is>
-          <t>weight_nav</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>NAV / asset-based weight</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D114" s="32" t="n"/>
-      <c r="E114" s="32" t="n"/>
-      <c r="F114" s="33" t="n"/>
-      <c r="G114" s="33" t="n"/>
-      <c r="H114" s="33" t="n"/>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="37" t="inlineStr">
+        <is>
+          <t>Section K — Football field weights  (Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="31" t="inlineStr">
         <is>
-          <t>selected_low</t>
+          <t>weight_dcf</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation low</t>
+          <t>DCF weight</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D115" s="32" t="n"/>
@@ -14612,17 +14632,17 @@
     <row r="116">
       <c r="A116" s="31" t="inlineStr">
         <is>
-          <t>selected_mid</t>
+          <t>weight_comps</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation mid</t>
+          <t>Comparable companies weight</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D116" s="32" t="n"/>
@@ -14634,17 +14654,17 @@
     <row r="117">
       <c r="A117" s="31" t="inlineStr">
         <is>
-          <t>selected_high</t>
+          <t>weight_precedent</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation high</t>
+          <t>Precedent transactions weight</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D117" s="32" t="n"/>
@@ -14653,27 +14673,64 @@
       <c r="G117" s="33" t="n"/>
       <c r="H117" s="33" t="n"/>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="37" t="inlineStr">
-        <is>
-          <t>Section L — Sensitivity ranges  (Extended)</t>
-        </is>
-      </c>
+    <row r="118">
+      <c r="A118" s="31" t="inlineStr">
+        <is>
+          <t>weight_nav</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>NAV / asset-based weight</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D118" s="32" t="n"/>
+      <c r="E118" s="32" t="n"/>
+      <c r="F118" s="33" t="n"/>
+      <c r="G118" s="33" t="n"/>
+      <c r="H118" s="33" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="31" t="inlineStr">
+        <is>
+          <t>selected_low</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Selected valuation low</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D119" s="32" t="n"/>
+      <c r="E119" s="32" t="n"/>
+      <c r="F119" s="33" t="n"/>
+      <c r="G119" s="33" t="n"/>
+      <c r="H119" s="33" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="31" t="inlineStr">
         <is>
-          <t>sens_wacc_step</t>
+          <t>selected_mid</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>WACC sensitivity step</t>
+          <t>Selected valuation mid</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D120" s="32" t="n"/>
@@ -14685,17 +14742,17 @@
     <row r="121">
       <c r="A121" s="31" t="inlineStr">
         <is>
-          <t>sens_wacc_count</t>
+          <t>selected_high</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>WACC steps each side of base</t>
+          <t>Selected valuation high</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D121" s="32" t="n"/>
@@ -14704,59 +14761,22 @@
       <c r="G121" s="33" t="n"/>
       <c r="H121" s="33" t="n"/>
     </row>
-    <row r="122">
-      <c r="A122" s="31" t="inlineStr">
-        <is>
-          <t>sens_terminal_g_step</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>Terminal g sensitivity step</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D122" s="32" t="n"/>
-      <c r="E122" s="32" t="n"/>
-      <c r="F122" s="33" t="n"/>
-      <c r="G122" s="33" t="n"/>
-      <c r="H122" s="33" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="31" t="inlineStr">
-        <is>
-          <t>sens_terminal_g_count</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Terminal g steps each side</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D123" s="32" t="n"/>
-      <c r="E123" s="32" t="n"/>
-      <c r="F123" s="33" t="n"/>
-      <c r="G123" s="33" t="n"/>
-      <c r="H123" s="33" t="n"/>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="37" t="inlineStr">
+        <is>
+          <t>Section L — Sensitivity ranges  (Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="31" t="inlineStr">
         <is>
-          <t>sens_revenue_g_step</t>
+          <t>sens_wacc_step</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth sens step</t>
+          <t>WACC sensitivity step</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -14773,17 +14793,17 @@
     <row r="125">
       <c r="A125" s="31" t="inlineStr">
         <is>
-          <t>sens_ebitda_margin_step</t>
+          <t>sens_wacc_count</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>EBITDA margin sens step</t>
+          <t>WACC steps each side of base</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D125" s="32" t="n"/>
@@ -14792,130 +14812,162 @@
       <c r="G125" s="33" t="n"/>
       <c r="H125" s="33" t="n"/>
     </row>
+    <row r="126">
+      <c r="A126" s="31" t="inlineStr">
+        <is>
+          <t>sens_terminal_g_step</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Terminal g sensitivity step</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D126" s="32" t="n"/>
+      <c r="E126" s="32" t="n"/>
+      <c r="F126" s="33" t="n"/>
+      <c r="G126" s="33" t="n"/>
+      <c r="H126" s="33" t="n"/>
+    </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Section G — Comparable companies table  (Core)</t>
-        </is>
-      </c>
+      <c r="A127" s="31" t="inlineStr">
+        <is>
+          <t>sens_terminal_g_count</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Terminal g steps each side</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D127" s="32" t="n"/>
+      <c r="E127" s="32" t="n"/>
+      <c r="F127" s="33" t="n"/>
+      <c r="G127" s="33" t="n"/>
+      <c r="H127" s="33" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="21" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B128" s="21" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="C128" s="21" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="D128" s="21" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="E128" s="21" t="inlineStr">
-        <is>
-          <t>Business description</t>
-        </is>
-      </c>
-      <c r="F128" s="21" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="G128" s="21" t="inlineStr">
-        <is>
-          <t>Accounting standard</t>
-        </is>
-      </c>
-      <c r="H128" s="21" t="inlineStr">
-        <is>
-          <t>Market cap (USD mm)</t>
-        </is>
-      </c>
-      <c r="I128" s="21" t="inlineStr">
-        <is>
-          <t>D/E ratio</t>
-        </is>
-      </c>
-      <c r="J128" s="21" t="inlineStr">
-        <is>
-          <t>Raw levered beta</t>
-        </is>
-      </c>
-      <c r="K128" s="21" t="inlineStr">
-        <is>
-          <t>Effective tax rate</t>
-        </is>
-      </c>
-      <c r="L128" s="21" t="inlineStr">
-        <is>
-          <t>Unlevered beta (calculated)</t>
-        </is>
-      </c>
+      <c r="A128" s="31" t="inlineStr">
+        <is>
+          <t>sens_revenue_g_step</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Revenue growth sens step</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D128" s="32" t="n"/>
+      <c r="E128" s="32" t="n"/>
+      <c r="F128" s="33" t="n"/>
+      <c r="G128" s="33" t="n"/>
+      <c r="H128" s="33" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="33" t="n"/>
-      <c r="B129" s="33" t="n"/>
-      <c r="C129" s="33" t="n"/>
-      <c r="D129" s="33" t="n"/>
-      <c r="E129" s="33" t="n"/>
+      <c r="A129" s="31" t="inlineStr">
+        <is>
+          <t>sens_ebitda_margin_step</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA margin sens step</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D129" s="32" t="n"/>
+      <c r="E129" s="32" t="n"/>
       <c r="F129" s="33" t="n"/>
       <c r="G129" s="33" t="n"/>
       <c r="H129" s="33" t="n"/>
-      <c r="I129" s="33" t="n"/>
-      <c r="J129" s="33" t="n"/>
-      <c r="K129" s="33" t="n"/>
-      <c r="L129" s="33" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="33" t="n"/>
-      <c r="B130" s="33" t="n"/>
-      <c r="C130" s="33" t="n"/>
-      <c r="D130" s="33" t="n"/>
-      <c r="E130" s="33" t="n"/>
-      <c r="F130" s="33" t="n"/>
-      <c r="G130" s="33" t="n"/>
-      <c r="H130" s="33" t="n"/>
-      <c r="I130" s="33" t="n"/>
-      <c r="J130" s="33" t="n"/>
-      <c r="K130" s="33" t="n"/>
-      <c r="L130" s="33" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="33" t="n"/>
-      <c r="B131" s="33" t="n"/>
-      <c r="C131" s="33" t="n"/>
-      <c r="D131" s="33" t="n"/>
-      <c r="E131" s="33" t="n"/>
-      <c r="F131" s="33" t="n"/>
-      <c r="G131" s="33" t="n"/>
-      <c r="H131" s="33" t="n"/>
-      <c r="I131" s="33" t="n"/>
-      <c r="J131" s="33" t="n"/>
-      <c r="K131" s="33" t="n"/>
-      <c r="L131" s="33" t="n"/>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Section G — Comparable companies table  (Core)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="33" t="n"/>
-      <c r="B132" s="33" t="n"/>
-      <c r="C132" s="33" t="n"/>
-      <c r="D132" s="33" t="n"/>
-      <c r="E132" s="33" t="n"/>
-      <c r="F132" s="33" t="n"/>
-      <c r="G132" s="33" t="n"/>
-      <c r="H132" s="33" t="n"/>
-      <c r="I132" s="33" t="n"/>
-      <c r="J132" s="33" t="n"/>
-      <c r="K132" s="33" t="n"/>
-      <c r="L132" s="33" t="n"/>
+      <c r="A132" s="21" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B132" s="21" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D132" s="21" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="E132" s="21" t="inlineStr">
+        <is>
+          <t>Business description</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="G132" s="21" t="inlineStr">
+        <is>
+          <t>Accounting standard</t>
+        </is>
+      </c>
+      <c r="H132" s="21" t="inlineStr">
+        <is>
+          <t>Market cap (USD mm)</t>
+        </is>
+      </c>
+      <c r="I132" s="21" t="inlineStr">
+        <is>
+          <t>D/E ratio</t>
+        </is>
+      </c>
+      <c r="J132" s="21" t="inlineStr">
+        <is>
+          <t>Raw levered beta</t>
+        </is>
+      </c>
+      <c r="K132" s="21" t="inlineStr">
+        <is>
+          <t>Effective tax rate</t>
+        </is>
+      </c>
+      <c r="L132" s="21" t="inlineStr">
+        <is>
+          <t>Unlevered beta (calculated)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="33" t="n"/>
@@ -15281,59 +15333,47 @@
       <c r="K158" s="33" t="n"/>
       <c r="L158" s="33" t="n"/>
     </row>
+    <row r="159">
+      <c r="A159" s="33" t="n"/>
+      <c r="B159" s="33" t="n"/>
+      <c r="C159" s="33" t="n"/>
+      <c r="D159" s="33" t="n"/>
+      <c r="E159" s="33" t="n"/>
+      <c r="F159" s="33" t="n"/>
+      <c r="G159" s="33" t="n"/>
+      <c r="H159" s="33" t="n"/>
+      <c r="I159" s="33" t="n"/>
+      <c r="J159" s="33" t="n"/>
+      <c r="K159" s="33" t="n"/>
+      <c r="L159" s="33" t="n"/>
+    </row>
     <row r="160">
-      <c r="A160" s="37" t="inlineStr">
-        <is>
-          <t>Section H — Precedent transactions  (Extended)</t>
-        </is>
-      </c>
+      <c r="A160" s="33" t="n"/>
+      <c r="B160" s="33" t="n"/>
+      <c r="C160" s="33" t="n"/>
+      <c r="D160" s="33" t="n"/>
+      <c r="E160" s="33" t="n"/>
+      <c r="F160" s="33" t="n"/>
+      <c r="G160" s="33" t="n"/>
+      <c r="H160" s="33" t="n"/>
+      <c r="I160" s="33" t="n"/>
+      <c r="J160" s="33" t="n"/>
+      <c r="K160" s="33" t="n"/>
+      <c r="L160" s="33" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="21" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="B161" s="21" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C161" s="21" t="inlineStr">
-        <is>
-          <t>Acquirer</t>
-        </is>
-      </c>
-      <c r="D161" s="21" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="E161" s="21" t="inlineStr">
-        <is>
-          <t>EV (USD mm)</t>
-        </is>
-      </c>
-      <c r="F161" s="21" t="inlineStr">
-        <is>
-          <t>EV/Revenue</t>
-        </is>
-      </c>
-      <c r="G161" s="21" t="inlineStr">
-        <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="H161" s="21" t="inlineStr">
-        <is>
-          <t>Premium paid</t>
-        </is>
-      </c>
-      <c r="I161" s="21" t="inlineStr">
-        <is>
-          <t>Strategic rationale</t>
-        </is>
-      </c>
+      <c r="A161" s="33" t="n"/>
+      <c r="B161" s="33" t="n"/>
+      <c r="C161" s="33" t="n"/>
+      <c r="D161" s="33" t="n"/>
+      <c r="E161" s="33" t="n"/>
+      <c r="F161" s="33" t="n"/>
+      <c r="G161" s="33" t="n"/>
+      <c r="H161" s="33" t="n"/>
+      <c r="I161" s="33" t="n"/>
+      <c r="J161" s="33" t="n"/>
+      <c r="K161" s="33" t="n"/>
+      <c r="L161" s="33" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="33" t="n"/>
@@ -15345,39 +15385,63 @@
       <c r="G162" s="33" t="n"/>
       <c r="H162" s="33" t="n"/>
       <c r="I162" s="33" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="33" t="n"/>
-      <c r="B163" s="33" t="n"/>
-      <c r="C163" s="33" t="n"/>
-      <c r="D163" s="33" t="n"/>
-      <c r="E163" s="33" t="n"/>
-      <c r="F163" s="33" t="n"/>
-      <c r="G163" s="33" t="n"/>
-      <c r="H163" s="33" t="n"/>
-      <c r="I163" s="33" t="n"/>
+      <c r="J162" s="33" t="n"/>
+      <c r="K162" s="33" t="n"/>
+      <c r="L162" s="33" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="33" t="n"/>
-      <c r="B164" s="33" t="n"/>
-      <c r="C164" s="33" t="n"/>
-      <c r="D164" s="33" t="n"/>
-      <c r="E164" s="33" t="n"/>
-      <c r="F164" s="33" t="n"/>
-      <c r="G164" s="33" t="n"/>
-      <c r="H164" s="33" t="n"/>
-      <c r="I164" s="33" t="n"/>
+      <c r="A164" s="37" t="inlineStr">
+        <is>
+          <t>Section H — Precedent transactions  (Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="33" t="n"/>
-      <c r="B165" s="33" t="n"/>
-      <c r="C165" s="33" t="n"/>
-      <c r="D165" s="33" t="n"/>
-      <c r="E165" s="33" t="n"/>
-      <c r="F165" s="33" t="n"/>
-      <c r="G165" s="33" t="n"/>
-      <c r="H165" s="33" t="n"/>
-      <c r="I165" s="33" t="n"/>
+      <c r="A165" s="21" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B165" s="21" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C165" s="21" t="inlineStr">
+        <is>
+          <t>Acquirer</t>
+        </is>
+      </c>
+      <c r="D165" s="21" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="E165" s="21" t="inlineStr">
+        <is>
+          <t>EV (USD mm)</t>
+        </is>
+      </c>
+      <c r="F165" s="21" t="inlineStr">
+        <is>
+          <t>EV/Revenue</t>
+        </is>
+      </c>
+      <c r="G165" s="21" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="H165" s="21" t="inlineStr">
+        <is>
+          <t>Premium paid</t>
+        </is>
+      </c>
+      <c r="I165" s="21" t="inlineStr">
+        <is>
+          <t>Strategic rationale</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="33" t="n"/>
@@ -15500,146 +15564,130 @@
       <c r="H176" s="33" t="n"/>
       <c r="I176" s="33" t="n"/>
     </row>
+    <row r="177">
+      <c r="A177" s="33" t="n"/>
+      <c r="B177" s="33" t="n"/>
+      <c r="C177" s="33" t="n"/>
+      <c r="D177" s="33" t="n"/>
+      <c r="E177" s="33" t="n"/>
+      <c r="F177" s="33" t="n"/>
+      <c r="G177" s="33" t="n"/>
+      <c r="H177" s="33" t="n"/>
+      <c r="I177" s="33" t="n"/>
+    </row>
     <row r="178">
-      <c r="A178" s="37" t="inlineStr">
+      <c r="A178" s="33" t="n"/>
+      <c r="B178" s="33" t="n"/>
+      <c r="C178" s="33" t="n"/>
+      <c r="D178" s="33" t="n"/>
+      <c r="E178" s="33" t="n"/>
+      <c r="F178" s="33" t="n"/>
+      <c r="G178" s="33" t="n"/>
+      <c r="H178" s="33" t="n"/>
+      <c r="I178" s="33" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="33" t="n"/>
+      <c r="B179" s="33" t="n"/>
+      <c r="C179" s="33" t="n"/>
+      <c r="D179" s="33" t="n"/>
+      <c r="E179" s="33" t="n"/>
+      <c r="F179" s="33" t="n"/>
+      <c r="G179" s="33" t="n"/>
+      <c r="H179" s="33" t="n"/>
+      <c r="I179" s="33" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="33" t="n"/>
+      <c r="B180" s="33" t="n"/>
+      <c r="C180" s="33" t="n"/>
+      <c r="D180" s="33" t="n"/>
+      <c r="E180" s="33" t="n"/>
+      <c r="F180" s="33" t="n"/>
+      <c r="G180" s="33" t="n"/>
+      <c r="H180" s="33" t="n"/>
+      <c r="I180" s="33" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="37" t="inlineStr">
         <is>
           <t>Section I — Revenue segments  (Optional)</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Optional segmented breakdown. Fill rows below + re-upload to override top-level revenue_growth / gross_margin with a segment aggregate. start_year=0 means the segment already exists in Y0; start_year&gt;0 introduces a new revenue line at that projection year.</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="21" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="21" t="inlineStr">
         <is>
           <t>Segment name</t>
         </is>
       </c>
-      <c r="B180" s="21" t="inlineStr">
+      <c r="B184" s="21" t="inlineStr">
         <is>
           <t>Start year</t>
         </is>
       </c>
-      <c r="C180" s="21" t="inlineStr">
+      <c r="C184" s="21" t="inlineStr">
         <is>
           <t>Initial revenue</t>
         </is>
       </c>
-      <c r="D180" s="21" t="inlineStr">
+      <c r="D184" s="21" t="inlineStr">
         <is>
           <t>Growth Y1</t>
         </is>
       </c>
-      <c r="E180" s="21" t="inlineStr">
+      <c r="E184" s="21" t="inlineStr">
         <is>
           <t>Growth Y2</t>
         </is>
       </c>
-      <c r="F180" s="21" t="inlineStr">
+      <c r="F184" s="21" t="inlineStr">
         <is>
           <t>Growth Y3</t>
         </is>
       </c>
-      <c r="G180" s="21" t="inlineStr">
+      <c r="G184" s="21" t="inlineStr">
         <is>
           <t>Growth Y4</t>
         </is>
       </c>
-      <c r="H180" s="21" t="inlineStr">
+      <c r="H184" s="21" t="inlineStr">
         <is>
           <t>Growth Y5</t>
         </is>
       </c>
-      <c r="I180" s="21" t="inlineStr">
+      <c r="I184" s="21" t="inlineStr">
         <is>
           <t>GM Y1</t>
         </is>
       </c>
-      <c r="J180" s="21" t="inlineStr">
+      <c r="J184" s="21" t="inlineStr">
         <is>
           <t>GM Y2</t>
         </is>
       </c>
-      <c r="K180" s="21" t="inlineStr">
+      <c r="K184" s="21" t="inlineStr">
         <is>
           <t>GM Y3</t>
         </is>
       </c>
-      <c r="L180" s="21" t="inlineStr">
+      <c r="L184" s="21" t="inlineStr">
         <is>
           <t>GM Y4</t>
         </is>
       </c>
-      <c r="M180" s="21" t="inlineStr">
+      <c r="M184" s="21" t="inlineStr">
         <is>
           <t>GM Y5</t>
         </is>
       </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="33" t="n"/>
-      <c r="B181" s="33" t="n"/>
-      <c r="C181" s="33" t="n"/>
-      <c r="D181" s="33" t="n"/>
-      <c r="E181" s="33" t="n"/>
-      <c r="F181" s="33" t="n"/>
-      <c r="G181" s="33" t="n"/>
-      <c r="H181" s="33" t="n"/>
-      <c r="I181" s="33" t="n"/>
-      <c r="J181" s="33" t="n"/>
-      <c r="K181" s="33" t="n"/>
-      <c r="L181" s="33" t="n"/>
-      <c r="M181" s="33" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="33" t="n"/>
-      <c r="B182" s="33" t="n"/>
-      <c r="C182" s="33" t="n"/>
-      <c r="D182" s="33" t="n"/>
-      <c r="E182" s="33" t="n"/>
-      <c r="F182" s="33" t="n"/>
-      <c r="G182" s="33" t="n"/>
-      <c r="H182" s="33" t="n"/>
-      <c r="I182" s="33" t="n"/>
-      <c r="J182" s="33" t="n"/>
-      <c r="K182" s="33" t="n"/>
-      <c r="L182" s="33" t="n"/>
-      <c r="M182" s="33" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="33" t="n"/>
-      <c r="B183" s="33" t="n"/>
-      <c r="C183" s="33" t="n"/>
-      <c r="D183" s="33" t="n"/>
-      <c r="E183" s="33" t="n"/>
-      <c r="F183" s="33" t="n"/>
-      <c r="G183" s="33" t="n"/>
-      <c r="H183" s="33" t="n"/>
-      <c r="I183" s="33" t="n"/>
-      <c r="J183" s="33" t="n"/>
-      <c r="K183" s="33" t="n"/>
-      <c r="L183" s="33" t="n"/>
-      <c r="M183" s="33" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="33" t="n"/>
-      <c r="B184" s="33" t="n"/>
-      <c r="C184" s="33" t="n"/>
-      <c r="D184" s="33" t="n"/>
-      <c r="E184" s="33" t="n"/>
-      <c r="F184" s="33" t="n"/>
-      <c r="G184" s="33" t="n"/>
-      <c r="H184" s="33" t="n"/>
-      <c r="I184" s="33" t="n"/>
-      <c r="J184" s="33" t="n"/>
-      <c r="K184" s="33" t="n"/>
-      <c r="L184" s="33" t="n"/>
-      <c r="M184" s="33" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="33" t="n"/>
@@ -15656,30 +15704,90 @@
       <c r="L185" s="33" t="n"/>
       <c r="M185" s="33" t="n"/>
     </row>
+    <row r="186">
+      <c r="A186" s="33" t="n"/>
+      <c r="B186" s="33" t="n"/>
+      <c r="C186" s="33" t="n"/>
+      <c r="D186" s="33" t="n"/>
+      <c r="E186" s="33" t="n"/>
+      <c r="F186" s="33" t="n"/>
+      <c r="G186" s="33" t="n"/>
+      <c r="H186" s="33" t="n"/>
+      <c r="I186" s="33" t="n"/>
+      <c r="J186" s="33" t="n"/>
+      <c r="K186" s="33" t="n"/>
+      <c r="L186" s="33" t="n"/>
+      <c r="M186" s="33" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="33" t="n"/>
+      <c r="B187" s="33" t="n"/>
+      <c r="C187" s="33" t="n"/>
+      <c r="D187" s="33" t="n"/>
+      <c r="E187" s="33" t="n"/>
+      <c r="F187" s="33" t="n"/>
+      <c r="G187" s="33" t="n"/>
+      <c r="H187" s="33" t="n"/>
+      <c r="I187" s="33" t="n"/>
+      <c r="J187" s="33" t="n"/>
+      <c r="K187" s="33" t="n"/>
+      <c r="L187" s="33" t="n"/>
+      <c r="M187" s="33" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="33" t="n"/>
+      <c r="B188" s="33" t="n"/>
+      <c r="C188" s="33" t="n"/>
+      <c r="D188" s="33" t="n"/>
+      <c r="E188" s="33" t="n"/>
+      <c r="F188" s="33" t="n"/>
+      <c r="G188" s="33" t="n"/>
+      <c r="H188" s="33" t="n"/>
+      <c r="I188" s="33" t="n"/>
+      <c r="J188" s="33" t="n"/>
+      <c r="K188" s="33" t="n"/>
+      <c r="L188" s="33" t="n"/>
+      <c r="M188" s="33" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="33" t="n"/>
+      <c r="B189" s="33" t="n"/>
+      <c r="C189" s="33" t="n"/>
+      <c r="D189" s="33" t="n"/>
+      <c r="E189" s="33" t="n"/>
+      <c r="F189" s="33" t="n"/>
+      <c r="G189" s="33" t="n"/>
+      <c r="H189" s="33" t="n"/>
+      <c r="I189" s="33" t="n"/>
+      <c r="J189" s="33" t="n"/>
+      <c r="K189" s="33" t="n"/>
+      <c r="L189" s="33" t="n"/>
+      <c r="M189" s="33" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A178:M178"/>
+    <mergeCell ref="A131:H131"/>
+    <mergeCell ref="A114:H114"/>
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A104:H104"/>
-    <mergeCell ref="A160:H160"/>
-    <mergeCell ref="A119:H119"/>
+    <mergeCell ref="A96:H96"/>
+    <mergeCell ref="A164:H164"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A179:M179"/>
+    <mergeCell ref="A108:H108"/>
+    <mergeCell ref="A123:H123"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A182:M182"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A127:H127"/>
+    <mergeCell ref="A183:M183"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F70 F71 F72 F73 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F105 F106 F107 F108 F111 F112 F113 F114 F115 F116 F117 F120 F121 F122 F123 F124 F125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F74 F75 F76 F77 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F109 F110 F111 F112 F115 F116 F117 F118 F119 F120 F121 F124 F125 F126 F127 F128 F129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Audited FS,Management Projections,Capital IQ,Bloomberg,Damodaran,Kroll,Mercer,Prospectus,Engagement Letter,Calculated,Manual"</formula1>
     </dataValidation>
-    <dataValidation sqref="D105 D107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D109 D111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16616,7 +16724,10 @@
           <t>(currency × unit)</t>
         </is>
       </c>
-      <c r="C12" s="41" t="n"/>
+      <c r="C12" s="41">
+        <f>IFERROR(gross_profit_y0,"")</f>
+        <v/>
+      </c>
       <c r="D12" s="41">
         <f>D8*gross_margin_y1</f>
         <v/>
@@ -16649,6 +16760,10 @@
           <t>%</t>
         </is>
       </c>
+      <c r="C13">
+        <f>IFERROR(gross_profit_y0/revenue_y0,"")</f>
+        <v/>
+      </c>
       <c r="D13" s="42">
         <f>gross_margin_y1</f>
         <v/>
@@ -16681,7 +16796,10 @@
           <t>(currency × unit)</t>
         </is>
       </c>
-      <c r="C14" s="41" t="n"/>
+      <c r="C14" s="41">
+        <f>IFERROR(opex_y0,"")</f>
+        <v/>
+      </c>
       <c r="D14" s="41">
         <f>-D8*opex_pct_revenue_y1</f>
         <v/>
@@ -16714,7 +16832,10 @@
           <t>(currency × unit)</t>
         </is>
       </c>
-      <c r="C15" s="41" t="n"/>
+      <c r="C15" s="41">
+        <f>IFERROR(ebitda_y0,"")</f>
+        <v/>
+      </c>
       <c r="D15" s="41">
         <f>D12+D14</f>
         <v/>
@@ -16746,6 +16867,10 @@
         <is>
           <t>%</t>
         </is>
+      </c>
+      <c r="C16">
+        <f>IFERROR(ebitda_y0/revenue_y0,"")</f>
+        <v/>
       </c>
       <c r="D16" s="42">
         <f>IFERROR(D15/D8,0)</f>
@@ -16812,7 +16937,10 @@
           <t>(currency × unit)</t>
         </is>
       </c>
-      <c r="C18" s="41" t="n"/>
+      <c r="C18" s="41">
+        <f>IFERROR(ebit_y0,"")</f>
+        <v/>
+      </c>
       <c r="D18" s="41">
         <f>D15+D17</f>
         <v/>
@@ -16844,6 +16972,10 @@
         <is>
           <t>%</t>
         </is>
+      </c>
+      <c r="C19">
+        <f>IFERROR(ebit_y0/revenue_y0,"")</f>
+        <v/>
       </c>
       <c r="D19" s="42">
         <f>IFERROR(D18/D8,0)</f>

--- a/materials/templates/orionmano-valuation-template-v1.xlsx
+++ b/materials/templates/orionmano-valuation-template-v1.xlsx
@@ -59,96 +59,98 @@
     <definedName name="opex_y0">'Inputs'!$D$39</definedName>
     <definedName name="ebitda_y0">'Inputs'!$D$40</definedName>
     <definedName name="ebit_y0">'Inputs'!$D$41</definedName>
-    <definedName name="revenue_growth_y1">'Inputs'!$D$42</definedName>
-    <definedName name="revenue_growth_y2">'Inputs'!$D$43</definedName>
-    <definedName name="revenue_growth_y3">'Inputs'!$D$44</definedName>
-    <definedName name="revenue_growth_y4">'Inputs'!$D$45</definedName>
-    <definedName name="revenue_growth_y5">'Inputs'!$D$46</definedName>
-    <definedName name="gross_margin_y1">'Inputs'!$D$47</definedName>
-    <definedName name="gross_margin_y2">'Inputs'!$D$48</definedName>
-    <definedName name="gross_margin_y3">'Inputs'!$D$49</definedName>
-    <definedName name="gross_margin_y4">'Inputs'!$D$50</definedName>
-    <definedName name="gross_margin_y5">'Inputs'!$D$51</definedName>
-    <definedName name="opex_pct_revenue_y1">'Inputs'!$D$52</definedName>
-    <definedName name="opex_pct_revenue_y2">'Inputs'!$D$53</definedName>
-    <definedName name="opex_pct_revenue_y3">'Inputs'!$D$54</definedName>
-    <definedName name="opex_pct_revenue_y4">'Inputs'!$D$55</definedName>
-    <definedName name="opex_pct_revenue_y5">'Inputs'!$D$56</definedName>
-    <definedName name="capex_pct_revenue_y1">'Inputs'!$D$57</definedName>
-    <definedName name="capex_pct_revenue_y2">'Inputs'!$D$58</definedName>
-    <definedName name="capex_pct_revenue_y3">'Inputs'!$D$59</definedName>
-    <definedName name="capex_pct_revenue_y4">'Inputs'!$D$60</definedName>
-    <definedName name="capex_pct_revenue_y5">'Inputs'!$D$61</definedName>
-    <definedName name="dep_pct_revenue_y1">'Inputs'!$D$62</definedName>
-    <definedName name="dep_pct_revenue_y2">'Inputs'!$D$63</definedName>
-    <definedName name="dep_pct_revenue_y3">'Inputs'!$D$64</definedName>
-    <definedName name="dep_pct_revenue_y4">'Inputs'!$D$65</definedName>
-    <definedName name="dep_pct_revenue_y5">'Inputs'!$D$66</definedName>
-    <definedName name="nwc_pct_sales_y1">'Inputs'!$D$67</definedName>
-    <definedName name="nwc_pct_sales_y2">'Inputs'!$D$68</definedName>
-    <definedName name="nwc_pct_sales_y3">'Inputs'!$D$69</definedName>
-    <definedName name="nwc_pct_sales_y4">'Inputs'!$D$70</definedName>
-    <definedName name="nwc_pct_sales_y5">'Inputs'!$D$71</definedName>
-    <definedName name="terminal_method">'Inputs'!$D$74</definedName>
-    <definedName name="terminal_growth_rate">'Inputs'!$D$75</definedName>
-    <definedName name="terminal_exit_multiple_type">'Inputs'!$D$76</definedName>
-    <definedName name="terminal_exit_multiple_value">'Inputs'!$D$77</definedName>
-    <definedName name="risk_free_rate">'Inputs'!$D$80</definedName>
-    <definedName name="risk_free_rate_source">'Inputs'!$D$81</definedName>
-    <definedName name="equity_risk_premium">'Inputs'!$D$82</definedName>
-    <definedName name="country_risk_premium">'Inputs'!$D$83</definedName>
-    <definedName name="unlevered_beta_per_mgmt">'Inputs'!$D$84</definedName>
-    <definedName name="unlevered_beta_indep">'Inputs'!$E$84</definedName>
-    <definedName name="target_debt_to_equity_per_mgmt">'Inputs'!$D$85</definedName>
-    <definedName name="target_debt_to_equity_indep">'Inputs'!$E$85</definedName>
-    <definedName name="levered_beta_per_mgmt">'Inputs'!$D$86</definedName>
-    <definedName name="levered_beta_indep">'Inputs'!$E$86</definedName>
-    <definedName name="size_premium_per_mgmt">'Inputs'!$D$87</definedName>
-    <definedName name="size_premium_indep">'Inputs'!$E$87</definedName>
-    <definedName name="specific_risk_premium_per_mgmt">'Inputs'!$D$88</definedName>
-    <definedName name="specific_risk_premium_indep">'Inputs'!$E$88</definedName>
-    <definedName name="cost_of_equity_per_mgmt">'Inputs'!$D$89</definedName>
-    <definedName name="cost_of_equity_indep">'Inputs'!$E$89</definedName>
-    <definedName name="pretax_cost_of_debt_per_mgmt">'Inputs'!$D$90</definedName>
-    <definedName name="pretax_cost_of_debt_indep">'Inputs'!$E$90</definedName>
-    <definedName name="aftertax_cost_of_debt_per_mgmt">'Inputs'!$D$91</definedName>
-    <definedName name="aftertax_cost_of_debt_indep">'Inputs'!$E$91</definedName>
-    <definedName name="target_debt_weight_per_mgmt">'Inputs'!$D$92</definedName>
-    <definedName name="target_debt_weight_indep">'Inputs'!$E$92</definedName>
-    <definedName name="target_equity_weight_per_mgmt">'Inputs'!$D$93</definedName>
-    <definedName name="target_equity_weight_indep">'Inputs'!$E$93</definedName>
-    <definedName name="wacc_per_mgmt">'Inputs'!$D$94</definedName>
-    <definedName name="wacc_indep">'Inputs'!$E$94</definedName>
-    <definedName name="surplus_assets">'Inputs'!$D$97</definedName>
-    <definedName name="net_debt_override">'Inputs'!$D$98</definedName>
-    <definedName name="minority_interests">'Inputs'!$D$99</definedName>
-    <definedName name="non_operating_assets">'Inputs'!$D$100</definedName>
-    <definedName name="dlom_pct">'Inputs'!$D$101</definedName>
-    <definedName name="dloc_pct">'Inputs'!$D$102</definedName>
-    <definedName name="equity_interest_pct">'Inputs'!$D$103</definedName>
-    <definedName name="shares_outstanding">'Inputs'!$D$104</definedName>
-    <definedName name="shares_outstanding_diluted">'Inputs'!$D$105</definedName>
-    <definedName name="pre_money_pct">'Inputs'!$D$106</definedName>
-    <definedName name="capitalize_rd">'Inputs'!$D$109</definedName>
-    <definedName name="rd_amortization_years">'Inputs'!$D$110</definedName>
-    <definedName name="convert_operating_leases">'Inputs'!$D$111</definedName>
-    <definedName name="lease_discount_rate">'Inputs'!$D$112</definedName>
-    <definedName name="weight_dcf">'Inputs'!$D$115</definedName>
-    <definedName name="weight_comps">'Inputs'!$D$116</definedName>
-    <definedName name="weight_precedent">'Inputs'!$D$117</definedName>
-    <definedName name="weight_nav">'Inputs'!$D$118</definedName>
-    <definedName name="selected_low">'Inputs'!$D$119</definedName>
-    <definedName name="selected_mid">'Inputs'!$D$120</definedName>
-    <definedName name="selected_high">'Inputs'!$D$121</definedName>
-    <definedName name="sens_wacc_step">'Inputs'!$D$124</definedName>
-    <definedName name="sens_wacc_count">'Inputs'!$D$125</definedName>
-    <definedName name="sens_terminal_g_step">'Inputs'!$D$126</definedName>
-    <definedName name="sens_terminal_g_count">'Inputs'!$D$127</definedName>
-    <definedName name="sens_revenue_g_step">'Inputs'!$D$128</definedName>
-    <definedName name="sens_ebitda_margin_step">'Inputs'!$D$129</definedName>
-    <definedName name="cocos_table">'Inputs'!$A$133:$L$162</definedName>
-    <definedName name="precedents_table">'Inputs'!$A$166:$I$180</definedName>
-    <definedName name="segments_table">'Inputs'!$A$185:$M$189</definedName>
+    <definedName name="tax_y0">'Inputs'!$D$42</definedName>
+    <definedName name="net_income_y0">'Inputs'!$D$43</definedName>
+    <definedName name="revenue_growth_y1">'Inputs'!$D$44</definedName>
+    <definedName name="revenue_growth_y2">'Inputs'!$D$45</definedName>
+    <definedName name="revenue_growth_y3">'Inputs'!$D$46</definedName>
+    <definedName name="revenue_growth_y4">'Inputs'!$D$47</definedName>
+    <definedName name="revenue_growth_y5">'Inputs'!$D$48</definedName>
+    <definedName name="gross_margin_y1">'Inputs'!$D$49</definedName>
+    <definedName name="gross_margin_y2">'Inputs'!$D$50</definedName>
+    <definedName name="gross_margin_y3">'Inputs'!$D$51</definedName>
+    <definedName name="gross_margin_y4">'Inputs'!$D$52</definedName>
+    <definedName name="gross_margin_y5">'Inputs'!$D$53</definedName>
+    <definedName name="opex_pct_revenue_y1">'Inputs'!$D$54</definedName>
+    <definedName name="opex_pct_revenue_y2">'Inputs'!$D$55</definedName>
+    <definedName name="opex_pct_revenue_y3">'Inputs'!$D$56</definedName>
+    <definedName name="opex_pct_revenue_y4">'Inputs'!$D$57</definedName>
+    <definedName name="opex_pct_revenue_y5">'Inputs'!$D$58</definedName>
+    <definedName name="capex_pct_revenue_y1">'Inputs'!$D$59</definedName>
+    <definedName name="capex_pct_revenue_y2">'Inputs'!$D$60</definedName>
+    <definedName name="capex_pct_revenue_y3">'Inputs'!$D$61</definedName>
+    <definedName name="capex_pct_revenue_y4">'Inputs'!$D$62</definedName>
+    <definedName name="capex_pct_revenue_y5">'Inputs'!$D$63</definedName>
+    <definedName name="dep_pct_revenue_y1">'Inputs'!$D$64</definedName>
+    <definedName name="dep_pct_revenue_y2">'Inputs'!$D$65</definedName>
+    <definedName name="dep_pct_revenue_y3">'Inputs'!$D$66</definedName>
+    <definedName name="dep_pct_revenue_y4">'Inputs'!$D$67</definedName>
+    <definedName name="dep_pct_revenue_y5">'Inputs'!$D$68</definedName>
+    <definedName name="nwc_pct_sales_y1">'Inputs'!$D$69</definedName>
+    <definedName name="nwc_pct_sales_y2">'Inputs'!$D$70</definedName>
+    <definedName name="nwc_pct_sales_y3">'Inputs'!$D$71</definedName>
+    <definedName name="nwc_pct_sales_y4">'Inputs'!$D$72</definedName>
+    <definedName name="nwc_pct_sales_y5">'Inputs'!$D$73</definedName>
+    <definedName name="terminal_method">'Inputs'!$D$76</definedName>
+    <definedName name="terminal_growth_rate">'Inputs'!$D$77</definedName>
+    <definedName name="terminal_exit_multiple_type">'Inputs'!$D$78</definedName>
+    <definedName name="terminal_exit_multiple_value">'Inputs'!$D$79</definedName>
+    <definedName name="risk_free_rate">'Inputs'!$D$82</definedName>
+    <definedName name="risk_free_rate_source">'Inputs'!$D$83</definedName>
+    <definedName name="equity_risk_premium">'Inputs'!$D$84</definedName>
+    <definedName name="country_risk_premium">'Inputs'!$D$85</definedName>
+    <definedName name="unlevered_beta_per_mgmt">'Inputs'!$D$86</definedName>
+    <definedName name="unlevered_beta_indep">'Inputs'!$E$86</definedName>
+    <definedName name="target_debt_to_equity_per_mgmt">'Inputs'!$D$87</definedName>
+    <definedName name="target_debt_to_equity_indep">'Inputs'!$E$87</definedName>
+    <definedName name="levered_beta_per_mgmt">'Inputs'!$D$88</definedName>
+    <definedName name="levered_beta_indep">'Inputs'!$E$88</definedName>
+    <definedName name="size_premium_per_mgmt">'Inputs'!$D$89</definedName>
+    <definedName name="size_premium_indep">'Inputs'!$E$89</definedName>
+    <definedName name="specific_risk_premium_per_mgmt">'Inputs'!$D$90</definedName>
+    <definedName name="specific_risk_premium_indep">'Inputs'!$E$90</definedName>
+    <definedName name="cost_of_equity_per_mgmt">'Inputs'!$D$91</definedName>
+    <definedName name="cost_of_equity_indep">'Inputs'!$E$91</definedName>
+    <definedName name="pretax_cost_of_debt_per_mgmt">'Inputs'!$D$92</definedName>
+    <definedName name="pretax_cost_of_debt_indep">'Inputs'!$E$92</definedName>
+    <definedName name="aftertax_cost_of_debt_per_mgmt">'Inputs'!$D$93</definedName>
+    <definedName name="aftertax_cost_of_debt_indep">'Inputs'!$E$93</definedName>
+    <definedName name="target_debt_weight_per_mgmt">'Inputs'!$D$94</definedName>
+    <definedName name="target_debt_weight_indep">'Inputs'!$E$94</definedName>
+    <definedName name="target_equity_weight_per_mgmt">'Inputs'!$D$95</definedName>
+    <definedName name="target_equity_weight_indep">'Inputs'!$E$95</definedName>
+    <definedName name="wacc_per_mgmt">'Inputs'!$D$96</definedName>
+    <definedName name="wacc_indep">'Inputs'!$E$96</definedName>
+    <definedName name="surplus_assets">'Inputs'!$D$99</definedName>
+    <definedName name="net_debt_override">'Inputs'!$D$100</definedName>
+    <definedName name="minority_interests">'Inputs'!$D$101</definedName>
+    <definedName name="non_operating_assets">'Inputs'!$D$102</definedName>
+    <definedName name="dlom_pct">'Inputs'!$D$103</definedName>
+    <definedName name="dloc_pct">'Inputs'!$D$104</definedName>
+    <definedName name="equity_interest_pct">'Inputs'!$D$105</definedName>
+    <definedName name="shares_outstanding">'Inputs'!$D$106</definedName>
+    <definedName name="shares_outstanding_diluted">'Inputs'!$D$107</definedName>
+    <definedName name="pre_money_pct">'Inputs'!$D$108</definedName>
+    <definedName name="capitalize_rd">'Inputs'!$D$111</definedName>
+    <definedName name="rd_amortization_years">'Inputs'!$D$112</definedName>
+    <definedName name="convert_operating_leases">'Inputs'!$D$113</definedName>
+    <definedName name="lease_discount_rate">'Inputs'!$D$114</definedName>
+    <definedName name="weight_dcf">'Inputs'!$D$117</definedName>
+    <definedName name="weight_comps">'Inputs'!$D$118</definedName>
+    <definedName name="weight_precedent">'Inputs'!$D$119</definedName>
+    <definedName name="weight_nav">'Inputs'!$D$120</definedName>
+    <definedName name="selected_low">'Inputs'!$D$121</definedName>
+    <definedName name="selected_mid">'Inputs'!$D$122</definedName>
+    <definedName name="selected_high">'Inputs'!$D$123</definedName>
+    <definedName name="sens_wacc_step">'Inputs'!$D$126</definedName>
+    <definedName name="sens_wacc_count">'Inputs'!$D$127</definedName>
+    <definedName name="sens_terminal_g_step">'Inputs'!$D$128</definedName>
+    <definedName name="sens_terminal_g_count">'Inputs'!$D$129</definedName>
+    <definedName name="sens_revenue_g_step">'Inputs'!$D$130</definedName>
+    <definedName name="sens_ebitda_margin_step">'Inputs'!$D$131</definedName>
+    <definedName name="cocos_table">'Inputs'!$A$135:$L$164</definedName>
+    <definedName name="precedents_table">'Inputs'!$A$168:$I$182</definedName>
+    <definedName name="segments_table">'Inputs'!$A$187:$M$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12391,7 +12393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13161,56 +13163,64 @@
     <row r="42">
       <c r="A42" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y1</t>
+          <t>tax_y0</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y1)</t>
+          <t>Tax (Y0)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D42" s="32" t="n"/>
       <c r="E42" s="32" t="n"/>
       <c r="F42" s="33" t="n"/>
       <c r="G42" s="33" t="n"/>
-      <c r="H42" s="33" t="n"/>
+      <c r="H42" s="34" t="inlineStr">
+        <is>
+          <t>Audited Y0 tax expense (negative); populates Projections!C22</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y2</t>
+          <t>net_income_y0</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y2)</t>
+          <t>Net income (Y0)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D43" s="32" t="n"/>
       <c r="E43" s="32" t="n"/>
       <c r="F43" s="33" t="n"/>
       <c r="G43" s="33" t="n"/>
-      <c r="H43" s="33" t="n"/>
+      <c r="H43" s="34" t="inlineStr">
+        <is>
+          <t>Audited Y0 net income; populates Projections!C23</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y3</t>
+          <t>revenue_growth_y1</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y3)</t>
+          <t>Revenue growth (Y1)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -13227,12 +13237,12 @@
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y4</t>
+          <t>revenue_growth_y2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y4)</t>
+          <t>Revenue growth (Y2)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -13249,12 +13259,12 @@
     <row r="46">
       <c r="A46" s="31" t="inlineStr">
         <is>
-          <t>revenue_growth_y5</t>
+          <t>revenue_growth_y3</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth (Y5)</t>
+          <t>Revenue growth (Y3)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -13271,12 +13281,12 @@
     <row r="47">
       <c r="A47" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y1</t>
+          <t>revenue_growth_y4</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y1)</t>
+          <t>Revenue growth (Y4)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -13293,12 +13303,12 @@
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y2</t>
+          <t>revenue_growth_y5</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y2)</t>
+          <t>Revenue growth (Y5)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13315,12 +13325,12 @@
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y3</t>
+          <t>gross_margin_y1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y3)</t>
+          <t>Gross margin (Y1)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -13337,12 +13347,12 @@
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y4</t>
+          <t>gross_margin_y2</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y4)</t>
+          <t>Gross margin (Y2)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -13359,12 +13369,12 @@
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
         <is>
-          <t>gross_margin_y5</t>
+          <t>gross_margin_y3</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Gross margin (Y5)</t>
+          <t>Gross margin (Y3)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -13381,12 +13391,12 @@
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y1</t>
+          <t>gross_margin_y4</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y1)</t>
+          <t>Gross margin (Y4)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -13403,12 +13413,12 @@
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y2</t>
+          <t>gross_margin_y5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y2)</t>
+          <t>Gross margin (Y5)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -13425,12 +13435,12 @@
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y3</t>
+          <t>opex_pct_revenue_y1</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y3)</t>
+          <t>Opex % of revenue (Y1)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13447,12 +13457,12 @@
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y4</t>
+          <t>opex_pct_revenue_y2</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y4)</t>
+          <t>Opex % of revenue (Y2)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13469,12 +13479,12 @@
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
         <is>
-          <t>opex_pct_revenue_y5</t>
+          <t>opex_pct_revenue_y3</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Opex % of revenue (Y5)</t>
+          <t>Opex % of revenue (Y3)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13491,12 +13501,12 @@
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y1</t>
+          <t>opex_pct_revenue_y4</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y1)</t>
+          <t>Opex % of revenue (Y4)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13513,12 +13523,12 @@
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y2</t>
+          <t>opex_pct_revenue_y5</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y2)</t>
+          <t>Opex % of revenue (Y5)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13535,12 +13545,12 @@
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y3</t>
+          <t>capex_pct_revenue_y1</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y3)</t>
+          <t>Capex % of revenue (Y1)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13557,12 +13567,12 @@
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y4</t>
+          <t>capex_pct_revenue_y2</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y4)</t>
+          <t>Capex % of revenue (Y2)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -13579,12 +13589,12 @@
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t>capex_pct_revenue_y5</t>
+          <t>capex_pct_revenue_y3</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Capex % of revenue (Y5)</t>
+          <t>Capex % of revenue (Y3)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -13601,12 +13611,12 @@
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y1</t>
+          <t>capex_pct_revenue_y4</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y1)</t>
+          <t>Capex % of revenue (Y4)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -13623,12 +13633,12 @@
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y2</t>
+          <t>capex_pct_revenue_y5</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y2)</t>
+          <t>Capex % of revenue (Y5)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -13645,12 +13655,12 @@
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y3</t>
+          <t>dep_pct_revenue_y1</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y3)</t>
+          <t>Depreciation % of revenue (Y1)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13667,12 +13677,12 @@
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y4</t>
+          <t>dep_pct_revenue_y2</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y4)</t>
+          <t>Depreciation % of revenue (Y2)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13689,12 +13699,12 @@
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>dep_pct_revenue_y5</t>
+          <t>dep_pct_revenue_y3</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Depreciation % of revenue (Y5)</t>
+          <t>Depreciation % of revenue (Y3)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -13711,12 +13721,12 @@
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y1</t>
+          <t>dep_pct_revenue_y4</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y1)</t>
+          <t>Depreciation % of revenue (Y4)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -13733,12 +13743,12 @@
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y2</t>
+          <t>dep_pct_revenue_y5</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y2)</t>
+          <t>Depreciation % of revenue (Y5)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -13755,12 +13765,12 @@
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y3</t>
+          <t>nwc_pct_sales_y1</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y3)</t>
+          <t>Working capital % of sales (Y1)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -13777,12 +13787,12 @@
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y4</t>
+          <t>nwc_pct_sales_y2</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y4)</t>
+          <t>Working capital % of sales (Y2)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -13799,12 +13809,12 @@
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>nwc_pct_sales_y5</t>
+          <t>nwc_pct_sales_y3</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Working capital % of sales (Y5)</t>
+          <t>Working capital % of sales (Y3)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -13818,70 +13828,66 @@
       <c r="G71" s="33" t="n"/>
       <c r="H71" s="33" t="n"/>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>nwc_pct_sales_y4</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Working capital % of sales (Y4)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="n"/>
+      <c r="E72" s="32" t="n"/>
+      <c r="F72" s="33" t="n"/>
+      <c r="G72" s="33" t="n"/>
+      <c r="H72" s="33" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>nwc_pct_sales_y5</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Working capital % of sales (Y5)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="n"/>
+      <c r="E73" s="32" t="n"/>
+      <c r="F73" s="33" t="n"/>
+      <c r="G73" s="33" t="n"/>
+      <c r="H73" s="33" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Section E — Terminal value  (Core)</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>terminal_method</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Terminal value method</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="n"/>
-      <c r="E74" s="32" t="n"/>
-      <c r="F74" s="33" t="n"/>
-      <c r="G74" s="33" t="n"/>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>gordon_growth | exit_multiple</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>terminal_growth_rate</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Terminal growth rate</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D75" s="32" t="n"/>
-      <c r="E75" s="32" t="n"/>
-      <c r="F75" s="33" t="n"/>
-      <c r="G75" s="33" t="n"/>
-      <c r="H75" s="33" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>terminal_exit_multiple_type</t>
+          <t>terminal_method</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Exit multiple metric</t>
+          <t>Terminal value method</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -13893,22 +13899,26 @@
       <c r="E76" s="32" t="n"/>
       <c r="F76" s="33" t="n"/>
       <c r="G76" s="33" t="n"/>
-      <c r="H76" s="33" t="n"/>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>gordon_growth | exit_multiple</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>terminal_exit_multiple_value</t>
+          <t>terminal_growth_rate</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Exit multiple value</t>
+          <t>Terminal growth rate</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D77" s="32" t="n"/>
@@ -13917,66 +13927,66 @@
       <c r="G77" s="33" t="n"/>
       <c r="H77" s="33" t="n"/>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>terminal_exit_multiple_type</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Exit multiple metric</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="n"/>
+      <c r="E78" s="32" t="n"/>
+      <c r="F78" s="33" t="n"/>
+      <c r="G78" s="33" t="n"/>
+      <c r="H78" s="33" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>terminal_exit_multiple_value</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Exit multiple value</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="n"/>
+      <c r="E79" s="32" t="n"/>
+      <c r="F79" s="33" t="n"/>
+      <c r="G79" s="33" t="n"/>
+      <c r="H79" s="33" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Section F — WACC inputs  (Core)</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>risk_free_rate</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="n"/>
-      <c r="E80" s="32" t="n"/>
-      <c r="F80" s="33" t="n"/>
-      <c r="G80" s="33" t="n"/>
-      <c r="H80" s="33" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>risk_free_rate_source</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Risk-free rate source descriptor</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="n"/>
-      <c r="E81" s="32" t="n"/>
-      <c r="F81" s="33" t="n"/>
-      <c r="G81" s="33" t="n"/>
-      <c r="H81" s="33" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>equity_risk_premium</t>
+          <t>risk_free_rate</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Equity risk premium (ERP)</t>
+          <t>Risk-free rate</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -13993,17 +14003,17 @@
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
         <is>
-          <t>country_risk_premium</t>
+          <t>risk_free_rate_source</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Country risk premium</t>
+          <t>Risk-free rate source descriptor</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D83" s="32" t="n"/>
@@ -14015,17 +14025,17 @@
     <row r="84">
       <c r="A84" s="31" t="inlineStr">
         <is>
-          <t>unlevered_beta</t>
+          <t>equity_risk_premium</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Unlevered beta</t>
+          <t>Equity risk premium (ERP)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D84" s="32" t="n"/>
@@ -14037,12 +14047,12 @@
     <row r="85">
       <c r="A85" s="31" t="inlineStr">
         <is>
-          <t>target_debt_to_equity</t>
+          <t>country_risk_premium</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Target D/E ratio</t>
+          <t>Country risk premium</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -14059,12 +14069,12 @@
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>levered_beta</t>
+          <t>unlevered_beta</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Levered beta (calculated)</t>
+          <t>Unlevered beta</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -14072,14 +14082,8 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D86" s="35">
-        <f>WACC!E10</f>
-        <v/>
-      </c>
-      <c r="E86" s="35">
-        <f>WACC!F10</f>
-        <v/>
-      </c>
+      <c r="D86" s="32" t="n"/>
+      <c r="E86" s="32" t="n"/>
       <c r="F86" s="33" t="n"/>
       <c r="G86" s="33" t="n"/>
       <c r="H86" s="33" t="n"/>
@@ -14087,12 +14091,12 @@
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
         <is>
-          <t>size_premium</t>
+          <t>target_debt_to_equity</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Size premium</t>
+          <t>Target D/E ratio</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -14109,21 +14113,27 @@
     <row r="88">
       <c r="A88" s="31" t="inlineStr">
         <is>
-          <t>specific_risk_premium</t>
+          <t>levered_beta</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Specific risk premium</t>
+          <t>Levered beta (calculated)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D88" s="32" t="n"/>
-      <c r="E88" s="32" t="n"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D88" s="35">
+        <f>WACC!E10</f>
+        <v/>
+      </c>
+      <c r="E88" s="35">
+        <f>WACC!F10</f>
+        <v/>
+      </c>
       <c r="F88" s="33" t="n"/>
       <c r="G88" s="33" t="n"/>
       <c r="H88" s="33" t="n"/>
@@ -14131,12 +14141,12 @@
     <row r="89">
       <c r="A89" s="31" t="inlineStr">
         <is>
-          <t>cost_of_equity</t>
+          <t>size_premium</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity (calculated)</t>
+          <t>Size premium</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -14144,14 +14154,8 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D89" s="36">
-        <f>WACC!E16</f>
-        <v/>
-      </c>
-      <c r="E89" s="36">
-        <f>WACC!F16</f>
-        <v/>
-      </c>
+      <c r="D89" s="32" t="n"/>
+      <c r="E89" s="32" t="n"/>
       <c r="F89" s="33" t="n"/>
       <c r="G89" s="33" t="n"/>
       <c r="H89" s="33" t="n"/>
@@ -14159,12 +14163,12 @@
     <row r="90">
       <c r="A90" s="31" t="inlineStr">
         <is>
-          <t>pretax_cost_of_debt</t>
+          <t>specific_risk_premium</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt</t>
+          <t>Specific risk premium</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -14181,12 +14185,12 @@
     <row r="91">
       <c r="A91" s="31" t="inlineStr">
         <is>
-          <t>aftertax_cost_of_debt</t>
+          <t>cost_of_equity</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>After-tax cost of debt (calculated)</t>
+          <t>Cost of equity (calculated)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -14195,11 +14199,11 @@
         </is>
       </c>
       <c r="D91" s="36">
-        <f>WACC!E20</f>
+        <f>WACC!E16</f>
         <v/>
       </c>
       <c r="E91" s="36">
-        <f>WACC!F20</f>
+        <f>WACC!F16</f>
         <v/>
       </c>
       <c r="F91" s="33" t="n"/>
@@ -14209,12 +14213,12 @@
     <row r="92">
       <c r="A92" s="31" t="inlineStr">
         <is>
-          <t>target_debt_weight</t>
+          <t>pretax_cost_of_debt</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>D/V (debt weight)</t>
+          <t>Pre-tax cost of debt</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -14231,12 +14235,12 @@
     <row r="93">
       <c r="A93" s="31" t="inlineStr">
         <is>
-          <t>target_equity_weight</t>
+          <t>aftertax_cost_of_debt</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>E/V (equity weight)</t>
+          <t>After-tax cost of debt (calculated)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -14244,8 +14248,14 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D93" s="32" t="n"/>
-      <c r="E93" s="32" t="n"/>
+      <c r="D93" s="36">
+        <f>WACC!E20</f>
+        <v/>
+      </c>
+      <c r="E93" s="36">
+        <f>WACC!F20</f>
+        <v/>
+      </c>
       <c r="F93" s="33" t="n"/>
       <c r="G93" s="33" t="n"/>
       <c r="H93" s="33" t="n"/>
@@ -14253,12 +14263,12 @@
     <row r="94">
       <c r="A94" s="31" t="inlineStr">
         <is>
-          <t>wacc</t>
+          <t>target_debt_weight</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>WACC (calculated)</t>
+          <t>D/V (debt weight)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -14266,78 +14276,78 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D94" s="36">
-        <f>WACC!E25</f>
-        <v/>
-      </c>
-      <c r="E94" s="36">
-        <f>WACC!F25</f>
-        <v/>
-      </c>
+      <c r="D94" s="32" t="n"/>
+      <c r="E94" s="32" t="n"/>
       <c r="F94" s="33" t="n"/>
       <c r="G94" s="33" t="n"/>
       <c r="H94" s="33" t="n"/>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>target_equity_weight</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>E/V (equity weight)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D95" s="32" t="n"/>
+      <c r="E95" s="32" t="n"/>
+      <c r="F95" s="33" t="n"/>
+      <c r="G95" s="33" t="n"/>
+      <c r="H95" s="33" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="31" t="inlineStr">
+        <is>
+          <t>wacc</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>WACC (calculated)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D96" s="36">
+        <f>WACC!E25</f>
+        <v/>
+      </c>
+      <c r="E96" s="36">
+        <f>WACC!F25</f>
+        <v/>
+      </c>
+      <c r="F96" s="33" t="n"/>
+      <c r="G96" s="33" t="n"/>
+      <c r="H96" s="33" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Section I — EV -&gt; Equity bridge  (Core)</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="31" t="inlineStr">
-        <is>
-          <t>surplus_assets</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Surplus / non-operating assets</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D97" s="32" t="n"/>
-      <c r="E97" s="32" t="n"/>
-      <c r="F97" s="33" t="n"/>
-      <c r="G97" s="33" t="n"/>
-      <c r="H97" s="33" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="31" t="inlineStr">
-        <is>
-          <t>net_debt_override</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Net debt (override)</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D98" s="32" t="n"/>
-      <c r="E98" s="32" t="n"/>
-      <c r="F98" s="33" t="n"/>
-      <c r="G98" s="33" t="n"/>
-      <c r="H98" s="33" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="31" t="inlineStr">
         <is>
-          <t>minority_interests</t>
+          <t>surplus_assets</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Minority interests</t>
+          <t>Surplus / non-operating assets</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14354,12 +14364,12 @@
     <row r="100">
       <c r="A100" s="31" t="inlineStr">
         <is>
-          <t>non_operating_assets</t>
+          <t>net_debt_override</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Non-operating assets</t>
+          <t>Net debt (override)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -14376,17 +14386,17 @@
     <row r="101">
       <c r="A101" s="31" t="inlineStr">
         <is>
-          <t>dlom_pct</t>
+          <t>minority_interests</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>DLOM rate</t>
+          <t>Minority interests</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D101" s="32" t="n"/>
@@ -14398,17 +14408,17 @@
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>dloc_pct</t>
+          <t>non_operating_assets</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>DLOC rate</t>
+          <t>Non-operating assets</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D102" s="32" t="n"/>
@@ -14420,12 +14430,12 @@
     <row r="103">
       <c r="A103" s="31" t="inlineStr">
         <is>
-          <t>equity_interest_pct</t>
+          <t>dlom_pct</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Client's % equity interest</t>
+          <t>DLOM rate</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -14442,17 +14452,17 @@
     <row r="104">
       <c r="A104" s="31" t="inlineStr">
         <is>
-          <t>shares_outstanding</t>
+          <t>dloc_pct</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Shares outstanding (basic)</t>
+          <t>DLOC rate</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D104" s="32" t="n"/>
@@ -14464,17 +14474,17 @@
     <row r="105">
       <c r="A105" s="31" t="inlineStr">
         <is>
-          <t>shares_outstanding_diluted</t>
+          <t>equity_interest_pct</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Shares outstanding (diluted)</t>
+          <t>Client's % equity interest</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D105" s="32" t="n"/>
@@ -14486,17 +14496,17 @@
     <row r="106">
       <c r="A106" s="31" t="inlineStr">
         <is>
-          <t>pre_money_pct</t>
+          <t>shares_outstanding</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Pre-money equity %</t>
+          <t>Shares outstanding (basic)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D106" s="32" t="n"/>
@@ -14505,66 +14515,66 @@
       <c r="G106" s="33" t="n"/>
       <c r="H106" s="33" t="n"/>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="37" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="31" t="inlineStr">
+        <is>
+          <t>shares_outstanding_diluted</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Shares outstanding (diluted)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="n"/>
+      <c r="E107" s="32" t="n"/>
+      <c r="F107" s="33" t="n"/>
+      <c r="G107" s="33" t="n"/>
+      <c r="H107" s="33" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="31" t="inlineStr">
+        <is>
+          <t>pre_money_pct</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Pre-money equity %</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D108" s="32" t="n"/>
+      <c r="E108" s="32" t="n"/>
+      <c r="F108" s="33" t="n"/>
+      <c r="G108" s="33" t="n"/>
+      <c r="H108" s="33" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="37" t="inlineStr">
         <is>
           <t>Section J — Adjustment toggles  (Extended)</t>
         </is>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="31" t="inlineStr">
-        <is>
-          <t>capitalize_rd</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Capitalize R&amp;D?</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D109" s="32" t="n"/>
-      <c r="E109" s="32" t="n"/>
-      <c r="F109" s="33" t="n"/>
-      <c r="G109" s="33" t="n"/>
-      <c r="H109" s="33" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="31" t="inlineStr">
-        <is>
-          <t>rd_amortization_years</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>R&amp;D amortization period (years)</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D110" s="32" t="n"/>
-      <c r="E110" s="32" t="n"/>
-      <c r="F110" s="33" t="n"/>
-      <c r="G110" s="33" t="n"/>
-      <c r="H110" s="33" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="31" t="inlineStr">
         <is>
-          <t>convert_operating_leases</t>
+          <t>capitalize_rd</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Convert operating leases to debt?</t>
+          <t>Capitalize R&amp;D?</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -14581,17 +14591,17 @@
     <row r="112">
       <c r="A112" s="31" t="inlineStr">
         <is>
-          <t>lease_discount_rate</t>
+          <t>rd_amortization_years</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Lease discount rate</t>
+          <t>R&amp;D amortization period (years)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D112" s="32" t="n"/>
@@ -14600,66 +14610,66 @@
       <c r="G112" s="33" t="n"/>
       <c r="H112" s="33" t="n"/>
     </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="37" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="31" t="inlineStr">
+        <is>
+          <t>convert_operating_leases</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Convert operating leases to debt?</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D113" s="32" t="n"/>
+      <c r="E113" s="32" t="n"/>
+      <c r="F113" s="33" t="n"/>
+      <c r="G113" s="33" t="n"/>
+      <c r="H113" s="33" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="31" t="inlineStr">
+        <is>
+          <t>lease_discount_rate</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Lease discount rate</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D114" s="32" t="n"/>
+      <c r="E114" s="32" t="n"/>
+      <c r="F114" s="33" t="n"/>
+      <c r="G114" s="33" t="n"/>
+      <c r="H114" s="33" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="37" t="inlineStr">
         <is>
           <t>Section K — Football field weights  (Extended)</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="31" t="inlineStr">
-        <is>
-          <t>weight_dcf</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>DCF weight</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D115" s="32" t="n"/>
-      <c r="E115" s="32" t="n"/>
-      <c r="F115" s="33" t="n"/>
-      <c r="G115" s="33" t="n"/>
-      <c r="H115" s="33" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="31" t="inlineStr">
-        <is>
-          <t>weight_comps</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Comparable companies weight</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D116" s="32" t="n"/>
-      <c r="E116" s="32" t="n"/>
-      <c r="F116" s="33" t="n"/>
-      <c r="G116" s="33" t="n"/>
-      <c r="H116" s="33" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="31" t="inlineStr">
         <is>
-          <t>weight_precedent</t>
+          <t>weight_dcf</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Precedent transactions weight</t>
+          <t>DCF weight</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -14676,12 +14686,12 @@
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
         <is>
-          <t>weight_nav</t>
+          <t>weight_comps</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>NAV / asset-based weight</t>
+          <t>Comparable companies weight</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -14698,17 +14708,17 @@
     <row r="119">
       <c r="A119" s="31" t="inlineStr">
         <is>
-          <t>selected_low</t>
+          <t>weight_precedent</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation low</t>
+          <t>Precedent transactions weight</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D119" s="32" t="n"/>
@@ -14720,17 +14730,17 @@
     <row r="120">
       <c r="A120" s="31" t="inlineStr">
         <is>
-          <t>selected_mid</t>
+          <t>weight_nav</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation mid</t>
+          <t>NAV / asset-based weight</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D120" s="32" t="n"/>
@@ -14742,12 +14752,12 @@
     <row r="121">
       <c r="A121" s="31" t="inlineStr">
         <is>
-          <t>selected_high</t>
+          <t>selected_low</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation high</t>
+          <t>Selected valuation low</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -14761,66 +14771,66 @@
       <c r="G121" s="33" t="n"/>
       <c r="H121" s="33" t="n"/>
     </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="37" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="31" t="inlineStr">
+        <is>
+          <t>selected_mid</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Selected valuation mid</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D122" s="32" t="n"/>
+      <c r="E122" s="32" t="n"/>
+      <c r="F122" s="33" t="n"/>
+      <c r="G122" s="33" t="n"/>
+      <c r="H122" s="33" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="31" t="inlineStr">
+        <is>
+          <t>selected_high</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Selected valuation high</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D123" s="32" t="n"/>
+      <c r="E123" s="32" t="n"/>
+      <c r="F123" s="33" t="n"/>
+      <c r="G123" s="33" t="n"/>
+      <c r="H123" s="33" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="37" t="inlineStr">
         <is>
           <t>Section L — Sensitivity ranges  (Extended)</t>
         </is>
       </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="31" t="inlineStr">
-        <is>
-          <t>sens_wacc_step</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>WACC sensitivity step</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D124" s="32" t="n"/>
-      <c r="E124" s="32" t="n"/>
-      <c r="F124" s="33" t="n"/>
-      <c r="G124" s="33" t="n"/>
-      <c r="H124" s="33" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="31" t="inlineStr">
-        <is>
-          <t>sens_wacc_count</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>WACC steps each side of base</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D125" s="32" t="n"/>
-      <c r="E125" s="32" t="n"/>
-      <c r="F125" s="33" t="n"/>
-      <c r="G125" s="33" t="n"/>
-      <c r="H125" s="33" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="31" t="inlineStr">
         <is>
-          <t>sens_terminal_g_step</t>
+          <t>sens_wacc_step</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Terminal g sensitivity step</t>
+          <t>WACC sensitivity step</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14837,12 +14847,12 @@
     <row r="127">
       <c r="A127" s="31" t="inlineStr">
         <is>
-          <t>sens_terminal_g_count</t>
+          <t>sens_wacc_count</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Terminal g steps each side</t>
+          <t>WACC steps each side of base</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14859,12 +14869,12 @@
     <row r="128">
       <c r="A128" s="31" t="inlineStr">
         <is>
-          <t>sens_revenue_g_step</t>
+          <t>sens_terminal_g_step</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth sens step</t>
+          <t>Terminal g sensitivity step</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -14881,17 +14891,17 @@
     <row r="129">
       <c r="A129" s="31" t="inlineStr">
         <is>
-          <t>sens_ebitda_margin_step</t>
+          <t>sens_terminal_g_count</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>EBITDA margin sens step</t>
+          <t>Terminal g steps each side</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D129" s="32" t="n"/>
@@ -14900,102 +14910,118 @@
       <c r="G129" s="33" t="n"/>
       <c r="H129" s="33" t="n"/>
     </row>
+    <row r="130">
+      <c r="A130" s="31" t="inlineStr">
+        <is>
+          <t>sens_revenue_g_step</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Revenue growth sens step</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D130" s="32" t="n"/>
+      <c r="E130" s="32" t="n"/>
+      <c r="F130" s="33" t="n"/>
+      <c r="G130" s="33" t="n"/>
+      <c r="H130" s="33" t="n"/>
+    </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="A131" s="31" t="inlineStr">
+        <is>
+          <t>sens_ebitda_margin_step</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA margin sens step</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D131" s="32" t="n"/>
+      <c r="E131" s="32" t="n"/>
+      <c r="F131" s="33" t="n"/>
+      <c r="G131" s="33" t="n"/>
+      <c r="H131" s="33" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>Section G — Comparable companies table  (Core)</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="21" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="21" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B132" s="21" t="inlineStr">
+      <c r="B134" s="21" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="C132" s="21" t="inlineStr">
+      <c r="C134" s="21" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D132" s="21" t="inlineStr">
+      <c r="D134" s="21" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="E132" s="21" t="inlineStr">
+      <c r="E134" s="21" t="inlineStr">
         <is>
           <t>Business description</t>
         </is>
       </c>
-      <c r="F132" s="21" t="inlineStr">
+      <c r="F134" s="21" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="G132" s="21" t="inlineStr">
+      <c r="G134" s="21" t="inlineStr">
         <is>
           <t>Accounting standard</t>
         </is>
       </c>
-      <c r="H132" s="21" t="inlineStr">
+      <c r="H134" s="21" t="inlineStr">
         <is>
           <t>Market cap (USD mm)</t>
         </is>
       </c>
-      <c r="I132" s="21" t="inlineStr">
+      <c r="I134" s="21" t="inlineStr">
         <is>
           <t>D/E ratio</t>
         </is>
       </c>
-      <c r="J132" s="21" t="inlineStr">
+      <c r="J134" s="21" t="inlineStr">
         <is>
           <t>Raw levered beta</t>
         </is>
       </c>
-      <c r="K132" s="21" t="inlineStr">
+      <c r="K134" s="21" t="inlineStr">
         <is>
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="L132" s="21" t="inlineStr">
+      <c r="L134" s="21" t="inlineStr">
         <is>
           <t>Unlevered beta (calculated)</t>
         </is>
       </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="33" t="n"/>
-      <c r="B133" s="33" t="n"/>
-      <c r="C133" s="33" t="n"/>
-      <c r="D133" s="33" t="n"/>
-      <c r="E133" s="33" t="n"/>
-      <c r="F133" s="33" t="n"/>
-      <c r="G133" s="33" t="n"/>
-      <c r="H133" s="33" t="n"/>
-      <c r="I133" s="33" t="n"/>
-      <c r="J133" s="33" t="n"/>
-      <c r="K133" s="33" t="n"/>
-      <c r="L133" s="33" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="33" t="n"/>
-      <c r="B134" s="33" t="n"/>
-      <c r="C134" s="33" t="n"/>
-      <c r="D134" s="33" t="n"/>
-      <c r="E134" s="33" t="n"/>
-      <c r="F134" s="33" t="n"/>
-      <c r="G134" s="33" t="n"/>
-      <c r="H134" s="33" t="n"/>
-      <c r="I134" s="33" t="n"/>
-      <c r="J134" s="33" t="n"/>
-      <c r="K134" s="33" t="n"/>
-      <c r="L134" s="33" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="33" t="n"/>
@@ -15389,81 +15415,87 @@
       <c r="K162" s="33" t="n"/>
       <c r="L162" s="33" t="n"/>
     </row>
+    <row r="163">
+      <c r="A163" s="33" t="n"/>
+      <c r="B163" s="33" t="n"/>
+      <c r="C163" s="33" t="n"/>
+      <c r="D163" s="33" t="n"/>
+      <c r="E163" s="33" t="n"/>
+      <c r="F163" s="33" t="n"/>
+      <c r="G163" s="33" t="n"/>
+      <c r="H163" s="33" t="n"/>
+      <c r="I163" s="33" t="n"/>
+      <c r="J163" s="33" t="n"/>
+      <c r="K163" s="33" t="n"/>
+      <c r="L163" s="33" t="n"/>
+    </row>
     <row r="164">
-      <c r="A164" s="37" t="inlineStr">
+      <c r="A164" s="33" t="n"/>
+      <c r="B164" s="33" t="n"/>
+      <c r="C164" s="33" t="n"/>
+      <c r="D164" s="33" t="n"/>
+      <c r="E164" s="33" t="n"/>
+      <c r="F164" s="33" t="n"/>
+      <c r="G164" s="33" t="n"/>
+      <c r="H164" s="33" t="n"/>
+      <c r="I164" s="33" t="n"/>
+      <c r="J164" s="33" t="n"/>
+      <c r="K164" s="33" t="n"/>
+      <c r="L164" s="33" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="37" t="inlineStr">
         <is>
           <t>Section H — Precedent transactions  (Extended)</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="21" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="21" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B165" s="21" t="inlineStr">
+      <c r="B167" s="21" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C165" s="21" t="inlineStr">
+      <c r="C167" s="21" t="inlineStr">
         <is>
           <t>Acquirer</t>
         </is>
       </c>
-      <c r="D165" s="21" t="inlineStr">
+      <c r="D167" s="21" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="E165" s="21" t="inlineStr">
+      <c r="E167" s="21" t="inlineStr">
         <is>
           <t>EV (USD mm)</t>
         </is>
       </c>
-      <c r="F165" s="21" t="inlineStr">
+      <c r="F167" s="21" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
-      <c r="G165" s="21" t="inlineStr">
+      <c r="G167" s="21" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="H165" s="21" t="inlineStr">
+      <c r="H167" s="21" t="inlineStr">
         <is>
           <t>Premium paid</t>
         </is>
       </c>
-      <c r="I165" s="21" t="inlineStr">
+      <c r="I167" s="21" t="inlineStr">
         <is>
           <t>Strategic rationale</t>
         </is>
       </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="33" t="n"/>
-      <c r="B166" s="33" t="n"/>
-      <c r="C166" s="33" t="n"/>
-      <c r="D166" s="33" t="n"/>
-      <c r="E166" s="33" t="n"/>
-      <c r="F166" s="33" t="n"/>
-      <c r="G166" s="33" t="n"/>
-      <c r="H166" s="33" t="n"/>
-      <c r="I166" s="33" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="33" t="n"/>
-      <c r="B167" s="33" t="n"/>
-      <c r="C167" s="33" t="n"/>
-      <c r="D167" s="33" t="n"/>
-      <c r="E167" s="33" t="n"/>
-      <c r="F167" s="33" t="n"/>
-      <c r="G167" s="33" t="n"/>
-      <c r="H167" s="33" t="n"/>
-      <c r="I167" s="33" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="33" t="n"/>
@@ -15608,116 +15640,108 @@
       <c r="H180" s="33" t="n"/>
       <c r="I180" s="33" t="n"/>
     </row>
+    <row r="181">
+      <c r="A181" s="33" t="n"/>
+      <c r="B181" s="33" t="n"/>
+      <c r="C181" s="33" t="n"/>
+      <c r="D181" s="33" t="n"/>
+      <c r="E181" s="33" t="n"/>
+      <c r="F181" s="33" t="n"/>
+      <c r="G181" s="33" t="n"/>
+      <c r="H181" s="33" t="n"/>
+      <c r="I181" s="33" t="n"/>
+    </row>
     <row r="182">
-      <c r="A182" s="37" t="inlineStr">
+      <c r="A182" s="33" t="n"/>
+      <c r="B182" s="33" t="n"/>
+      <c r="C182" s="33" t="n"/>
+      <c r="D182" s="33" t="n"/>
+      <c r="E182" s="33" t="n"/>
+      <c r="F182" s="33" t="n"/>
+      <c r="G182" s="33" t="n"/>
+      <c r="H182" s="33" t="n"/>
+      <c r="I182" s="33" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="37" t="inlineStr">
         <is>
           <t>Section I — Revenue segments  (Optional)</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Optional segmented breakdown. Fill rows below + re-upload to override top-level revenue_growth / gross_margin with a segment aggregate. start_year=0 means the segment already exists in Y0; start_year&gt;0 introduces a new revenue line at that projection year.</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="21" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="21" t="inlineStr">
         <is>
           <t>Segment name</t>
         </is>
       </c>
-      <c r="B184" s="21" t="inlineStr">
+      <c r="B186" s="21" t="inlineStr">
         <is>
           <t>Start year</t>
         </is>
       </c>
-      <c r="C184" s="21" t="inlineStr">
+      <c r="C186" s="21" t="inlineStr">
         <is>
           <t>Initial revenue</t>
         </is>
       </c>
-      <c r="D184" s="21" t="inlineStr">
+      <c r="D186" s="21" t="inlineStr">
         <is>
           <t>Growth Y1</t>
         </is>
       </c>
-      <c r="E184" s="21" t="inlineStr">
+      <c r="E186" s="21" t="inlineStr">
         <is>
           <t>Growth Y2</t>
         </is>
       </c>
-      <c r="F184" s="21" t="inlineStr">
+      <c r="F186" s="21" t="inlineStr">
         <is>
           <t>Growth Y3</t>
         </is>
       </c>
-      <c r="G184" s="21" t="inlineStr">
+      <c r="G186" s="21" t="inlineStr">
         <is>
           <t>Growth Y4</t>
         </is>
       </c>
-      <c r="H184" s="21" t="inlineStr">
+      <c r="H186" s="21" t="inlineStr">
         <is>
           <t>Growth Y5</t>
         </is>
       </c>
-      <c r="I184" s="21" t="inlineStr">
+      <c r="I186" s="21" t="inlineStr">
         <is>
           <t>GM Y1</t>
         </is>
       </c>
-      <c r="J184" s="21" t="inlineStr">
+      <c r="J186" s="21" t="inlineStr">
         <is>
           <t>GM Y2</t>
         </is>
       </c>
-      <c r="K184" s="21" t="inlineStr">
+      <c r="K186" s="21" t="inlineStr">
         <is>
           <t>GM Y3</t>
         </is>
       </c>
-      <c r="L184" s="21" t="inlineStr">
+      <c r="L186" s="21" t="inlineStr">
         <is>
           <t>GM Y4</t>
         </is>
       </c>
-      <c r="M184" s="21" t="inlineStr">
+      <c r="M186" s="21" t="inlineStr">
         <is>
           <t>GM Y5</t>
         </is>
       </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="33" t="n"/>
-      <c r="B185" s="33" t="n"/>
-      <c r="C185" s="33" t="n"/>
-      <c r="D185" s="33" t="n"/>
-      <c r="E185" s="33" t="n"/>
-      <c r="F185" s="33" t="n"/>
-      <c r="G185" s="33" t="n"/>
-      <c r="H185" s="33" t="n"/>
-      <c r="I185" s="33" t="n"/>
-      <c r="J185" s="33" t="n"/>
-      <c r="K185" s="33" t="n"/>
-      <c r="L185" s="33" t="n"/>
-      <c r="M185" s="33" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="33" t="n"/>
-      <c r="B186" s="33" t="n"/>
-      <c r="C186" s="33" t="n"/>
-      <c r="D186" s="33" t="n"/>
-      <c r="E186" s="33" t="n"/>
-      <c r="F186" s="33" t="n"/>
-      <c r="G186" s="33" t="n"/>
-      <c r="H186" s="33" t="n"/>
-      <c r="I186" s="33" t="n"/>
-      <c r="J186" s="33" t="n"/>
-      <c r="K186" s="33" t="n"/>
-      <c r="L186" s="33" t="n"/>
-      <c r="M186" s="33" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="33" t="n"/>
@@ -15764,30 +15788,60 @@
       <c r="L189" s="33" t="n"/>
       <c r="M189" s="33" t="n"/>
     </row>
+    <row r="190">
+      <c r="A190" s="33" t="n"/>
+      <c r="B190" s="33" t="n"/>
+      <c r="C190" s="33" t="n"/>
+      <c r="D190" s="33" t="n"/>
+      <c r="E190" s="33" t="n"/>
+      <c r="F190" s="33" t="n"/>
+      <c r="G190" s="33" t="n"/>
+      <c r="H190" s="33" t="n"/>
+      <c r="I190" s="33" t="n"/>
+      <c r="J190" s="33" t="n"/>
+      <c r="K190" s="33" t="n"/>
+      <c r="L190" s="33" t="n"/>
+      <c r="M190" s="33" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="33" t="n"/>
+      <c r="B191" s="33" t="n"/>
+      <c r="C191" s="33" t="n"/>
+      <c r="D191" s="33" t="n"/>
+      <c r="E191" s="33" t="n"/>
+      <c r="F191" s="33" t="n"/>
+      <c r="G191" s="33" t="n"/>
+      <c r="H191" s="33" t="n"/>
+      <c r="I191" s="33" t="n"/>
+      <c r="J191" s="33" t="n"/>
+      <c r="K191" s="33" t="n"/>
+      <c r="L191" s="33" t="n"/>
+      <c r="M191" s="33" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A131:H131"/>
-    <mergeCell ref="A114:H114"/>
+    <mergeCell ref="A185:M185"/>
+    <mergeCell ref="A166:H166"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A125:H125"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A96:H96"/>
-    <mergeCell ref="A164:H164"/>
+    <mergeCell ref="A98:H98"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A108:H108"/>
-    <mergeCell ref="A123:H123"/>
+    <mergeCell ref="A184:M184"/>
+    <mergeCell ref="A116:H116"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A182:M182"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A133:H133"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A183:M183"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F74 F75 F76 F77 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F109 F110 F111 F112 F115 F116 F117 F118 F119 F120 F121 F124 F125 F126 F127 F128 F129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F76 F77 F78 F79 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F111 F112 F113 F114 F117 F118 F119 F120 F121 F122 F123 F126 F127 F128 F129 F130 F131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Audited FS,Management Projections,Capital IQ,Bloomberg,Damodaran,Kroll,Mercer,Prospectus,Engagement Letter,Calculated,Manual"</formula1>
     </dataValidation>
-    <dataValidation sqref="D109 D111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D111 D113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17016,7 +17070,10 @@
           <t>(currency × unit)</t>
         </is>
       </c>
-      <c r="C22" s="41" t="n"/>
+      <c r="C22" s="41">
+        <f>IFERROR(tax_y0,"")</f>
+        <v/>
+      </c>
       <c r="D22" s="41">
         <f>IF(ISNUMBER(tax_effective_rate),-MAX(D18,0)*tax_effective_rate,IF(EXACT(tax_type,"two_tier"),IF(D18&lt;=tax_threshold,-MAX(D18,0)*tax_rate_low,-(tax_threshold*tax_rate_low+MAX(D18-tax_threshold,0)*tax_rate_high)),-MAX(D18,0)*tax_rate_high))</f>
         <v/>
@@ -17049,7 +17106,10 @@
           <t>(currency × unit)</t>
         </is>
       </c>
-      <c r="C23" s="41" t="n"/>
+      <c r="C23" s="41">
+        <f>IFERROR(net_income_y0,"")</f>
+        <v/>
+      </c>
       <c r="D23" s="41">
         <f>D18+D22</f>
         <v/>

--- a/materials/templates/orionmano-valuation-template-v1.xlsx
+++ b/materials/templates/orionmano-valuation-template-v1.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Historical FS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Projections" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DCF (Independent)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Comps" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Football Field" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="WACC" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="CoCo Selection" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="CoCo Multiples" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="CoCo Margins" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="CoCo Ratios" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="CIQ Data Timeline" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Country ERP" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Industry Averages" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Adjustments" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Sensitivity" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Valuation Summary" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="_dropdowns" sheetId="21" state="hidden" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical FS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projections" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF (Independent)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Football Field" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Selection" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Multiples" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Margins" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoCo Ratios" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CIQ Data Timeline" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country ERP" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industry Averages" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjustments" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_dropdowns" sheetId="21" state="hidden" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="company_name">'Inputs'!$D$7</definedName>
@@ -100,62 +100,63 @@
     <definedName name="terminal_growth_rate">'Inputs'!$D$82</definedName>
     <definedName name="terminal_exit_multiple_type">'Inputs'!$D$83</definedName>
     <definedName name="terminal_exit_multiple_value">'Inputs'!$D$84</definedName>
-    <definedName name="risk_free_rate">'Inputs'!$D$87</definedName>
-    <definedName name="risk_free_rate_source">'Inputs'!$D$88</definedName>
-    <definedName name="equity_risk_premium">'Inputs'!$D$89</definedName>
-    <definedName name="country_risk_premium">'Inputs'!$D$90</definedName>
-    <definedName name="unlevered_beta_per_mgmt">'Inputs'!$D$91</definedName>
-    <definedName name="unlevered_beta_indep">'Inputs'!$E$91</definedName>
-    <definedName name="target_debt_to_equity_per_mgmt">'Inputs'!$D$92</definedName>
-    <definedName name="target_debt_to_equity_indep">'Inputs'!$E$92</definedName>
-    <definedName name="levered_beta_per_mgmt">'Inputs'!$D$93</definedName>
-    <definedName name="levered_beta_indep">'Inputs'!$E$93</definedName>
-    <definedName name="size_premium_per_mgmt">'Inputs'!$D$94</definedName>
-    <definedName name="size_premium_indep">'Inputs'!$E$94</definedName>
-    <definedName name="specific_risk_premium_per_mgmt">'Inputs'!$D$95</definedName>
-    <definedName name="specific_risk_premium_indep">'Inputs'!$E$95</definedName>
-    <definedName name="cost_of_equity_per_mgmt">'Inputs'!$D$96</definedName>
-    <definedName name="cost_of_equity_indep">'Inputs'!$E$96</definedName>
-    <definedName name="pretax_cost_of_debt_per_mgmt">'Inputs'!$D$97</definedName>
-    <definedName name="pretax_cost_of_debt_indep">'Inputs'!$E$97</definedName>
-    <definedName name="aftertax_cost_of_debt_per_mgmt">'Inputs'!$D$98</definedName>
-    <definedName name="aftertax_cost_of_debt_indep">'Inputs'!$E$98</definedName>
-    <definedName name="target_debt_weight_per_mgmt">'Inputs'!$D$99</definedName>
-    <definedName name="target_debt_weight_indep">'Inputs'!$E$99</definedName>
-    <definedName name="target_equity_weight_per_mgmt">'Inputs'!$D$100</definedName>
-    <definedName name="target_equity_weight_indep">'Inputs'!$E$100</definedName>
-    <definedName name="wacc_per_mgmt">'Inputs'!$D$101</definedName>
-    <definedName name="wacc_indep">'Inputs'!$E$101</definedName>
-    <definedName name="surplus_assets">'Inputs'!$D$104</definedName>
-    <definedName name="net_debt_override">'Inputs'!$D$105</definedName>
-    <definedName name="minority_interests">'Inputs'!$D$106</definedName>
-    <definedName name="non_operating_assets">'Inputs'!$D$107</definedName>
-    <definedName name="dlom_pct">'Inputs'!$D$108</definedName>
-    <definedName name="dloc_pct">'Inputs'!$D$109</definedName>
-    <definedName name="equity_interest_pct">'Inputs'!$D$110</definedName>
-    <definedName name="shares_outstanding">'Inputs'!$D$111</definedName>
-    <definedName name="shares_outstanding_diluted">'Inputs'!$D$112</definedName>
-    <definedName name="pre_money_pct">'Inputs'!$D$113</definedName>
-    <definedName name="capitalize_rd">'Inputs'!$D$116</definedName>
-    <definedName name="rd_amortization_years">'Inputs'!$D$117</definedName>
-    <definedName name="convert_operating_leases">'Inputs'!$D$118</definedName>
-    <definedName name="lease_discount_rate">'Inputs'!$D$119</definedName>
-    <definedName name="weight_dcf">'Inputs'!$D$122</definedName>
-    <definedName name="weight_comps">'Inputs'!$D$123</definedName>
-    <definedName name="weight_precedent">'Inputs'!$D$124</definedName>
-    <definedName name="weight_nav">'Inputs'!$D$125</definedName>
-    <definedName name="selected_low">'Inputs'!$D$126</definedName>
-    <definedName name="selected_mid">'Inputs'!$D$127</definedName>
-    <definedName name="selected_high">'Inputs'!$D$128</definedName>
-    <definedName name="sens_wacc_step">'Inputs'!$D$131</definedName>
-    <definedName name="sens_wacc_count">'Inputs'!$D$132</definedName>
-    <definedName name="sens_terminal_g_step">'Inputs'!$D$133</definedName>
-    <definedName name="sens_terminal_g_count">'Inputs'!$D$134</definedName>
-    <definedName name="sens_revenue_g_step">'Inputs'!$D$135</definedName>
-    <definedName name="sens_ebitda_margin_step">'Inputs'!$D$136</definedName>
-    <definedName name="cocos_table">'Inputs'!$A$140:$L$169</definedName>
-    <definedName name="precedents_table">'Inputs'!$A$173:$I$187</definedName>
-    <definedName name="segments_table">'Inputs'!$A$192:$M$196</definedName>
+    <definedName name="terminal_nominal_gdp_growth">'Inputs'!$D$85</definedName>
+    <definedName name="risk_free_rate">'Inputs'!$D$88</definedName>
+    <definedName name="risk_free_rate_source">'Inputs'!$D$89</definedName>
+    <definedName name="equity_risk_premium">'Inputs'!$D$90</definedName>
+    <definedName name="country_risk_premium">'Inputs'!$D$91</definedName>
+    <definedName name="unlevered_beta_per_mgmt">'Inputs'!$D$92</definedName>
+    <definedName name="unlevered_beta_indep">'Inputs'!$E$92</definedName>
+    <definedName name="target_debt_to_equity_per_mgmt">'Inputs'!$D$93</definedName>
+    <definedName name="target_debt_to_equity_indep">'Inputs'!$E$93</definedName>
+    <definedName name="levered_beta_per_mgmt">'Inputs'!$D$94</definedName>
+    <definedName name="levered_beta_indep">'Inputs'!$E$94</definedName>
+    <definedName name="size_premium_per_mgmt">'Inputs'!$D$95</definedName>
+    <definedName name="size_premium_indep">'Inputs'!$E$95</definedName>
+    <definedName name="specific_risk_premium_per_mgmt">'Inputs'!$D$96</definedName>
+    <definedName name="specific_risk_premium_indep">'Inputs'!$E$96</definedName>
+    <definedName name="cost_of_equity_per_mgmt">'Inputs'!$D$97</definedName>
+    <definedName name="cost_of_equity_indep">'Inputs'!$E$97</definedName>
+    <definedName name="pretax_cost_of_debt_per_mgmt">'Inputs'!$D$98</definedName>
+    <definedName name="pretax_cost_of_debt_indep">'Inputs'!$E$98</definedName>
+    <definedName name="aftertax_cost_of_debt_per_mgmt">'Inputs'!$D$99</definedName>
+    <definedName name="aftertax_cost_of_debt_indep">'Inputs'!$E$99</definedName>
+    <definedName name="target_debt_weight_per_mgmt">'Inputs'!$D$100</definedName>
+    <definedName name="target_debt_weight_indep">'Inputs'!$E$100</definedName>
+    <definedName name="target_equity_weight_per_mgmt">'Inputs'!$D$101</definedName>
+    <definedName name="target_equity_weight_indep">'Inputs'!$E$101</definedName>
+    <definedName name="wacc_per_mgmt">'Inputs'!$D$102</definedName>
+    <definedName name="wacc_indep">'Inputs'!$E$102</definedName>
+    <definedName name="surplus_assets">'Inputs'!$D$105</definedName>
+    <definedName name="net_debt_override">'Inputs'!$D$106</definedName>
+    <definedName name="minority_interests">'Inputs'!$D$107</definedName>
+    <definedName name="non_operating_assets">'Inputs'!$D$108</definedName>
+    <definedName name="dlom_pct">'Inputs'!$D$109</definedName>
+    <definedName name="dloc_pct">'Inputs'!$D$110</definedName>
+    <definedName name="equity_interest_pct">'Inputs'!$D$111</definedName>
+    <definedName name="shares_outstanding">'Inputs'!$D$112</definedName>
+    <definedName name="shares_outstanding_diluted">'Inputs'!$D$113</definedName>
+    <definedName name="pre_money_pct">'Inputs'!$D$114</definedName>
+    <definedName name="capitalize_rd">'Inputs'!$D$117</definedName>
+    <definedName name="rd_amortization_years">'Inputs'!$D$118</definedName>
+    <definedName name="convert_operating_leases">'Inputs'!$D$119</definedName>
+    <definedName name="lease_discount_rate">'Inputs'!$D$120</definedName>
+    <definedName name="weight_dcf">'Inputs'!$D$123</definedName>
+    <definedName name="weight_comps">'Inputs'!$D$124</definedName>
+    <definedName name="weight_precedent">'Inputs'!$D$125</definedName>
+    <definedName name="weight_nav">'Inputs'!$D$126</definedName>
+    <definedName name="selected_low">'Inputs'!$D$127</definedName>
+    <definedName name="selected_mid">'Inputs'!$D$128</definedName>
+    <definedName name="selected_high">'Inputs'!$D$129</definedName>
+    <definedName name="sens_wacc_step">'Inputs'!$D$132</definedName>
+    <definedName name="sens_wacc_count">'Inputs'!$D$133</definedName>
+    <definedName name="sens_terminal_g_step">'Inputs'!$D$134</definedName>
+    <definedName name="sens_terminal_g_count">'Inputs'!$D$135</definedName>
+    <definedName name="sens_revenue_g_step">'Inputs'!$D$136</definedName>
+    <definedName name="sens_ebitda_margin_step">'Inputs'!$D$137</definedName>
+    <definedName name="cocos_table">'Inputs'!$A$141:$L$170</definedName>
+    <definedName name="precedents_table">'Inputs'!$A$174:$I$188</definedName>
+    <definedName name="segments_table">'Inputs'!$A$193:$U$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -290,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -392,6 +393,7 @@
     <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1882,11 +1884,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="56">
         <f>IF(ISNUMBER(tax_effective_rate),tax_effective_rate,tax_rate_high)</f>
         <v/>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="56">
         <f>IF(ISNUMBER(tax_effective_rate),tax_effective_rate,tax_rate_high)</f>
         <v/>
       </c>
@@ -1902,11 +1904,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="57">
         <f>unlevered_beta_per_mgmt</f>
         <v/>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="57">
         <f>unlevered_beta_indep</f>
         <v/>
       </c>
@@ -1922,11 +1924,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="56">
         <f>target_debt_to_equity_per_mgmt</f>
         <v/>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="56">
         <f>target_debt_to_equity_indep</f>
         <v/>
       </c>
@@ -1942,11 +1944,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="57">
         <f>E8*(1+(1-E7)*E9)</f>
         <v/>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="57">
         <f>F8*(1+(1-F7)*F9)</f>
         <v/>
       </c>
@@ -1962,11 +1964,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="56">
         <f>risk_free_rate</f>
         <v/>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="56">
         <f>risk_free_rate</f>
         <v/>
       </c>
@@ -1982,11 +1984,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="56">
         <f>equity_risk_premium</f>
         <v/>
       </c>
-      <c r="F12" s="55">
+      <c r="F12" s="56">
         <f>equity_risk_premium</f>
         <v/>
       </c>
@@ -2002,11 +2004,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="56">
         <f>country_risk_premium</f>
         <v/>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="56">
         <f>country_risk_premium</f>
         <v/>
       </c>
@@ -2022,11 +2024,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="56">
         <f>size_premium_per_mgmt</f>
         <v/>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="56">
         <f>size_premium_indep</f>
         <v/>
       </c>
@@ -2042,11 +2044,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="56">
         <f>specific_risk_premium_per_mgmt</f>
         <v/>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="56">
         <f>specific_risk_premium_indep</f>
         <v/>
       </c>
@@ -2062,11 +2064,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="56">
         <f>E11+E10*E12+E13+E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="56">
         <f>F11+F10*F12+F13+F14+F15</f>
         <v/>
       </c>
@@ -2089,11 +2091,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="56">
         <f>pretax_cost_of_debt_per_mgmt</f>
         <v/>
       </c>
-      <c r="F19" s="55">
+      <c r="F19" s="56">
         <f>pretax_cost_of_debt_indep</f>
         <v/>
       </c>
@@ -2109,11 +2111,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="56">
         <f>E19*(1-E7)</f>
         <v/>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="56">
         <f>F19*(1-F7)</f>
         <v/>
       </c>
@@ -2136,11 +2138,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="56">
         <f>target_debt_weight_per_mgmt</f>
         <v/>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="56">
         <f>target_debt_weight_indep</f>
         <v/>
       </c>
@@ -2156,11 +2158,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="56">
         <f>target_equity_weight_per_mgmt</f>
         <v/>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="56">
         <f>target_equity_weight_indep</f>
         <v/>
       </c>
@@ -2176,11 +2178,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="56">
         <f>E16*E24+E20*E23</f>
         <v/>
       </c>
-      <c r="F25" s="55">
+      <c r="F25" s="56">
         <f>F16*F24+F20*F23</f>
         <v/>
       </c>
@@ -3909,12 +3911,12 @@
         <f>Inputs!D127</f>
         <v/>
       </c>
-      <c r="E6" s="57" t="n"/>
-      <c r="F6" s="57" t="n"/>
-      <c r="G6" s="58" t="n"/>
-      <c r="H6" s="58" t="n"/>
-      <c r="I6" s="58" t="n"/>
-      <c r="J6" s="58" t="n"/>
+      <c r="E6" s="58" t="n"/>
+      <c r="F6" s="58" t="n"/>
+      <c r="G6" s="59" t="n"/>
+      <c r="H6" s="59" t="n"/>
+      <c r="I6" s="59" t="n"/>
+      <c r="J6" s="59" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="33">
@@ -3933,12 +3935,12 @@
         <f>Inputs!D128</f>
         <v/>
       </c>
-      <c r="E7" s="57" t="n"/>
-      <c r="F7" s="57" t="n"/>
-      <c r="G7" s="58" t="n"/>
-      <c r="H7" s="58" t="n"/>
-      <c r="I7" s="58" t="n"/>
-      <c r="J7" s="58" t="n"/>
+      <c r="E7" s="58" t="n"/>
+      <c r="F7" s="58" t="n"/>
+      <c r="G7" s="59" t="n"/>
+      <c r="H7" s="59" t="n"/>
+      <c r="I7" s="59" t="n"/>
+      <c r="J7" s="59" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="33">
@@ -3957,12 +3959,12 @@
         <f>Inputs!D129</f>
         <v/>
       </c>
-      <c r="E8" s="57" t="n"/>
-      <c r="F8" s="57" t="n"/>
-      <c r="G8" s="58" t="n"/>
-      <c r="H8" s="58" t="n"/>
-      <c r="I8" s="58" t="n"/>
-      <c r="J8" s="58" t="n"/>
+      <c r="E8" s="58" t="n"/>
+      <c r="F8" s="58" t="n"/>
+      <c r="G8" s="59" t="n"/>
+      <c r="H8" s="59" t="n"/>
+      <c r="I8" s="59" t="n"/>
+      <c r="J8" s="59" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="33">
@@ -3981,12 +3983,12 @@
         <f>Inputs!D130</f>
         <v/>
       </c>
-      <c r="E9" s="57" t="n"/>
-      <c r="F9" s="57" t="n"/>
-      <c r="G9" s="58" t="n"/>
-      <c r="H9" s="58" t="n"/>
-      <c r="I9" s="58" t="n"/>
-      <c r="J9" s="58" t="n"/>
+      <c r="E9" s="58" t="n"/>
+      <c r="F9" s="58" t="n"/>
+      <c r="G9" s="59" t="n"/>
+      <c r="H9" s="59" t="n"/>
+      <c r="I9" s="59" t="n"/>
+      <c r="J9" s="59" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="33">
@@ -4005,12 +4007,12 @@
         <f>Inputs!D131</f>
         <v/>
       </c>
-      <c r="E10" s="57" t="n"/>
-      <c r="F10" s="57" t="n"/>
-      <c r="G10" s="58" t="n"/>
-      <c r="H10" s="58" t="n"/>
-      <c r="I10" s="58" t="n"/>
-      <c r="J10" s="58" t="n"/>
+      <c r="E10" s="58" t="n"/>
+      <c r="F10" s="58" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="n"/>
+      <c r="J10" s="59" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="33">
@@ -4029,12 +4031,12 @@
         <f>Inputs!D132</f>
         <v/>
       </c>
-      <c r="E11" s="57" t="n"/>
-      <c r="F11" s="57" t="n"/>
-      <c r="G11" s="58" t="n"/>
-      <c r="H11" s="58" t="n"/>
-      <c r="I11" s="58" t="n"/>
-      <c r="J11" s="58" t="n"/>
+      <c r="E11" s="58" t="n"/>
+      <c r="F11" s="58" t="n"/>
+      <c r="G11" s="59" t="n"/>
+      <c r="H11" s="59" t="n"/>
+      <c r="I11" s="59" t="n"/>
+      <c r="J11" s="59" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="33">
@@ -4053,12 +4055,12 @@
         <f>Inputs!D133</f>
         <v/>
       </c>
-      <c r="E12" s="57" t="n"/>
-      <c r="F12" s="57" t="n"/>
-      <c r="G12" s="58" t="n"/>
-      <c r="H12" s="58" t="n"/>
-      <c r="I12" s="58" t="n"/>
-      <c r="J12" s="58" t="n"/>
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="58" t="n"/>
+      <c r="G12" s="59" t="n"/>
+      <c r="H12" s="59" t="n"/>
+      <c r="I12" s="59" t="n"/>
+      <c r="J12" s="59" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="33">
@@ -4077,12 +4079,12 @@
         <f>Inputs!D134</f>
         <v/>
       </c>
-      <c r="E13" s="57" t="n"/>
-      <c r="F13" s="57" t="n"/>
-      <c r="G13" s="58" t="n"/>
-      <c r="H13" s="58" t="n"/>
-      <c r="I13" s="58" t="n"/>
-      <c r="J13" s="58" t="n"/>
+      <c r="E13" s="58" t="n"/>
+      <c r="F13" s="58" t="n"/>
+      <c r="G13" s="59" t="n"/>
+      <c r="H13" s="59" t="n"/>
+      <c r="I13" s="59" t="n"/>
+      <c r="J13" s="59" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="33">
@@ -4101,12 +4103,12 @@
         <f>Inputs!D135</f>
         <v/>
       </c>
-      <c r="E14" s="57" t="n"/>
-      <c r="F14" s="57" t="n"/>
-      <c r="G14" s="58" t="n"/>
-      <c r="H14" s="58" t="n"/>
-      <c r="I14" s="58" t="n"/>
-      <c r="J14" s="58" t="n"/>
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="59" t="n"/>
+      <c r="H14" s="59" t="n"/>
+      <c r="I14" s="59" t="n"/>
+      <c r="J14" s="59" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="33">
@@ -4125,12 +4127,12 @@
         <f>Inputs!D136</f>
         <v/>
       </c>
-      <c r="E15" s="57" t="n"/>
-      <c r="F15" s="57" t="n"/>
-      <c r="G15" s="58" t="n"/>
-      <c r="H15" s="58" t="n"/>
-      <c r="I15" s="58" t="n"/>
-      <c r="J15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="59" t="n"/>
+      <c r="H15" s="59" t="n"/>
+      <c r="I15" s="59" t="n"/>
+      <c r="J15" s="59" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="33">
@@ -4149,12 +4151,12 @@
         <f>Inputs!D137</f>
         <v/>
       </c>
-      <c r="E16" s="57" t="n"/>
-      <c r="F16" s="57" t="n"/>
-      <c r="G16" s="58" t="n"/>
-      <c r="H16" s="58" t="n"/>
-      <c r="I16" s="58" t="n"/>
-      <c r="J16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="59" t="n"/>
+      <c r="H16" s="59" t="n"/>
+      <c r="I16" s="59" t="n"/>
+      <c r="J16" s="59" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="33">
@@ -4173,12 +4175,12 @@
         <f>Inputs!D138</f>
         <v/>
       </c>
-      <c r="E17" s="57" t="n"/>
-      <c r="F17" s="57" t="n"/>
-      <c r="G17" s="58" t="n"/>
-      <c r="H17" s="58" t="n"/>
-      <c r="I17" s="58" t="n"/>
-      <c r="J17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="59" t="n"/>
+      <c r="H17" s="59" t="n"/>
+      <c r="I17" s="59" t="n"/>
+      <c r="J17" s="59" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="33">
@@ -4197,12 +4199,12 @@
         <f>Inputs!D139</f>
         <v/>
       </c>
-      <c r="E18" s="57" t="n"/>
-      <c r="F18" s="57" t="n"/>
-      <c r="G18" s="58" t="n"/>
-      <c r="H18" s="58" t="n"/>
-      <c r="I18" s="58" t="n"/>
-      <c r="J18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="59" t="n"/>
+      <c r="H18" s="59" t="n"/>
+      <c r="I18" s="59" t="n"/>
+      <c r="J18" s="59" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="33">
@@ -4221,12 +4223,12 @@
         <f>Inputs!D140</f>
         <v/>
       </c>
-      <c r="E19" s="57" t="n"/>
-      <c r="F19" s="57" t="n"/>
-      <c r="G19" s="58" t="n"/>
-      <c r="H19" s="58" t="n"/>
-      <c r="I19" s="58" t="n"/>
-      <c r="J19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="59" t="n"/>
+      <c r="H19" s="59" t="n"/>
+      <c r="I19" s="59" t="n"/>
+      <c r="J19" s="59" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="33">
@@ -4245,12 +4247,12 @@
         <f>Inputs!D141</f>
         <v/>
       </c>
-      <c r="E20" s="57" t="n"/>
-      <c r="F20" s="57" t="n"/>
-      <c r="G20" s="58" t="n"/>
-      <c r="H20" s="58" t="n"/>
-      <c r="I20" s="58" t="n"/>
-      <c r="J20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="59" t="n"/>
+      <c r="H20" s="59" t="n"/>
+      <c r="I20" s="59" t="n"/>
+      <c r="J20" s="59" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="33">
@@ -4269,12 +4271,12 @@
         <f>Inputs!D142</f>
         <v/>
       </c>
-      <c r="E21" s="57" t="n"/>
-      <c r="F21" s="57" t="n"/>
-      <c r="G21" s="58" t="n"/>
-      <c r="H21" s="58" t="n"/>
-      <c r="I21" s="58" t="n"/>
-      <c r="J21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="59" t="n"/>
+      <c r="H21" s="59" t="n"/>
+      <c r="I21" s="59" t="n"/>
+      <c r="J21" s="59" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="33">
@@ -4293,12 +4295,12 @@
         <f>Inputs!D143</f>
         <v/>
       </c>
-      <c r="E22" s="57" t="n"/>
-      <c r="F22" s="57" t="n"/>
-      <c r="G22" s="58" t="n"/>
-      <c r="H22" s="58" t="n"/>
-      <c r="I22" s="58" t="n"/>
-      <c r="J22" s="58" t="n"/>
+      <c r="E22" s="58" t="n"/>
+      <c r="F22" s="58" t="n"/>
+      <c r="G22" s="59" t="n"/>
+      <c r="H22" s="59" t="n"/>
+      <c r="I22" s="59" t="n"/>
+      <c r="J22" s="59" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="33">
@@ -4317,12 +4319,12 @@
         <f>Inputs!D144</f>
         <v/>
       </c>
-      <c r="E23" s="57" t="n"/>
-      <c r="F23" s="57" t="n"/>
-      <c r="G23" s="58" t="n"/>
-      <c r="H23" s="58" t="n"/>
-      <c r="I23" s="58" t="n"/>
-      <c r="J23" s="58" t="n"/>
+      <c r="E23" s="58" t="n"/>
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="59" t="n"/>
+      <c r="H23" s="59" t="n"/>
+      <c r="I23" s="59" t="n"/>
+      <c r="J23" s="59" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="33">
@@ -4341,12 +4343,12 @@
         <f>Inputs!D145</f>
         <v/>
       </c>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="57" t="n"/>
-      <c r="G24" s="58" t="n"/>
-      <c r="H24" s="58" t="n"/>
-      <c r="I24" s="58" t="n"/>
-      <c r="J24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="58" t="n"/>
+      <c r="G24" s="59" t="n"/>
+      <c r="H24" s="59" t="n"/>
+      <c r="I24" s="59" t="n"/>
+      <c r="J24" s="59" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="33">
@@ -4365,12 +4367,12 @@
         <f>Inputs!D146</f>
         <v/>
       </c>
-      <c r="E25" s="57" t="n"/>
-      <c r="F25" s="57" t="n"/>
-      <c r="G25" s="58" t="n"/>
-      <c r="H25" s="58" t="n"/>
-      <c r="I25" s="58" t="n"/>
-      <c r="J25" s="58" t="n"/>
+      <c r="E25" s="58" t="n"/>
+      <c r="F25" s="58" t="n"/>
+      <c r="G25" s="59" t="n"/>
+      <c r="H25" s="59" t="n"/>
+      <c r="I25" s="59" t="n"/>
+      <c r="J25" s="59" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="33">
@@ -4389,12 +4391,12 @@
         <f>Inputs!D147</f>
         <v/>
       </c>
-      <c r="E26" s="57" t="n"/>
-      <c r="F26" s="57" t="n"/>
-      <c r="G26" s="58" t="n"/>
-      <c r="H26" s="58" t="n"/>
-      <c r="I26" s="58" t="n"/>
-      <c r="J26" s="58" t="n"/>
+      <c r="E26" s="58" t="n"/>
+      <c r="F26" s="58" t="n"/>
+      <c r="G26" s="59" t="n"/>
+      <c r="H26" s="59" t="n"/>
+      <c r="I26" s="59" t="n"/>
+      <c r="J26" s="59" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="33">
@@ -4413,12 +4415,12 @@
         <f>Inputs!D148</f>
         <v/>
       </c>
-      <c r="E27" s="57" t="n"/>
-      <c r="F27" s="57" t="n"/>
-      <c r="G27" s="58" t="n"/>
-      <c r="H27" s="58" t="n"/>
-      <c r="I27" s="58" t="n"/>
-      <c r="J27" s="58" t="n"/>
+      <c r="E27" s="58" t="n"/>
+      <c r="F27" s="58" t="n"/>
+      <c r="G27" s="59" t="n"/>
+      <c r="H27" s="59" t="n"/>
+      <c r="I27" s="59" t="n"/>
+      <c r="J27" s="59" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="33">
@@ -4437,12 +4439,12 @@
         <f>Inputs!D149</f>
         <v/>
       </c>
-      <c r="E28" s="57" t="n"/>
-      <c r="F28" s="57" t="n"/>
-      <c r="G28" s="58" t="n"/>
-      <c r="H28" s="58" t="n"/>
-      <c r="I28" s="58" t="n"/>
-      <c r="J28" s="58" t="n"/>
+      <c r="E28" s="58" t="n"/>
+      <c r="F28" s="58" t="n"/>
+      <c r="G28" s="59" t="n"/>
+      <c r="H28" s="59" t="n"/>
+      <c r="I28" s="59" t="n"/>
+      <c r="J28" s="59" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="33">
@@ -4461,12 +4463,12 @@
         <f>Inputs!D150</f>
         <v/>
       </c>
-      <c r="E29" s="57" t="n"/>
-      <c r="F29" s="57" t="n"/>
-      <c r="G29" s="58" t="n"/>
-      <c r="H29" s="58" t="n"/>
-      <c r="I29" s="58" t="n"/>
-      <c r="J29" s="58" t="n"/>
+      <c r="E29" s="58" t="n"/>
+      <c r="F29" s="58" t="n"/>
+      <c r="G29" s="59" t="n"/>
+      <c r="H29" s="59" t="n"/>
+      <c r="I29" s="59" t="n"/>
+      <c r="J29" s="59" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="33">
@@ -4485,12 +4487,12 @@
         <f>Inputs!D151</f>
         <v/>
       </c>
-      <c r="E30" s="57" t="n"/>
-      <c r="F30" s="57" t="n"/>
-      <c r="G30" s="58" t="n"/>
-      <c r="H30" s="58" t="n"/>
-      <c r="I30" s="58" t="n"/>
-      <c r="J30" s="58" t="n"/>
+      <c r="E30" s="58" t="n"/>
+      <c r="F30" s="58" t="n"/>
+      <c r="G30" s="59" t="n"/>
+      <c r="H30" s="59" t="n"/>
+      <c r="I30" s="59" t="n"/>
+      <c r="J30" s="59" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="33">
@@ -4509,12 +4511,12 @@
         <f>Inputs!D152</f>
         <v/>
       </c>
-      <c r="E31" s="57" t="n"/>
-      <c r="F31" s="57" t="n"/>
-      <c r="G31" s="58" t="n"/>
-      <c r="H31" s="58" t="n"/>
-      <c r="I31" s="58" t="n"/>
-      <c r="J31" s="58" t="n"/>
+      <c r="E31" s="58" t="n"/>
+      <c r="F31" s="58" t="n"/>
+      <c r="G31" s="59" t="n"/>
+      <c r="H31" s="59" t="n"/>
+      <c r="I31" s="59" t="n"/>
+      <c r="J31" s="59" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="33">
@@ -4533,12 +4535,12 @@
         <f>Inputs!D153</f>
         <v/>
       </c>
-      <c r="E32" s="57" t="n"/>
-      <c r="F32" s="57" t="n"/>
-      <c r="G32" s="58" t="n"/>
-      <c r="H32" s="58" t="n"/>
-      <c r="I32" s="58" t="n"/>
-      <c r="J32" s="58" t="n"/>
+      <c r="E32" s="58" t="n"/>
+      <c r="F32" s="58" t="n"/>
+      <c r="G32" s="59" t="n"/>
+      <c r="H32" s="59" t="n"/>
+      <c r="I32" s="59" t="n"/>
+      <c r="J32" s="59" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="33">
@@ -4557,12 +4559,12 @@
         <f>Inputs!D154</f>
         <v/>
       </c>
-      <c r="E33" s="57" t="n"/>
-      <c r="F33" s="57" t="n"/>
-      <c r="G33" s="58" t="n"/>
-      <c r="H33" s="58" t="n"/>
-      <c r="I33" s="58" t="n"/>
-      <c r="J33" s="58" t="n"/>
+      <c r="E33" s="58" t="n"/>
+      <c r="F33" s="58" t="n"/>
+      <c r="G33" s="59" t="n"/>
+      <c r="H33" s="59" t="n"/>
+      <c r="I33" s="59" t="n"/>
+      <c r="J33" s="59" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="33">
@@ -4581,12 +4583,12 @@
         <f>Inputs!D155</f>
         <v/>
       </c>
-      <c r="E34" s="57" t="n"/>
-      <c r="F34" s="57" t="n"/>
-      <c r="G34" s="58" t="n"/>
-      <c r="H34" s="58" t="n"/>
-      <c r="I34" s="58" t="n"/>
-      <c r="J34" s="58" t="n"/>
+      <c r="E34" s="58" t="n"/>
+      <c r="F34" s="58" t="n"/>
+      <c r="G34" s="59" t="n"/>
+      <c r="H34" s="59" t="n"/>
+      <c r="I34" s="59" t="n"/>
+      <c r="J34" s="59" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="33">
@@ -4605,12 +4607,12 @@
         <f>Inputs!D156</f>
         <v/>
       </c>
-      <c r="E35" s="57" t="n"/>
-      <c r="F35" s="57" t="n"/>
-      <c r="G35" s="58" t="n"/>
-      <c r="H35" s="58" t="n"/>
-      <c r="I35" s="58" t="n"/>
-      <c r="J35" s="58" t="n"/>
+      <c r="E35" s="58" t="n"/>
+      <c r="F35" s="58" t="n"/>
+      <c r="G35" s="59" t="n"/>
+      <c r="H35" s="59" t="n"/>
+      <c r="I35" s="59" t="n"/>
+      <c r="J35" s="59" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="44" t="inlineStr">
@@ -4618,27 +4620,27 @@
           <t>Maximum</t>
         </is>
       </c>
-      <c r="E37" s="59">
+      <c r="E37" s="60">
         <f>IFERROR(MAX(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F37" s="59">
+      <c r="F37" s="60">
         <f>IFERROR(MAX(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G37" s="60">
+      <c r="G37" s="61">
         <f>IFERROR(MAX(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H37" s="60">
+      <c r="H37" s="61">
         <f>IFERROR(MAX(H6:H35),"n/a")</f>
         <v/>
       </c>
-      <c r="I37" s="60">
+      <c r="I37" s="61">
         <f>IFERROR(MAX(I6:I35),"n/a")</f>
         <v/>
       </c>
-      <c r="J37" s="60">
+      <c r="J37" s="61">
         <f>IFERROR(MAX(J6:J35),"n/a")</f>
         <v/>
       </c>
@@ -4649,27 +4651,27 @@
           <t>Q3 (75%)</t>
         </is>
       </c>
-      <c r="E38" s="59">
+      <c r="E38" s="60">
         <f>IFERROR(QUARTILE(E6:E35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="F38" s="59">
+      <c r="F38" s="60">
         <f>IFERROR(QUARTILE(F6:F35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="G38" s="60">
+      <c r="G38" s="61">
         <f>IFERROR(QUARTILE(G6:G35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="H38" s="60">
+      <c r="H38" s="61">
         <f>IFERROR(QUARTILE(H6:H35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="I38" s="60">
+      <c r="I38" s="61">
         <f>IFERROR(QUARTILE(I6:I35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="J38" s="60">
+      <c r="J38" s="61">
         <f>IFERROR(QUARTILE(J6:J35,3),"n/a")</f>
         <v/>
       </c>
@@ -4680,27 +4682,27 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="E39" s="61">
+      <c r="E39" s="62">
         <f>IFERROR(MEDIAN(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F39" s="61">
+      <c r="F39" s="62">
         <f>IFERROR(MEDIAN(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G39" s="62">
+      <c r="G39" s="63">
         <f>IFERROR(MEDIAN(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H39" s="62">
+      <c r="H39" s="63">
         <f>IFERROR(MEDIAN(H6:H35),"n/a")</f>
         <v/>
       </c>
-      <c r="I39" s="62">
+      <c r="I39" s="63">
         <f>IFERROR(MEDIAN(I6:I35),"n/a")</f>
         <v/>
       </c>
-      <c r="J39" s="62">
+      <c r="J39" s="63">
         <f>IFERROR(MEDIAN(J6:J35),"n/a")</f>
         <v/>
       </c>
@@ -4711,27 +4713,27 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="E40" s="59">
+      <c r="E40" s="60">
         <f>IFERROR(AVERAGE(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F40" s="59">
+      <c r="F40" s="60">
         <f>IFERROR(AVERAGE(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G40" s="60">
+      <c r="G40" s="61">
         <f>IFERROR(AVERAGE(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H40" s="60">
+      <c r="H40" s="61">
         <f>IFERROR(AVERAGE(H6:H35),"n/a")</f>
         <v/>
       </c>
-      <c r="I40" s="60">
+      <c r="I40" s="61">
         <f>IFERROR(AVERAGE(I6:I35),"n/a")</f>
         <v/>
       </c>
-      <c r="J40" s="60">
+      <c r="J40" s="61">
         <f>IFERROR(AVERAGE(J6:J35),"n/a")</f>
         <v/>
       </c>
@@ -4742,27 +4744,27 @@
           <t>Q1 (25%)</t>
         </is>
       </c>
-      <c r="E41" s="59">
+      <c r="E41" s="60">
         <f>IFERROR(QUARTILE(E6:E35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="F41" s="59">
+      <c r="F41" s="60">
         <f>IFERROR(QUARTILE(F6:F35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="G41" s="60">
+      <c r="G41" s="61">
         <f>IFERROR(QUARTILE(G6:G35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="H41" s="60">
+      <c r="H41" s="61">
         <f>IFERROR(QUARTILE(H6:H35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="I41" s="60">
+      <c r="I41" s="61">
         <f>IFERROR(QUARTILE(I6:I35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="J41" s="60">
+      <c r="J41" s="61">
         <f>IFERROR(QUARTILE(J6:J35,1),"n/a")</f>
         <v/>
       </c>
@@ -4773,27 +4775,27 @@
           <t>Minimum</t>
         </is>
       </c>
-      <c r="E42" s="59">
+      <c r="E42" s="60">
         <f>IFERROR(MIN(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F42" s="59">
+      <c r="F42" s="60">
         <f>IFERROR(MIN(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G42" s="60">
+      <c r="G42" s="61">
         <f>IFERROR(MIN(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H42" s="60">
+      <c r="H42" s="61">
         <f>IFERROR(MIN(H6:H35),"n/a")</f>
         <v/>
       </c>
-      <c r="I42" s="60">
+      <c r="I42" s="61">
         <f>IFERROR(MIN(I6:I35),"n/a")</f>
         <v/>
       </c>
-      <c r="J42" s="60">
+      <c r="J42" s="61">
         <f>IFERROR(MIN(J6:J35),"n/a")</f>
         <v/>
       </c>
@@ -4819,19 +4821,19 @@
         <f>IFERROR(AVERAGEIFS(F6:F35,$A$6:$A$35,1,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="G45" s="63">
+      <c r="G45" s="64">
         <f>IFERROR(AVERAGEIFS(G6:G35,$A$6:$A$35,1,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="H45" s="63">
+      <c r="H45" s="64">
         <f>IFERROR(AVERAGEIFS(H6:H35,$A$6:$A$35,1,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="I45" s="63">
+      <c r="I45" s="64">
         <f>IFERROR(AVERAGEIFS(I6:I35,$A$6:$A$35,1,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="J45" s="63">
+      <c r="J45" s="64">
         <f>IFERROR(AVERAGEIFS(J6:J35,$A$6:$A$35,1,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
@@ -4850,19 +4852,19 @@
         <f>IFERROR(AVERAGEIFS(F6:F35,$A$6:$A$35,2,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="G46" s="63">
+      <c r="G46" s="64">
         <f>IFERROR(AVERAGEIFS(G6:G35,$A$6:$A$35,2,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="H46" s="63">
+      <c r="H46" s="64">
         <f>IFERROR(AVERAGEIFS(H6:H35,$A$6:$A$35,2,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="I46" s="63">
+      <c r="I46" s="64">
         <f>IFERROR(AVERAGEIFS(I6:I35,$A$6:$A$35,2,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="J46" s="63">
+      <c r="J46" s="64">
         <f>IFERROR(AVERAGEIFS(J6:J35,$A$6:$A$35,2,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
@@ -4881,19 +4883,19 @@
         <f>IFERROR(AVERAGEIFS(F6:F35,$A$6:$A$35,3,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="G47" s="63">
+      <c r="G47" s="64">
         <f>IFERROR(AVERAGEIFS(G6:G35,$A$6:$A$35,3,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="H47" s="63">
+      <c r="H47" s="64">
         <f>IFERROR(AVERAGEIFS(H6:H35,$A$6:$A$35,3,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="I47" s="63">
+      <c r="I47" s="64">
         <f>IFERROR(AVERAGEIFS(I6:I35,$A$6:$A$35,3,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
-      <c r="J47" s="63">
+      <c r="J47" s="64">
         <f>IFERROR(AVERAGEIFS(J6:J35,$A$6:$A$35,3,$B$6:$B$35,TRUE),"n/a")</f>
         <v/>
       </c>
@@ -4993,9 +4995,9 @@
         <f>Inputs!D127</f>
         <v/>
       </c>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="n"/>
-      <c r="G6" s="64" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="n"/>
+      <c r="G6" s="65" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="33">
@@ -5014,9 +5016,9 @@
         <f>Inputs!D128</f>
         <v/>
       </c>
-      <c r="E7" s="64" t="n"/>
-      <c r="F7" s="64" t="n"/>
-      <c r="G7" s="64" t="n"/>
+      <c r="E7" s="65" t="n"/>
+      <c r="F7" s="65" t="n"/>
+      <c r="G7" s="65" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="33">
@@ -5035,9 +5037,9 @@
         <f>Inputs!D129</f>
         <v/>
       </c>
-      <c r="E8" s="64" t="n"/>
-      <c r="F8" s="64" t="n"/>
-      <c r="G8" s="64" t="n"/>
+      <c r="E8" s="65" t="n"/>
+      <c r="F8" s="65" t="n"/>
+      <c r="G8" s="65" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="33">
@@ -5056,9 +5058,9 @@
         <f>Inputs!D130</f>
         <v/>
       </c>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="64" t="n"/>
-      <c r="G9" s="64" t="n"/>
+      <c r="E9" s="65" t="n"/>
+      <c r="F9" s="65" t="n"/>
+      <c r="G9" s="65" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="33">
@@ -5077,9 +5079,9 @@
         <f>Inputs!D131</f>
         <v/>
       </c>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="64" t="n"/>
-      <c r="G10" s="64" t="n"/>
+      <c r="E10" s="65" t="n"/>
+      <c r="F10" s="65" t="n"/>
+      <c r="G10" s="65" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="33">
@@ -5098,9 +5100,9 @@
         <f>Inputs!D132</f>
         <v/>
       </c>
-      <c r="E11" s="64" t="n"/>
-      <c r="F11" s="64" t="n"/>
-      <c r="G11" s="64" t="n"/>
+      <c r="E11" s="65" t="n"/>
+      <c r="F11" s="65" t="n"/>
+      <c r="G11" s="65" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="33">
@@ -5119,9 +5121,9 @@
         <f>Inputs!D133</f>
         <v/>
       </c>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="64" t="n"/>
-      <c r="G12" s="64" t="n"/>
+      <c r="E12" s="65" t="n"/>
+      <c r="F12" s="65" t="n"/>
+      <c r="G12" s="65" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="33">
@@ -5140,9 +5142,9 @@
         <f>Inputs!D134</f>
         <v/>
       </c>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="64" t="n"/>
-      <c r="G13" s="64" t="n"/>
+      <c r="E13" s="65" t="n"/>
+      <c r="F13" s="65" t="n"/>
+      <c r="G13" s="65" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="33">
@@ -5161,9 +5163,9 @@
         <f>Inputs!D135</f>
         <v/>
       </c>
-      <c r="E14" s="64" t="n"/>
-      <c r="F14" s="64" t="n"/>
-      <c r="G14" s="64" t="n"/>
+      <c r="E14" s="65" t="n"/>
+      <c r="F14" s="65" t="n"/>
+      <c r="G14" s="65" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="33">
@@ -5182,9 +5184,9 @@
         <f>Inputs!D136</f>
         <v/>
       </c>
-      <c r="E15" s="64" t="n"/>
-      <c r="F15" s="64" t="n"/>
-      <c r="G15" s="64" t="n"/>
+      <c r="E15" s="65" t="n"/>
+      <c r="F15" s="65" t="n"/>
+      <c r="G15" s="65" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="33">
@@ -5203,9 +5205,9 @@
         <f>Inputs!D137</f>
         <v/>
       </c>
-      <c r="E16" s="64" t="n"/>
-      <c r="F16" s="64" t="n"/>
-      <c r="G16" s="64" t="n"/>
+      <c r="E16" s="65" t="n"/>
+      <c r="F16" s="65" t="n"/>
+      <c r="G16" s="65" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="33">
@@ -5224,9 +5226,9 @@
         <f>Inputs!D138</f>
         <v/>
       </c>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="64" t="n"/>
-      <c r="G17" s="64" t="n"/>
+      <c r="E17" s="65" t="n"/>
+      <c r="F17" s="65" t="n"/>
+      <c r="G17" s="65" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="33">
@@ -5245,9 +5247,9 @@
         <f>Inputs!D139</f>
         <v/>
       </c>
-      <c r="E18" s="64" t="n"/>
-      <c r="F18" s="64" t="n"/>
-      <c r="G18" s="64" t="n"/>
+      <c r="E18" s="65" t="n"/>
+      <c r="F18" s="65" t="n"/>
+      <c r="G18" s="65" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="33">
@@ -5266,9 +5268,9 @@
         <f>Inputs!D140</f>
         <v/>
       </c>
-      <c r="E19" s="64" t="n"/>
-      <c r="F19" s="64" t="n"/>
-      <c r="G19" s="64" t="n"/>
+      <c r="E19" s="65" t="n"/>
+      <c r="F19" s="65" t="n"/>
+      <c r="G19" s="65" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="33">
@@ -5287,9 +5289,9 @@
         <f>Inputs!D141</f>
         <v/>
       </c>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="64" t="n"/>
-      <c r="G20" s="64" t="n"/>
+      <c r="E20" s="65" t="n"/>
+      <c r="F20" s="65" t="n"/>
+      <c r="G20" s="65" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="33">
@@ -5308,9 +5310,9 @@
         <f>Inputs!D142</f>
         <v/>
       </c>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="64" t="n"/>
-      <c r="G21" s="64" t="n"/>
+      <c r="E21" s="65" t="n"/>
+      <c r="F21" s="65" t="n"/>
+      <c r="G21" s="65" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="33">
@@ -5329,9 +5331,9 @@
         <f>Inputs!D143</f>
         <v/>
       </c>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="64" t="n"/>
-      <c r="G22" s="64" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="65" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="33">
@@ -5350,9 +5352,9 @@
         <f>Inputs!D144</f>
         <v/>
       </c>
-      <c r="E23" s="64" t="n"/>
-      <c r="F23" s="64" t="n"/>
-      <c r="G23" s="64" t="n"/>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="65" t="n"/>
+      <c r="G23" s="65" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="33">
@@ -5371,9 +5373,9 @@
         <f>Inputs!D145</f>
         <v/>
       </c>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="64" t="n"/>
-      <c r="G24" s="64" t="n"/>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="65" t="n"/>
+      <c r="G24" s="65" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="33">
@@ -5392,9 +5394,9 @@
         <f>Inputs!D146</f>
         <v/>
       </c>
-      <c r="E25" s="64" t="n"/>
-      <c r="F25" s="64" t="n"/>
-      <c r="G25" s="64" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="65" t="n"/>
+      <c r="G25" s="65" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="33">
@@ -5413,9 +5415,9 @@
         <f>Inputs!D147</f>
         <v/>
       </c>
-      <c r="E26" s="64" t="n"/>
-      <c r="F26" s="64" t="n"/>
-      <c r="G26" s="64" t="n"/>
+      <c r="E26" s="65" t="n"/>
+      <c r="F26" s="65" t="n"/>
+      <c r="G26" s="65" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="33">
@@ -5434,9 +5436,9 @@
         <f>Inputs!D148</f>
         <v/>
       </c>
-      <c r="E27" s="64" t="n"/>
-      <c r="F27" s="64" t="n"/>
-      <c r="G27" s="64" t="n"/>
+      <c r="E27" s="65" t="n"/>
+      <c r="F27" s="65" t="n"/>
+      <c r="G27" s="65" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="33">
@@ -5455,9 +5457,9 @@
         <f>Inputs!D149</f>
         <v/>
       </c>
-      <c r="E28" s="64" t="n"/>
-      <c r="F28" s="64" t="n"/>
-      <c r="G28" s="64" t="n"/>
+      <c r="E28" s="65" t="n"/>
+      <c r="F28" s="65" t="n"/>
+      <c r="G28" s="65" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="33">
@@ -5476,9 +5478,9 @@
         <f>Inputs!D150</f>
         <v/>
       </c>
-      <c r="E29" s="64" t="n"/>
-      <c r="F29" s="64" t="n"/>
-      <c r="G29" s="64" t="n"/>
+      <c r="E29" s="65" t="n"/>
+      <c r="F29" s="65" t="n"/>
+      <c r="G29" s="65" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="33">
@@ -5497,9 +5499,9 @@
         <f>Inputs!D151</f>
         <v/>
       </c>
-      <c r="E30" s="64" t="n"/>
-      <c r="F30" s="64" t="n"/>
-      <c r="G30" s="64" t="n"/>
+      <c r="E30" s="65" t="n"/>
+      <c r="F30" s="65" t="n"/>
+      <c r="G30" s="65" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="33">
@@ -5518,9 +5520,9 @@
         <f>Inputs!D152</f>
         <v/>
       </c>
-      <c r="E31" s="64" t="n"/>
-      <c r="F31" s="64" t="n"/>
-      <c r="G31" s="64" t="n"/>
+      <c r="E31" s="65" t="n"/>
+      <c r="F31" s="65" t="n"/>
+      <c r="G31" s="65" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="33">
@@ -5539,9 +5541,9 @@
         <f>Inputs!D153</f>
         <v/>
       </c>
-      <c r="E32" s="64" t="n"/>
-      <c r="F32" s="64" t="n"/>
-      <c r="G32" s="64" t="n"/>
+      <c r="E32" s="65" t="n"/>
+      <c r="F32" s="65" t="n"/>
+      <c r="G32" s="65" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="33">
@@ -5560,9 +5562,9 @@
         <f>Inputs!D154</f>
         <v/>
       </c>
-      <c r="E33" s="64" t="n"/>
-      <c r="F33" s="64" t="n"/>
-      <c r="G33" s="64" t="n"/>
+      <c r="E33" s="65" t="n"/>
+      <c r="F33" s="65" t="n"/>
+      <c r="G33" s="65" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="33">
@@ -5581,9 +5583,9 @@
         <f>Inputs!D155</f>
         <v/>
       </c>
-      <c r="E34" s="64" t="n"/>
-      <c r="F34" s="64" t="n"/>
-      <c r="G34" s="64" t="n"/>
+      <c r="E34" s="65" t="n"/>
+      <c r="F34" s="65" t="n"/>
+      <c r="G34" s="65" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="33">
@@ -5602,9 +5604,9 @@
         <f>Inputs!D156</f>
         <v/>
       </c>
-      <c r="E35" s="64" t="n"/>
-      <c r="F35" s="64" t="n"/>
-      <c r="G35" s="64" t="n"/>
+      <c r="E35" s="65" t="n"/>
+      <c r="F35" s="65" t="n"/>
+      <c r="G35" s="65" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="44" t="inlineStr">
@@ -5612,15 +5614,15 @@
           <t>Maximum</t>
         </is>
       </c>
-      <c r="E37" s="65">
+      <c r="E37" s="66">
         <f>IFERROR(MAX(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F37" s="65">
+      <c r="F37" s="66">
         <f>IFERROR(MAX(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G37" s="65">
+      <c r="G37" s="66">
         <f>IFERROR(MAX(G6:G35),"n/a")</f>
         <v/>
       </c>
@@ -5631,15 +5633,15 @@
           <t>Q3 (75%)</t>
         </is>
       </c>
-      <c r="E38" s="65">
+      <c r="E38" s="66">
         <f>IFERROR(QUARTILE(E6:E35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="F38" s="65">
+      <c r="F38" s="66">
         <f>IFERROR(QUARTILE(F6:F35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="G38" s="65">
+      <c r="G38" s="66">
         <f>IFERROR(QUARTILE(G6:G35,3),"n/a")</f>
         <v/>
       </c>
@@ -5650,15 +5652,15 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="E39" s="66">
+      <c r="E39" s="67">
         <f>IFERROR(MEDIAN(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F39" s="66">
+      <c r="F39" s="67">
         <f>IFERROR(MEDIAN(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G39" s="66">
+      <c r="G39" s="67">
         <f>IFERROR(MEDIAN(G6:G35),"n/a")</f>
         <v/>
       </c>
@@ -5669,15 +5671,15 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="E40" s="65">
+      <c r="E40" s="66">
         <f>IFERROR(AVERAGE(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F40" s="65">
+      <c r="F40" s="66">
         <f>IFERROR(AVERAGE(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G40" s="65">
+      <c r="G40" s="66">
         <f>IFERROR(AVERAGE(G6:G35),"n/a")</f>
         <v/>
       </c>
@@ -5688,15 +5690,15 @@
           <t>Q1 (25%)</t>
         </is>
       </c>
-      <c r="E41" s="65">
+      <c r="E41" s="66">
         <f>IFERROR(QUARTILE(E6:E35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="F41" s="65">
+      <c r="F41" s="66">
         <f>IFERROR(QUARTILE(F6:F35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="G41" s="65">
+      <c r="G41" s="66">
         <f>IFERROR(QUARTILE(G6:G35,1),"n/a")</f>
         <v/>
       </c>
@@ -5707,15 +5709,15 @@
           <t>Minimum</t>
         </is>
       </c>
-      <c r="E42" s="65">
+      <c r="E42" s="66">
         <f>IFERROR(MIN(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F42" s="65">
+      <c r="F42" s="66">
         <f>IFERROR(MIN(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G42" s="65">
+      <c r="G42" s="66">
         <f>IFERROR(MIN(G6:G35),"n/a")</f>
         <v/>
       </c>
@@ -5885,10 +5887,10 @@
         <f>Inputs!D127</f>
         <v/>
       </c>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="n"/>
-      <c r="G6" s="57" t="n"/>
-      <c r="H6" s="57" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="n"/>
+      <c r="G6" s="58" t="n"/>
+      <c r="H6" s="58" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="33">
@@ -5907,10 +5909,10 @@
         <f>Inputs!D128</f>
         <v/>
       </c>
-      <c r="E7" s="64" t="n"/>
-      <c r="F7" s="64" t="n"/>
-      <c r="G7" s="57" t="n"/>
-      <c r="H7" s="57" t="n"/>
+      <c r="E7" s="65" t="n"/>
+      <c r="F7" s="65" t="n"/>
+      <c r="G7" s="58" t="n"/>
+      <c r="H7" s="58" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="33">
@@ -5929,10 +5931,10 @@
         <f>Inputs!D129</f>
         <v/>
       </c>
-      <c r="E8" s="64" t="n"/>
-      <c r="F8" s="64" t="n"/>
-      <c r="G8" s="57" t="n"/>
-      <c r="H8" s="57" t="n"/>
+      <c r="E8" s="65" t="n"/>
+      <c r="F8" s="65" t="n"/>
+      <c r="G8" s="58" t="n"/>
+      <c r="H8" s="58" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="33">
@@ -5951,10 +5953,10 @@
         <f>Inputs!D130</f>
         <v/>
       </c>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="64" t="n"/>
-      <c r="G9" s="57" t="n"/>
-      <c r="H9" s="57" t="n"/>
+      <c r="E9" s="65" t="n"/>
+      <c r="F9" s="65" t="n"/>
+      <c r="G9" s="58" t="n"/>
+      <c r="H9" s="58" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="33">
@@ -5973,10 +5975,10 @@
         <f>Inputs!D131</f>
         <v/>
       </c>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="64" t="n"/>
-      <c r="G10" s="57" t="n"/>
-      <c r="H10" s="57" t="n"/>
+      <c r="E10" s="65" t="n"/>
+      <c r="F10" s="65" t="n"/>
+      <c r="G10" s="58" t="n"/>
+      <c r="H10" s="58" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="33">
@@ -5995,10 +5997,10 @@
         <f>Inputs!D132</f>
         <v/>
       </c>
-      <c r="E11" s="64" t="n"/>
-      <c r="F11" s="64" t="n"/>
-      <c r="G11" s="57" t="n"/>
-      <c r="H11" s="57" t="n"/>
+      <c r="E11" s="65" t="n"/>
+      <c r="F11" s="65" t="n"/>
+      <c r="G11" s="58" t="n"/>
+      <c r="H11" s="58" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="33">
@@ -6017,10 +6019,10 @@
         <f>Inputs!D133</f>
         <v/>
       </c>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="64" t="n"/>
-      <c r="G12" s="57" t="n"/>
-      <c r="H12" s="57" t="n"/>
+      <c r="E12" s="65" t="n"/>
+      <c r="F12" s="65" t="n"/>
+      <c r="G12" s="58" t="n"/>
+      <c r="H12" s="58" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="33">
@@ -6039,10 +6041,10 @@
         <f>Inputs!D134</f>
         <v/>
       </c>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="64" t="n"/>
-      <c r="G13" s="57" t="n"/>
-      <c r="H13" s="57" t="n"/>
+      <c r="E13" s="65" t="n"/>
+      <c r="F13" s="65" t="n"/>
+      <c r="G13" s="58" t="n"/>
+      <c r="H13" s="58" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="33">
@@ -6061,10 +6063,10 @@
         <f>Inputs!D135</f>
         <v/>
       </c>
-      <c r="E14" s="64" t="n"/>
-      <c r="F14" s="64" t="n"/>
-      <c r="G14" s="57" t="n"/>
-      <c r="H14" s="57" t="n"/>
+      <c r="E14" s="65" t="n"/>
+      <c r="F14" s="65" t="n"/>
+      <c r="G14" s="58" t="n"/>
+      <c r="H14" s="58" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="33">
@@ -6083,10 +6085,10 @@
         <f>Inputs!D136</f>
         <v/>
       </c>
-      <c r="E15" s="64" t="n"/>
-      <c r="F15" s="64" t="n"/>
-      <c r="G15" s="57" t="n"/>
-      <c r="H15" s="57" t="n"/>
+      <c r="E15" s="65" t="n"/>
+      <c r="F15" s="65" t="n"/>
+      <c r="G15" s="58" t="n"/>
+      <c r="H15" s="58" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="33">
@@ -6105,10 +6107,10 @@
         <f>Inputs!D137</f>
         <v/>
       </c>
-      <c r="E16" s="64" t="n"/>
-      <c r="F16" s="64" t="n"/>
-      <c r="G16" s="57" t="n"/>
-      <c r="H16" s="57" t="n"/>
+      <c r="E16" s="65" t="n"/>
+      <c r="F16" s="65" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="58" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="33">
@@ -6127,10 +6129,10 @@
         <f>Inputs!D138</f>
         <v/>
       </c>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="64" t="n"/>
-      <c r="G17" s="57" t="n"/>
-      <c r="H17" s="57" t="n"/>
+      <c r="E17" s="65" t="n"/>
+      <c r="F17" s="65" t="n"/>
+      <c r="G17" s="58" t="n"/>
+      <c r="H17" s="58" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="33">
@@ -6149,10 +6151,10 @@
         <f>Inputs!D139</f>
         <v/>
       </c>
-      <c r="E18" s="64" t="n"/>
-      <c r="F18" s="64" t="n"/>
-      <c r="G18" s="57" t="n"/>
-      <c r="H18" s="57" t="n"/>
+      <c r="E18" s="65" t="n"/>
+      <c r="F18" s="65" t="n"/>
+      <c r="G18" s="58" t="n"/>
+      <c r="H18" s="58" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="33">
@@ -6171,10 +6173,10 @@
         <f>Inputs!D140</f>
         <v/>
       </c>
-      <c r="E19" s="64" t="n"/>
-      <c r="F19" s="64" t="n"/>
-      <c r="G19" s="57" t="n"/>
-      <c r="H19" s="57" t="n"/>
+      <c r="E19" s="65" t="n"/>
+      <c r="F19" s="65" t="n"/>
+      <c r="G19" s="58" t="n"/>
+      <c r="H19" s="58" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="33">
@@ -6193,10 +6195,10 @@
         <f>Inputs!D141</f>
         <v/>
       </c>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="64" t="n"/>
-      <c r="G20" s="57" t="n"/>
-      <c r="H20" s="57" t="n"/>
+      <c r="E20" s="65" t="n"/>
+      <c r="F20" s="65" t="n"/>
+      <c r="G20" s="58" t="n"/>
+      <c r="H20" s="58" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="33">
@@ -6215,10 +6217,10 @@
         <f>Inputs!D142</f>
         <v/>
       </c>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="64" t="n"/>
-      <c r="G21" s="57" t="n"/>
-      <c r="H21" s="57" t="n"/>
+      <c r="E21" s="65" t="n"/>
+      <c r="F21" s="65" t="n"/>
+      <c r="G21" s="58" t="n"/>
+      <c r="H21" s="58" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="33">
@@ -6237,10 +6239,10 @@
         <f>Inputs!D143</f>
         <v/>
       </c>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="64" t="n"/>
-      <c r="G22" s="57" t="n"/>
-      <c r="H22" s="57" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="58" t="n"/>
+      <c r="H22" s="58" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="33">
@@ -6259,10 +6261,10 @@
         <f>Inputs!D144</f>
         <v/>
       </c>
-      <c r="E23" s="64" t="n"/>
-      <c r="F23" s="64" t="n"/>
-      <c r="G23" s="57" t="n"/>
-      <c r="H23" s="57" t="n"/>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="65" t="n"/>
+      <c r="G23" s="58" t="n"/>
+      <c r="H23" s="58" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="33">
@@ -6281,10 +6283,10 @@
         <f>Inputs!D145</f>
         <v/>
       </c>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="64" t="n"/>
-      <c r="G24" s="57" t="n"/>
-      <c r="H24" s="57" t="n"/>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="65" t="n"/>
+      <c r="G24" s="58" t="n"/>
+      <c r="H24" s="58" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="33">
@@ -6303,10 +6305,10 @@
         <f>Inputs!D146</f>
         <v/>
       </c>
-      <c r="E25" s="64" t="n"/>
-      <c r="F25" s="64" t="n"/>
-      <c r="G25" s="57" t="n"/>
-      <c r="H25" s="57" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="65" t="n"/>
+      <c r="G25" s="58" t="n"/>
+      <c r="H25" s="58" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="33">
@@ -6325,10 +6327,10 @@
         <f>Inputs!D147</f>
         <v/>
       </c>
-      <c r="E26" s="64" t="n"/>
-      <c r="F26" s="64" t="n"/>
-      <c r="G26" s="57" t="n"/>
-      <c r="H26" s="57" t="n"/>
+      <c r="E26" s="65" t="n"/>
+      <c r="F26" s="65" t="n"/>
+      <c r="G26" s="58" t="n"/>
+      <c r="H26" s="58" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="33">
@@ -6347,10 +6349,10 @@
         <f>Inputs!D148</f>
         <v/>
       </c>
-      <c r="E27" s="64" t="n"/>
-      <c r="F27" s="64" t="n"/>
-      <c r="G27" s="57" t="n"/>
-      <c r="H27" s="57" t="n"/>
+      <c r="E27" s="65" t="n"/>
+      <c r="F27" s="65" t="n"/>
+      <c r="G27" s="58" t="n"/>
+      <c r="H27" s="58" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="33">
@@ -6369,10 +6371,10 @@
         <f>Inputs!D149</f>
         <v/>
       </c>
-      <c r="E28" s="64" t="n"/>
-      <c r="F28" s="64" t="n"/>
-      <c r="G28" s="57" t="n"/>
-      <c r="H28" s="57" t="n"/>
+      <c r="E28" s="65" t="n"/>
+      <c r="F28" s="65" t="n"/>
+      <c r="G28" s="58" t="n"/>
+      <c r="H28" s="58" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="33">
@@ -6391,10 +6393,10 @@
         <f>Inputs!D150</f>
         <v/>
       </c>
-      <c r="E29" s="64" t="n"/>
-      <c r="F29" s="64" t="n"/>
-      <c r="G29" s="57" t="n"/>
-      <c r="H29" s="57" t="n"/>
+      <c r="E29" s="65" t="n"/>
+      <c r="F29" s="65" t="n"/>
+      <c r="G29" s="58" t="n"/>
+      <c r="H29" s="58" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="33">
@@ -6413,10 +6415,10 @@
         <f>Inputs!D151</f>
         <v/>
       </c>
-      <c r="E30" s="64" t="n"/>
-      <c r="F30" s="64" t="n"/>
-      <c r="G30" s="57" t="n"/>
-      <c r="H30" s="57" t="n"/>
+      <c r="E30" s="65" t="n"/>
+      <c r="F30" s="65" t="n"/>
+      <c r="G30" s="58" t="n"/>
+      <c r="H30" s="58" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="33">
@@ -6435,10 +6437,10 @@
         <f>Inputs!D152</f>
         <v/>
       </c>
-      <c r="E31" s="64" t="n"/>
-      <c r="F31" s="64" t="n"/>
-      <c r="G31" s="57" t="n"/>
-      <c r="H31" s="57" t="n"/>
+      <c r="E31" s="65" t="n"/>
+      <c r="F31" s="65" t="n"/>
+      <c r="G31" s="58" t="n"/>
+      <c r="H31" s="58" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="33">
@@ -6457,10 +6459,10 @@
         <f>Inputs!D153</f>
         <v/>
       </c>
-      <c r="E32" s="64" t="n"/>
-      <c r="F32" s="64" t="n"/>
-      <c r="G32" s="57" t="n"/>
-      <c r="H32" s="57" t="n"/>
+      <c r="E32" s="65" t="n"/>
+      <c r="F32" s="65" t="n"/>
+      <c r="G32" s="58" t="n"/>
+      <c r="H32" s="58" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="33">
@@ -6479,10 +6481,10 @@
         <f>Inputs!D154</f>
         <v/>
       </c>
-      <c r="E33" s="64" t="n"/>
-      <c r="F33" s="64" t="n"/>
-      <c r="G33" s="57" t="n"/>
-      <c r="H33" s="57" t="n"/>
+      <c r="E33" s="65" t="n"/>
+      <c r="F33" s="65" t="n"/>
+      <c r="G33" s="58" t="n"/>
+      <c r="H33" s="58" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="33">
@@ -6501,10 +6503,10 @@
         <f>Inputs!D155</f>
         <v/>
       </c>
-      <c r="E34" s="64" t="n"/>
-      <c r="F34" s="64" t="n"/>
-      <c r="G34" s="57" t="n"/>
-      <c r="H34" s="57" t="n"/>
+      <c r="E34" s="65" t="n"/>
+      <c r="F34" s="65" t="n"/>
+      <c r="G34" s="58" t="n"/>
+      <c r="H34" s="58" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="33">
@@ -6523,10 +6525,10 @@
         <f>Inputs!D156</f>
         <v/>
       </c>
-      <c r="E35" s="64" t="n"/>
-      <c r="F35" s="64" t="n"/>
-      <c r="G35" s="57" t="n"/>
-      <c r="H35" s="57" t="n"/>
+      <c r="E35" s="65" t="n"/>
+      <c r="F35" s="65" t="n"/>
+      <c r="G35" s="58" t="n"/>
+      <c r="H35" s="58" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="44" t="inlineStr">
@@ -6534,19 +6536,19 @@
           <t>Maximum</t>
         </is>
       </c>
-      <c r="E37" s="65">
+      <c r="E37" s="66">
         <f>IFERROR(MAX(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F37" s="65">
+      <c r="F37" s="66">
         <f>IFERROR(MAX(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G37" s="59">
+      <c r="G37" s="60">
         <f>IFERROR(MAX(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H37" s="59">
+      <c r="H37" s="60">
         <f>IFERROR(MAX(H6:H35),"n/a")</f>
         <v/>
       </c>
@@ -6557,19 +6559,19 @@
           <t>Q3 (75%)</t>
         </is>
       </c>
-      <c r="E38" s="65">
+      <c r="E38" s="66">
         <f>IFERROR(QUARTILE(E6:E35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="F38" s="65">
+      <c r="F38" s="66">
         <f>IFERROR(QUARTILE(F6:F35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="G38" s="59">
+      <c r="G38" s="60">
         <f>IFERROR(QUARTILE(G6:G35,3),"n/a")</f>
         <v/>
       </c>
-      <c r="H38" s="59">
+      <c r="H38" s="60">
         <f>IFERROR(QUARTILE(H6:H35,3),"n/a")</f>
         <v/>
       </c>
@@ -6580,19 +6582,19 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="E39" s="66">
+      <c r="E39" s="67">
         <f>IFERROR(MEDIAN(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F39" s="66">
+      <c r="F39" s="67">
         <f>IFERROR(MEDIAN(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G39" s="61">
+      <c r="G39" s="62">
         <f>IFERROR(MEDIAN(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H39" s="61">
+      <c r="H39" s="62">
         <f>IFERROR(MEDIAN(H6:H35),"n/a")</f>
         <v/>
       </c>
@@ -6603,19 +6605,19 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="E40" s="65">
+      <c r="E40" s="66">
         <f>IFERROR(AVERAGE(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F40" s="65">
+      <c r="F40" s="66">
         <f>IFERROR(AVERAGE(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G40" s="59">
+      <c r="G40" s="60">
         <f>IFERROR(AVERAGE(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H40" s="59">
+      <c r="H40" s="60">
         <f>IFERROR(AVERAGE(H6:H35),"n/a")</f>
         <v/>
       </c>
@@ -6626,19 +6628,19 @@
           <t>Q1 (25%)</t>
         </is>
       </c>
-      <c r="E41" s="65">
+      <c r="E41" s="66">
         <f>IFERROR(QUARTILE(E6:E35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="F41" s="65">
+      <c r="F41" s="66">
         <f>IFERROR(QUARTILE(F6:F35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="G41" s="59">
+      <c r="G41" s="60">
         <f>IFERROR(QUARTILE(G6:G35,1),"n/a")</f>
         <v/>
       </c>
-      <c r="H41" s="59">
+      <c r="H41" s="60">
         <f>IFERROR(QUARTILE(H6:H35,1),"n/a")</f>
         <v/>
       </c>
@@ -6649,19 +6651,19 @@
           <t>Minimum</t>
         </is>
       </c>
-      <c r="E42" s="65">
+      <c r="E42" s="66">
         <f>IFERROR(MIN(E6:E35),"n/a")</f>
         <v/>
       </c>
-      <c r="F42" s="65">
+      <c r="F42" s="66">
         <f>IFERROR(MIN(F6:F35),"n/a")</f>
         <v/>
       </c>
-      <c r="G42" s="59">
+      <c r="G42" s="60">
         <f>IFERROR(MIN(G6:G35),"n/a")</f>
         <v/>
       </c>
-      <c r="H42" s="59">
+      <c r="H42" s="60">
         <f>IFERROR(MIN(H6:H35),"n/a")</f>
         <v/>
       </c>
@@ -6785,7 +6787,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>TODO — formulas to be added in subsequent build pass.</t>
         </is>
@@ -6886,13 +6888,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D5" s="55" t="n">
+      <c r="D5" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E5" s="55" t="n">
+      <c r="E5" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="55" t="n">
+      <c r="F5" s="56" t="n">
         <v>0.21</v>
       </c>
       <c r="G5" s="33" t="inlineStr">
@@ -6917,13 +6919,13 @@
           <t>Aa3</t>
         </is>
       </c>
-      <c r="D6" s="55" t="n">
+      <c r="D6" s="56" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E6" s="55" t="n">
+      <c r="E6" s="56" t="n">
         <v>0.005</v>
       </c>
-      <c r="F6" s="55" t="n">
+      <c r="F6" s="56" t="n">
         <v>0.25</v>
       </c>
       <c r="G6" s="33" t="inlineStr">
@@ -6948,13 +6950,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D7" s="55" t="n">
+      <c r="D7" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="56" t="n">
         <v>0.298</v>
       </c>
       <c r="G7" s="33" t="inlineStr">
@@ -6979,13 +6981,13 @@
           <t>Aa3</t>
         </is>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="56" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E8" s="55" t="n">
+      <c r="E8" s="56" t="n">
         <v>0.005</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="56" t="n">
         <v>0.258</v>
       </c>
       <c r="G8" s="33" t="inlineStr">
@@ -7010,13 +7012,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D9" s="55" t="n">
+      <c r="D9" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E9" s="55" t="n">
+      <c r="E9" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="56" t="n">
         <v>0.144</v>
       </c>
       <c r="G9" s="33" t="inlineStr">
@@ -7041,13 +7043,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D10" s="55" t="n">
+      <c r="D10" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E10" s="55" t="n">
+      <c r="E10" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="56" t="n">
         <v>0.258</v>
       </c>
       <c r="G10" s="33" t="inlineStr">
@@ -7072,13 +7074,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D11" s="55" t="n">
+      <c r="D11" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E11" s="55" t="n">
+      <c r="E11" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="56" t="n">
         <v>0.3</v>
       </c>
       <c r="G11" s="33" t="inlineStr">
@@ -7103,13 +7105,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D12" s="55" t="n">
+      <c r="D12" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E12" s="55" t="n">
+      <c r="E12" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="56" t="n">
         <v>0.28</v>
       </c>
       <c r="G12" s="33" t="inlineStr">
@@ -7134,13 +7136,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D13" s="55" t="n">
+      <c r="D13" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E13" s="55" t="n">
+      <c r="E13" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="56" t="n">
         <v>0.265</v>
       </c>
       <c r="G13" s="33" t="inlineStr">
@@ -7165,13 +7167,13 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="D14" s="55" t="n">
+      <c r="D14" s="56" t="n">
         <v>0.0567</v>
       </c>
-      <c r="E14" s="55" t="n">
+      <c r="E14" s="56" t="n">
         <v>0.011</v>
       </c>
-      <c r="F14" s="55" t="n">
+      <c r="F14" s="56" t="n">
         <v>0.305</v>
       </c>
       <c r="G14" s="33" t="inlineStr">
@@ -7196,13 +7198,13 @@
           <t>Aa2</t>
         </is>
       </c>
-      <c r="D15" s="55" t="n">
+      <c r="D15" s="56" t="n">
         <v>0.0489</v>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="56" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="56" t="n">
         <v>0.275</v>
       </c>
       <c r="G15" s="33" t="inlineStr">
@@ -7227,13 +7229,13 @@
           <t>Aa3</t>
         </is>
       </c>
-      <c r="D16" s="55" t="n">
+      <c r="D16" s="56" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="56" t="n">
         <v>0.005</v>
       </c>
-      <c r="F16" s="55" t="n">
+      <c r="F16" s="56" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" s="33" t="inlineStr">
@@ -7258,13 +7260,13 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="D17" s="55" t="n">
+      <c r="D17" s="56" t="n">
         <v>0.0567</v>
       </c>
-      <c r="E17" s="55" t="n">
+      <c r="E17" s="56" t="n">
         <v>0.011</v>
       </c>
-      <c r="F17" s="55" t="n">
+      <c r="F17" s="56" t="n">
         <v>0.25</v>
       </c>
       <c r="G17" s="33" t="inlineStr">
@@ -7289,13 +7291,13 @@
           <t>Aa3</t>
         </is>
       </c>
-      <c r="D18" s="55" t="n">
+      <c r="D18" s="56" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E18" s="55" t="n">
+      <c r="E18" s="56" t="n">
         <v>0.005</v>
       </c>
-      <c r="F18" s="55" t="n">
+      <c r="F18" s="56" t="n">
         <v>0.165</v>
       </c>
       <c r="G18" s="33" t="inlineStr">
@@ -7320,13 +7322,13 @@
           <t>Aaa</t>
         </is>
       </c>
-      <c r="D19" s="55" t="n">
+      <c r="D19" s="56" t="n">
         <v>0.0457</v>
       </c>
-      <c r="E19" s="55" t="n">
+      <c r="E19" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="55" t="n">
+      <c r="F19" s="56" t="n">
         <v>0.17</v>
       </c>
       <c r="G19" s="33" t="inlineStr">
@@ -7351,13 +7353,13 @@
           <t>A3</t>
         </is>
       </c>
-      <c r="D20" s="55" t="n">
+      <c r="D20" s="56" t="n">
         <v>0.0623</v>
       </c>
-      <c r="E20" s="55" t="n">
+      <c r="E20" s="56" t="n">
         <v>0.0166</v>
       </c>
-      <c r="F20" s="55" t="n">
+      <c r="F20" s="56" t="n">
         <v>0.24</v>
       </c>
       <c r="G20" s="33" t="inlineStr">
@@ -7382,13 +7384,13 @@
           <t>Baa1</t>
         </is>
       </c>
-      <c r="D21" s="55" t="n">
+      <c r="D21" s="56" t="n">
         <v>0.06909999999999999</v>
       </c>
-      <c r="E21" s="55" t="n">
+      <c r="E21" s="56" t="n">
         <v>0.0234</v>
       </c>
-      <c r="F21" s="55" t="n">
+      <c r="F21" s="56" t="n">
         <v>0.2</v>
       </c>
       <c r="G21" s="33" t="inlineStr">
@@ -7413,13 +7415,13 @@
           <t>Ba2</t>
         </is>
       </c>
-      <c r="D22" s="55" t="n">
+      <c r="D22" s="56" t="n">
         <v>0.08550000000000001</v>
       </c>
-      <c r="E22" s="55" t="n">
+      <c r="E22" s="56" t="n">
         <v>0.0398</v>
       </c>
-      <c r="F22" s="55" t="n">
+      <c r="F22" s="56" t="n">
         <v>0.2</v>
       </c>
       <c r="G22" s="33" t="inlineStr">
@@ -7444,13 +7446,13 @@
           <t>Baa2</t>
         </is>
       </c>
-      <c r="D23" s="55" t="n">
+      <c r="D23" s="56" t="n">
         <v>0.0735</v>
       </c>
-      <c r="E23" s="55" t="n">
+      <c r="E23" s="56" t="n">
         <v>0.0278</v>
       </c>
-      <c r="F23" s="55" t="n">
+      <c r="F23" s="56" t="n">
         <v>0.22</v>
       </c>
       <c r="G23" s="33" t="inlineStr">
@@ -7475,13 +7477,13 @@
           <t>Baa2</t>
         </is>
       </c>
-      <c r="D24" s="55" t="n">
+      <c r="D24" s="56" t="n">
         <v>0.0735</v>
       </c>
-      <c r="E24" s="55" t="n">
+      <c r="E24" s="56" t="n">
         <v>0.0278</v>
       </c>
-      <c r="F24" s="55" t="n">
+      <c r="F24" s="56" t="n">
         <v>0.25</v>
       </c>
       <c r="G24" s="33" t="inlineStr">
@@ -7506,13 +7508,13 @@
           <t>Baa3</t>
         </is>
       </c>
-      <c r="D25" s="55" t="n">
+      <c r="D25" s="56" t="n">
         <v>0.0786</v>
       </c>
-      <c r="E25" s="55" t="n">
+      <c r="E25" s="56" t="n">
         <v>0.0329</v>
       </c>
-      <c r="F25" s="55" t="n">
+      <c r="F25" s="56" t="n">
         <v>0.252</v>
       </c>
       <c r="G25" s="33" t="inlineStr">
@@ -7537,13 +7539,13 @@
           <t>Caa2</t>
         </is>
       </c>
-      <c r="D26" s="55" t="n">
+      <c r="D26" s="56" t="n">
         <v>0.1421</v>
       </c>
-      <c r="E26" s="55" t="n">
+      <c r="E26" s="56" t="n">
         <v>0.0964</v>
       </c>
-      <c r="F26" s="55" t="n">
+      <c r="F26" s="56" t="n">
         <v>0.29</v>
       </c>
       <c r="G26" s="33" t="inlineStr">
@@ -7568,13 +7570,13 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="D27" s="55" t="n">
+      <c r="D27" s="56" t="n">
         <v>0.1142</v>
       </c>
-      <c r="E27" s="55" t="n">
+      <c r="E27" s="56" t="n">
         <v>0.06850000000000001</v>
       </c>
-      <c r="F27" s="55" t="n">
+      <c r="F27" s="56" t="n">
         <v>0.275</v>
       </c>
       <c r="G27" s="33" t="inlineStr">
@@ -7599,13 +7601,13 @@
           <t>Aa3</t>
         </is>
       </c>
-      <c r="D28" s="55" t="n">
+      <c r="D28" s="56" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E28" s="55" t="n">
+      <c r="E28" s="56" t="n">
         <v>0.005</v>
       </c>
-      <c r="F28" s="55" t="n">
+      <c r="F28" s="56" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="33" t="inlineStr">
@@ -7630,13 +7632,13 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="D29" s="55" t="n">
+      <c r="D29" s="56" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E29" s="55" t="n">
+      <c r="E29" s="56" t="n">
         <v>0.005</v>
       </c>
-      <c r="F29" s="55" t="n">
+      <c r="F29" s="56" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="33" t="inlineStr">
@@ -7661,13 +7663,13 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="D30" s="55" t="n">
+      <c r="D30" s="56" t="n">
         <v>0.0596</v>
       </c>
-      <c r="E30" s="55" t="n">
+      <c r="E30" s="56" t="n">
         <v>0.0139</v>
       </c>
-      <c r="F30" s="55" t="n">
+      <c r="F30" s="56" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="33" t="inlineStr">
@@ -7692,13 +7694,13 @@
           <t>Ba2</t>
         </is>
       </c>
-      <c r="D31" s="55" t="n">
+      <c r="D31" s="56" t="n">
         <v>0.08550000000000001</v>
       </c>
-      <c r="E31" s="55" t="n">
+      <c r="E31" s="56" t="n">
         <v>0.0398</v>
       </c>
-      <c r="F31" s="55" t="n">
+      <c r="F31" s="56" t="n">
         <v>0.34</v>
       </c>
       <c r="G31" s="33" t="inlineStr">
@@ -7723,13 +7725,13 @@
           <t>Baa2</t>
         </is>
       </c>
-      <c r="D32" s="55" t="n">
+      <c r="D32" s="56" t="n">
         <v>0.0735</v>
       </c>
-      <c r="E32" s="55" t="n">
+      <c r="E32" s="56" t="n">
         <v>0.0278</v>
       </c>
-      <c r="F32" s="55" t="n">
+      <c r="F32" s="56" t="n">
         <v>0.3</v>
       </c>
       <c r="G32" s="33" t="inlineStr">
@@ -7754,13 +7756,13 @@
           <t>Aa2</t>
         </is>
       </c>
-      <c r="D33" s="55" t="n">
+      <c r="D33" s="56" t="n">
         <v>0.0489</v>
       </c>
-      <c r="E33" s="55" t="n">
+      <c r="E33" s="56" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F33" s="55" t="n">
+      <c r="F33" s="56" t="n">
         <v>0.09</v>
       </c>
       <c r="G33" s="33" t="inlineStr">
@@ -7785,13 +7787,13 @@
           <t>Aa3</t>
         </is>
       </c>
-      <c r="D34" s="55" t="n">
+      <c r="D34" s="56" t="n">
         <v>0.0507</v>
       </c>
-      <c r="E34" s="55" t="n">
+      <c r="E34" s="56" t="n">
         <v>0.005</v>
       </c>
-      <c r="F34" s="55" t="n">
+      <c r="F34" s="56" t="n">
         <v>0.2</v>
       </c>
       <c r="G34" s="33" t="inlineStr">
@@ -7816,13 +7818,13 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="D35" s="55" t="n">
+      <c r="D35" s="56" t="n">
         <v>0.0596</v>
       </c>
-      <c r="E35" s="55" t="n">
+      <c r="E35" s="56" t="n">
         <v>0.0139</v>
       </c>
-      <c r="F35" s="55" t="n">
+      <c r="F35" s="56" t="n">
         <v>0.23</v>
       </c>
       <c r="G35" s="33" t="inlineStr">
@@ -10764,42 +10766,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" s="69" t="inlineStr">
         <is>
           <t>WACC ↓ / g →</t>
         </is>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="70">
         <f>terminal_growth_rate+(-3)*sens_terminal_g_step</f>
         <v/>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="70">
         <f>terminal_growth_rate+(-2)*sens_terminal_g_step</f>
         <v/>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="70">
         <f>terminal_growth_rate+(-1)*sens_terminal_g_step</f>
         <v/>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="70">
         <f>terminal_growth_rate+(0)*sens_terminal_g_step</f>
         <v/>
       </c>
-      <c r="G6" s="69">
+      <c r="G6" s="70">
         <f>terminal_growth_rate+(1)*sens_terminal_g_step</f>
         <v/>
       </c>
-      <c r="H6" s="69">
+      <c r="H6" s="70">
         <f>terminal_growth_rate+(2)*sens_terminal_g_step</f>
         <v/>
       </c>
-      <c r="I6" s="69">
+      <c r="I6" s="70">
         <f>terminal_growth_rate+(3)*sens_terminal_g_step</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="69">
+      <c r="B7" s="70">
         <f>wacc_per_mgmt+(-3)*sens_wacc_step</f>
         <v/>
       </c>
@@ -10833,7 +10835,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="69">
+      <c r="B8" s="70">
         <f>wacc_per_mgmt+(-2)*sens_wacc_step</f>
         <v/>
       </c>
@@ -10867,7 +10869,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="69">
+      <c r="B9" s="70">
         <f>wacc_per_mgmt+(-1)*sens_wacc_step</f>
         <v/>
       </c>
@@ -10901,7 +10903,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="69">
+      <c r="B10" s="70">
         <f>wacc_per_mgmt+(0)*sens_wacc_step</f>
         <v/>
       </c>
@@ -10917,7 +10919,7 @@
         <f>IFERROR(Projections!D40/(1+$B$10)^1+Projections!E40/(1+$B$10)^2+Projections!F40/(1+$B$10)^3+Projections!G40/(1+$B$10)^4+Projections!H40/(1+$B$10)^5+Projections!H40*(1+E$6)/($B$10-E$6)/(1+$B$10)^5,"err")</f>
         <v/>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="71">
         <f>IFERROR(Projections!D40/(1+$B$10)^1+Projections!E40/(1+$B$10)^2+Projections!F40/(1+$B$10)^3+Projections!G40/(1+$B$10)^4+Projections!H40/(1+$B$10)^5+Projections!H40*(1+F$6)/($B$10-F$6)/(1+$B$10)^5,"err")</f>
         <v/>
       </c>
@@ -10935,7 +10937,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="69">
+      <c r="B11" s="70">
         <f>wacc_per_mgmt+(1)*sens_wacc_step</f>
         <v/>
       </c>
@@ -10969,7 +10971,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="69">
+      <c r="B12" s="70">
         <f>wacc_per_mgmt+(2)*sens_wacc_step</f>
         <v/>
       </c>
@@ -11003,7 +11005,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="69">
+      <c r="B13" s="70">
         <f>wacc_per_mgmt+(3)*sens_wacc_step</f>
         <v/>
       </c>
@@ -11273,7 +11275,7 @@
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>NTM medians × target metrics.</t>
+          <t>Cross-check vs DCF (±10% band).</t>
         </is>
       </c>
     </row>
@@ -11305,14 +11307,14 @@
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>Mean EV/EBITDA × Y1 EBITDA.</t>
+          <t>Cross-check vs DCF (±10% band).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Weighted-average EV</t>
+          <t>Concluded EV (DCF primary)</t>
         </is>
       </c>
       <c r="G17" s="24">
@@ -12028,15 +12030,15 @@
           <t>actual currency</t>
         </is>
       </c>
-      <c r="C16" s="71">
+      <c r="C16" s="72">
         <f>IFERROR(Adjustments!C20*C14/C15,0)</f>
         <v/>
       </c>
-      <c r="D16" s="71">
+      <c r="D16" s="72">
         <f>IFERROR(Adjustments!D20*D14/D15,0)</f>
         <v/>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="72">
         <f>AVERAGE(C16:D16)</f>
         <v/>
       </c>
@@ -12073,15 +12075,15 @@
           <t>actual currency</t>
         </is>
       </c>
-      <c r="C18" s="72">
+      <c r="C18" s="73">
         <f>IFERROR(Adjustments!C20*C14/C17,0)</f>
         <v/>
       </c>
-      <c r="D18" s="72">
+      <c r="D18" s="73">
         <f>IFERROR(Adjustments!D20*D14/D17,0)</f>
         <v/>
       </c>
-      <c r="E18" s="72">
+      <c r="E18" s="73">
         <f>AVERAGE(C18:D18)</f>
         <v/>
       </c>
@@ -12104,15 +12106,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" s="55">
+      <c r="C21" s="56">
         <f>wacc_per_mgmt</f>
         <v/>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="56">
         <f>wacc_indep</f>
         <v/>
       </c>
-      <c r="E21" s="55" t="n"/>
+      <c r="E21" s="56" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -12125,15 +12127,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="56">
         <f>terminal_growth_rate</f>
         <v/>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="56">
         <f>terminal_growth_rate</f>
         <v/>
       </c>
-      <c r="E22" s="55" t="n"/>
+      <c r="E22" s="56" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12157,42 +12159,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>report_purpose</t>
         </is>
       </c>
-      <c r="B1" s="73" t="inlineStr">
+      <c r="B1" s="74" t="inlineStr">
         <is>
           <t>accounting_standard</t>
         </is>
       </c>
-      <c r="C1" s="73" t="inlineStr">
+      <c r="C1" s="74" t="inlineStr">
         <is>
           <t>tax_type</t>
         </is>
       </c>
-      <c r="D1" s="73" t="inlineStr">
+      <c r="D1" s="74" t="inlineStr">
         <is>
           <t>terminal_method</t>
         </is>
       </c>
-      <c r="E1" s="73" t="inlineStr">
+      <c r="E1" s="74" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F1" s="73" t="inlineStr">
+      <c r="F1" s="74" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="G1" s="73" t="inlineStr">
+      <c r="G1" s="74" t="inlineStr">
         <is>
           <t>coco_tier</t>
         </is>
       </c>
-      <c r="H1" s="73" t="inlineStr">
+      <c r="H1" s="74" t="inlineStr">
         <is>
           <t>revenue_growth_method</t>
         </is>
@@ -12399,7 +12401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:U197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -14087,49 +14089,53 @@
       <c r="G84" s="33" t="n"/>
       <c r="H84" s="33" t="n"/>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
+          <t>terminal_nominal_gdp_growth</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Nominal GDP growth (reference ceiling)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="n"/>
+      <c r="E85" s="32" t="n"/>
+      <c r="F85" s="33" t="n"/>
+      <c r="G85" s="33" t="n"/>
+      <c r="H85" s="34" t="inlineStr">
+        <is>
+          <t>Long-run nominal GDP of the operating jurisdiction; terminal g at/above GDP − 50bps is flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Section F — WACC inputs  (Core)</t>
         </is>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="31" t="inlineStr">
-        <is>
-          <t>risk_free_rate</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D87" s="32" t="n"/>
-      <c r="E87" s="32" t="n"/>
-      <c r="F87" s="33" t="n"/>
-      <c r="G87" s="33" t="n"/>
-      <c r="H87" s="33" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="31" t="inlineStr">
         <is>
-          <t>risk_free_rate_source</t>
+          <t>risk_free_rate</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Risk-free rate source descriptor</t>
+          <t>Risk-free rate</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D88" s="32" t="n"/>
@@ -14141,17 +14147,17 @@
     <row r="89">
       <c r="A89" s="31" t="inlineStr">
         <is>
-          <t>equity_risk_premium</t>
+          <t>risk_free_rate_source</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Equity risk premium (ERP)</t>
+          <t>Risk-free rate source descriptor</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D89" s="32" t="n"/>
@@ -14163,12 +14169,12 @@
     <row r="90">
       <c r="A90" s="31" t="inlineStr">
         <is>
-          <t>country_risk_premium</t>
+          <t>equity_risk_premium</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Country risk premium</t>
+          <t>Equity risk premium (ERP)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -14185,17 +14191,17 @@
     <row r="91">
       <c r="A91" s="31" t="inlineStr">
         <is>
-          <t>unlevered_beta</t>
+          <t>country_risk_premium</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Unlevered beta</t>
+          <t>Country risk premium</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D91" s="32" t="n"/>
@@ -14207,17 +14213,17 @@
     <row r="92">
       <c r="A92" s="31" t="inlineStr">
         <is>
-          <t>target_debt_to_equity</t>
+          <t>unlevered_beta</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Target D/E ratio</t>
+          <t>Unlevered beta</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D92" s="32" t="n"/>
@@ -14229,27 +14235,21 @@
     <row r="93">
       <c r="A93" s="31" t="inlineStr">
         <is>
-          <t>levered_beta</t>
+          <t>target_debt_to_equity</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Levered beta (calculated)</t>
+          <t>Target D/E ratio</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D93" s="35">
-        <f>WACC!E10</f>
-        <v/>
-      </c>
-      <c r="E93" s="35">
-        <f>WACC!F10</f>
-        <v/>
-      </c>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="n"/>
+      <c r="E93" s="32" t="n"/>
       <c r="F93" s="33" t="n"/>
       <c r="G93" s="33" t="n"/>
       <c r="H93" s="33" t="n"/>
@@ -14257,21 +14257,27 @@
     <row r="94">
       <c r="A94" s="31" t="inlineStr">
         <is>
-          <t>size_premium</t>
+          <t>levered_beta</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Size premium</t>
+          <t>Levered beta (calculated)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D94" s="32" t="n"/>
-      <c r="E94" s="32" t="n"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D94" s="35">
+        <f>WACC!E10</f>
+        <v/>
+      </c>
+      <c r="E94" s="35">
+        <f>WACC!F10</f>
+        <v/>
+      </c>
       <c r="F94" s="33" t="n"/>
       <c r="G94" s="33" t="n"/>
       <c r="H94" s="33" t="n"/>
@@ -14279,12 +14285,12 @@
     <row r="95">
       <c r="A95" s="31" t="inlineStr">
         <is>
-          <t>specific_risk_premium</t>
+          <t>size_premium</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Specific risk premium</t>
+          <t>Size premium</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -14301,12 +14307,12 @@
     <row r="96">
       <c r="A96" s="31" t="inlineStr">
         <is>
-          <t>cost_of_equity</t>
+          <t>specific_risk_premium</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Cost of equity (calculated)</t>
+          <t>Specific risk premium</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -14314,14 +14320,8 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D96" s="36">
-        <f>WACC!E16</f>
-        <v/>
-      </c>
-      <c r="E96" s="36">
-        <f>WACC!F16</f>
-        <v/>
-      </c>
+      <c r="D96" s="32" t="n"/>
+      <c r="E96" s="32" t="n"/>
       <c r="F96" s="33" t="n"/>
       <c r="G96" s="33" t="n"/>
       <c r="H96" s="33" t="n"/>
@@ -14329,12 +14329,12 @@
     <row r="97">
       <c r="A97" s="31" t="inlineStr">
         <is>
-          <t>pretax_cost_of_debt</t>
+          <t>cost_of_equity</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt</t>
+          <t>Cost of equity (calculated)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -14342,8 +14342,14 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D97" s="32" t="n"/>
-      <c r="E97" s="32" t="n"/>
+      <c r="D97" s="36">
+        <f>WACC!E16</f>
+        <v/>
+      </c>
+      <c r="E97" s="36">
+        <f>WACC!F16</f>
+        <v/>
+      </c>
       <c r="F97" s="33" t="n"/>
       <c r="G97" s="33" t="n"/>
       <c r="H97" s="33" t="n"/>
@@ -14351,12 +14357,12 @@
     <row r="98">
       <c r="A98" s="31" t="inlineStr">
         <is>
-          <t>aftertax_cost_of_debt</t>
+          <t>pretax_cost_of_debt</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>After-tax cost of debt (calculated)</t>
+          <t>Pre-tax cost of debt</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14364,14 +14370,8 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D98" s="36">
-        <f>WACC!E20</f>
-        <v/>
-      </c>
-      <c r="E98" s="36">
-        <f>WACC!F20</f>
-        <v/>
-      </c>
+      <c r="D98" s="32" t="n"/>
+      <c r="E98" s="32" t="n"/>
       <c r="F98" s="33" t="n"/>
       <c r="G98" s="33" t="n"/>
       <c r="H98" s="33" t="n"/>
@@ -14379,12 +14379,12 @@
     <row r="99">
       <c r="A99" s="31" t="inlineStr">
         <is>
-          <t>target_debt_weight</t>
+          <t>aftertax_cost_of_debt</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>D/V (debt weight)</t>
+          <t>After-tax cost of debt (calculated)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14392,8 +14392,14 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D99" s="32" t="n"/>
-      <c r="E99" s="32" t="n"/>
+      <c r="D99" s="36">
+        <f>WACC!E20</f>
+        <v/>
+      </c>
+      <c r="E99" s="36">
+        <f>WACC!F20</f>
+        <v/>
+      </c>
       <c r="F99" s="33" t="n"/>
       <c r="G99" s="33" t="n"/>
       <c r="H99" s="33" t="n"/>
@@ -14401,12 +14407,12 @@
     <row r="100">
       <c r="A100" s="31" t="inlineStr">
         <is>
-          <t>target_equity_weight</t>
+          <t>target_debt_weight</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>E/V (equity weight)</t>
+          <t>D/V (debt weight)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -14423,12 +14429,12 @@
     <row r="101">
       <c r="A101" s="31" t="inlineStr">
         <is>
-          <t>wacc</t>
+          <t>target_equity_weight</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>WACC (calculated)</t>
+          <t>E/V (equity weight)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -14436,56 +14442,56 @@
           <t>percentage</t>
         </is>
       </c>
-      <c r="D101" s="36">
-        <f>WACC!E25</f>
-        <v/>
-      </c>
-      <c r="E101" s="36">
-        <f>WACC!F25</f>
-        <v/>
-      </c>
+      <c r="D101" s="32" t="n"/>
+      <c r="E101" s="32" t="n"/>
       <c r="F101" s="33" t="n"/>
       <c r="G101" s="33" t="n"/>
       <c r="H101" s="33" t="n"/>
     </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="31" t="inlineStr">
+        <is>
+          <t>wacc</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>WACC (calculated)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D102" s="36">
+        <f>WACC!E25</f>
+        <v/>
+      </c>
+      <c r="E102" s="36">
+        <f>WACC!F25</f>
+        <v/>
+      </c>
+      <c r="F102" s="33" t="n"/>
+      <c r="G102" s="33" t="n"/>
+      <c r="H102" s="33" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Section I — EV -&gt; Equity bridge  (Core)</t>
         </is>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="31" t="inlineStr">
-        <is>
-          <t>surplus_assets</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>Surplus / non-operating assets</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D104" s="32" t="n"/>
-      <c r="E104" s="32" t="n"/>
-      <c r="F104" s="33" t="n"/>
-      <c r="G104" s="33" t="n"/>
-      <c r="H104" s="33" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="31" t="inlineStr">
         <is>
-          <t>net_debt_override</t>
+          <t>surplus_assets</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Net debt (override)</t>
+          <t>Surplus / non-operating assets</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -14502,12 +14508,12 @@
     <row r="106">
       <c r="A106" s="31" t="inlineStr">
         <is>
-          <t>minority_interests</t>
+          <t>net_debt_override</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Minority interests</t>
+          <t>Net debt (override)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -14524,12 +14530,12 @@
     <row r="107">
       <c r="A107" s="31" t="inlineStr">
         <is>
-          <t>non_operating_assets</t>
+          <t>minority_interests</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Non-operating assets</t>
+          <t>Minority interests</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -14546,17 +14552,17 @@
     <row r="108">
       <c r="A108" s="31" t="inlineStr">
         <is>
-          <t>dlom_pct</t>
+          <t>non_operating_assets</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>DLOM rate</t>
+          <t>Non-operating assets</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D108" s="32" t="n"/>
@@ -14568,12 +14574,12 @@
     <row r="109">
       <c r="A109" s="31" t="inlineStr">
         <is>
-          <t>dloc_pct</t>
+          <t>dlom_pct</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>DLOC rate</t>
+          <t>DLOM rate</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -14590,12 +14596,12 @@
     <row r="110">
       <c r="A110" s="31" t="inlineStr">
         <is>
-          <t>equity_interest_pct</t>
+          <t>dloc_pct</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Client's % equity interest</t>
+          <t>DLOC rate</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -14612,17 +14618,17 @@
     <row r="111">
       <c r="A111" s="31" t="inlineStr">
         <is>
-          <t>shares_outstanding</t>
+          <t>equity_interest_pct</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Shares outstanding (basic)</t>
+          <t>Client's % equity interest</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D111" s="32" t="n"/>
@@ -14634,12 +14640,12 @@
     <row r="112">
       <c r="A112" s="31" t="inlineStr">
         <is>
-          <t>shares_outstanding_diluted</t>
+          <t>shares_outstanding</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Shares outstanding (diluted)</t>
+          <t>Shares outstanding (basic)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -14656,17 +14662,17 @@
     <row r="113">
       <c r="A113" s="31" t="inlineStr">
         <is>
-          <t>pre_money_pct</t>
+          <t>shares_outstanding_diluted</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Pre-money equity %</t>
+          <t>Shares outstanding (diluted)</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D113" s="32" t="n"/>
@@ -14675,49 +14681,49 @@
       <c r="G113" s="33" t="n"/>
       <c r="H113" s="33" t="n"/>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="37" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="31" t="inlineStr">
+        <is>
+          <t>pre_money_pct</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Pre-money equity %</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D114" s="32" t="n"/>
+      <c r="E114" s="32" t="n"/>
+      <c r="F114" s="33" t="n"/>
+      <c r="G114" s="33" t="n"/>
+      <c r="H114" s="33" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="37" t="inlineStr">
         <is>
           <t>Section J — Adjustment toggles  (Extended)</t>
         </is>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="31" t="inlineStr">
-        <is>
-          <t>capitalize_rd</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Capitalize R&amp;D?</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D116" s="32" t="n"/>
-      <c r="E116" s="32" t="n"/>
-      <c r="F116" s="33" t="n"/>
-      <c r="G116" s="33" t="n"/>
-      <c r="H116" s="33" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="31" t="inlineStr">
         <is>
-          <t>rd_amortization_years</t>
+          <t>capitalize_rd</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D amortization period (years)</t>
+          <t>Capitalize R&amp;D?</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D117" s="32" t="n"/>
@@ -14729,17 +14735,17 @@
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
         <is>
-          <t>convert_operating_leases</t>
+          <t>rd_amortization_years</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Convert operating leases to debt?</t>
+          <t>R&amp;D amortization period (years)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D118" s="32" t="n"/>
@@ -14751,17 +14757,17 @@
     <row r="119">
       <c r="A119" s="31" t="inlineStr">
         <is>
-          <t>lease_discount_rate</t>
+          <t>convert_operating_leases</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Lease discount rate</t>
+          <t>Convert operating leases to debt?</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D119" s="32" t="n"/>
@@ -14770,44 +14776,44 @@
       <c r="G119" s="33" t="n"/>
       <c r="H119" s="33" t="n"/>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="37" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="31" t="inlineStr">
+        <is>
+          <t>lease_discount_rate</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Lease discount rate</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D120" s="32" t="n"/>
+      <c r="E120" s="32" t="n"/>
+      <c r="F120" s="33" t="n"/>
+      <c r="G120" s="33" t="n"/>
+      <c r="H120" s="33" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="37" t="inlineStr">
         <is>
           <t>Section K — Football field weights  (Extended)</t>
         </is>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="31" t="inlineStr">
-        <is>
-          <t>weight_dcf</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>DCF weight</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D122" s="32" t="n"/>
-      <c r="E122" s="32" t="n"/>
-      <c r="F122" s="33" t="n"/>
-      <c r="G122" s="33" t="n"/>
-      <c r="H122" s="33" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="31" t="inlineStr">
         <is>
-          <t>weight_comps</t>
+          <t>weight_dcf</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Comparable companies weight</t>
+          <t>DCF weight</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -14824,12 +14830,12 @@
     <row r="124">
       <c r="A124" s="31" t="inlineStr">
         <is>
-          <t>weight_precedent</t>
+          <t>weight_comps</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Precedent transactions weight</t>
+          <t>Comparable companies weight</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -14846,12 +14852,12 @@
     <row r="125">
       <c r="A125" s="31" t="inlineStr">
         <is>
-          <t>weight_nav</t>
+          <t>weight_precedent</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>NAV / asset-based weight</t>
+          <t>Precedent transactions weight</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -14868,17 +14874,17 @@
     <row r="126">
       <c r="A126" s="31" t="inlineStr">
         <is>
-          <t>selected_low</t>
+          <t>weight_nav</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation low</t>
+          <t>NAV / asset-based weight</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D126" s="32" t="n"/>
@@ -14890,12 +14896,12 @@
     <row r="127">
       <c r="A127" s="31" t="inlineStr">
         <is>
-          <t>selected_mid</t>
+          <t>selected_low</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation mid</t>
+          <t>Selected valuation low</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14912,12 +14918,12 @@
     <row r="128">
       <c r="A128" s="31" t="inlineStr">
         <is>
-          <t>selected_high</t>
+          <t>selected_mid</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Selected valuation high</t>
+          <t>Selected valuation mid</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -14931,49 +14937,49 @@
       <c r="G128" s="33" t="n"/>
       <c r="H128" s="33" t="n"/>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="37" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="31" t="inlineStr">
+        <is>
+          <t>selected_high</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Selected valuation high</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D129" s="32" t="n"/>
+      <c r="E129" s="32" t="n"/>
+      <c r="F129" s="33" t="n"/>
+      <c r="G129" s="33" t="n"/>
+      <c r="H129" s="33" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="37" t="inlineStr">
         <is>
           <t>Section L — Sensitivity ranges  (Extended)</t>
         </is>
       </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="31" t="inlineStr">
-        <is>
-          <t>sens_wacc_step</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>WACC sensitivity step</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="D131" s="32" t="n"/>
-      <c r="E131" s="32" t="n"/>
-      <c r="F131" s="33" t="n"/>
-      <c r="G131" s="33" t="n"/>
-      <c r="H131" s="33" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="31" t="inlineStr">
         <is>
-          <t>sens_wacc_count</t>
+          <t>sens_wacc_step</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>WACC steps each side of base</t>
+          <t>WACC sensitivity step</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D132" s="32" t="n"/>
@@ -14985,17 +14991,17 @@
     <row r="133">
       <c r="A133" s="31" t="inlineStr">
         <is>
-          <t>sens_terminal_g_step</t>
+          <t>sens_wacc_count</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Terminal g sensitivity step</t>
+          <t>WACC steps each side of base</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D133" s="32" t="n"/>
@@ -15007,17 +15013,17 @@
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
         <is>
-          <t>sens_terminal_g_count</t>
+          <t>sens_terminal_g_step</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Terminal g steps each side</t>
+          <t>Terminal g sensitivity step</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="D134" s="32" t="n"/>
@@ -15029,17 +15035,17 @@
     <row r="135">
       <c r="A135" s="31" t="inlineStr">
         <is>
-          <t>sens_revenue_g_step</t>
+          <t>sens_terminal_g_count</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Revenue growth sens step</t>
+          <t>Terminal g steps each side</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D135" s="32" t="n"/>
@@ -15051,12 +15057,12 @@
     <row r="136">
       <c r="A136" s="31" t="inlineStr">
         <is>
-          <t>sens_ebitda_margin_step</t>
+          <t>sens_revenue_g_step</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>EBITDA margin sens step</t>
+          <t>Revenue growth sens step</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -15070,88 +15076,96 @@
       <c r="G136" s="33" t="n"/>
       <c r="H136" s="33" t="n"/>
     </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="31" t="inlineStr">
+        <is>
+          <t>sens_ebitda_margin_step</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA margin sens step</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="D137" s="32" t="n"/>
+      <c r="E137" s="32" t="n"/>
+      <c r="F137" s="33" t="n"/>
+      <c r="G137" s="33" t="n"/>
+      <c r="H137" s="33" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>Section G — Comparable companies table  (Core)</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="21" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="21" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B139" s="21" t="inlineStr">
+      <c r="B140" s="21" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="C139" s="21" t="inlineStr">
+      <c r="C140" s="21" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D139" s="21" t="inlineStr">
+      <c r="D140" s="21" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="E139" s="21" t="inlineStr">
+      <c r="E140" s="21" t="inlineStr">
         <is>
           <t>Business description</t>
         </is>
       </c>
-      <c r="F139" s="21" t="inlineStr">
+      <c r="F140" s="21" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="G139" s="21" t="inlineStr">
+      <c r="G140" s="21" t="inlineStr">
         <is>
           <t>Accounting standard</t>
         </is>
       </c>
-      <c r="H139" s="21" t="inlineStr">
+      <c r="H140" s="21" t="inlineStr">
         <is>
           <t>Market cap (USD mm)</t>
         </is>
       </c>
-      <c r="I139" s="21" t="inlineStr">
+      <c r="I140" s="21" t="inlineStr">
         <is>
           <t>D/E ratio</t>
         </is>
       </c>
-      <c r="J139" s="21" t="inlineStr">
+      <c r="J140" s="21" t="inlineStr">
         <is>
           <t>Raw levered beta</t>
         </is>
       </c>
-      <c r="K139" s="21" t="inlineStr">
+      <c r="K140" s="21" t="inlineStr">
         <is>
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="L139" s="21" t="inlineStr">
+      <c r="L140" s="21" t="inlineStr">
         <is>
           <t>Unlevered beta (calculated)</t>
         </is>
       </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="33" t="n"/>
-      <c r="B140" s="33" t="n"/>
-      <c r="C140" s="33" t="n"/>
-      <c r="D140" s="33" t="n"/>
-      <c r="E140" s="33" t="n"/>
-      <c r="F140" s="33" t="n"/>
-      <c r="G140" s="33" t="n"/>
-      <c r="H140" s="33" t="n"/>
-      <c r="I140" s="33" t="n"/>
-      <c r="J140" s="33" t="n"/>
-      <c r="K140" s="33" t="n"/>
-      <c r="L140" s="33" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="33" t="n"/>
@@ -15559,70 +15573,73 @@
       <c r="K169" s="33" t="n"/>
       <c r="L169" s="33" t="n"/>
     </row>
-    <row r="171">
-      <c r="A171" s="37" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="33" t="n"/>
+      <c r="B170" s="33" t="n"/>
+      <c r="C170" s="33" t="n"/>
+      <c r="D170" s="33" t="n"/>
+      <c r="E170" s="33" t="n"/>
+      <c r="F170" s="33" t="n"/>
+      <c r="G170" s="33" t="n"/>
+      <c r="H170" s="33" t="n"/>
+      <c r="I170" s="33" t="n"/>
+      <c r="J170" s="33" t="n"/>
+      <c r="K170" s="33" t="n"/>
+      <c r="L170" s="33" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="37" t="inlineStr">
         <is>
           <t>Section H — Precedent transactions  (Extended)</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="21" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="21" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="B172" s="21" t="inlineStr">
+      <c r="B173" s="21" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C172" s="21" t="inlineStr">
+      <c r="C173" s="21" t="inlineStr">
         <is>
           <t>Acquirer</t>
         </is>
       </c>
-      <c r="D172" s="21" t="inlineStr">
+      <c r="D173" s="21" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="E172" s="21" t="inlineStr">
+      <c r="E173" s="21" t="inlineStr">
         <is>
           <t>EV (USD mm)</t>
         </is>
       </c>
-      <c r="F172" s="21" t="inlineStr">
+      <c r="F173" s="21" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
-      <c r="G172" s="21" t="inlineStr">
+      <c r="G173" s="21" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="H172" s="21" t="inlineStr">
+      <c r="H173" s="21" t="inlineStr">
         <is>
           <t>Premium paid</t>
         </is>
       </c>
-      <c r="I172" s="21" t="inlineStr">
+      <c r="I173" s="21" t="inlineStr">
         <is>
           <t>Strategic rationale</t>
         </is>
       </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="33" t="n"/>
-      <c r="B173" s="33" t="n"/>
-      <c r="C173" s="33" t="n"/>
-      <c r="D173" s="33" t="n"/>
-      <c r="E173" s="33" t="n"/>
-      <c r="F173" s="33" t="n"/>
-      <c r="G173" s="33" t="n"/>
-      <c r="H173" s="33" t="n"/>
-      <c r="I173" s="33" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="33" t="n"/>
@@ -15778,101 +15795,137 @@
       <c r="H187" s="33" t="n"/>
       <c r="I187" s="33" t="n"/>
     </row>
-    <row r="189">
-      <c r="A189" s="37" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="33" t="n"/>
+      <c r="B188" s="33" t="n"/>
+      <c r="C188" s="33" t="n"/>
+      <c r="D188" s="33" t="n"/>
+      <c r="E188" s="33" t="n"/>
+      <c r="F188" s="33" t="n"/>
+      <c r="G188" s="33" t="n"/>
+      <c r="H188" s="33" t="n"/>
+      <c r="I188" s="33" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="37" t="inlineStr">
         <is>
           <t>Section I — Revenue segments  (Optional)</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>Optional segmented breakdown. Fill rows below + re-upload to override top-level revenue_growth / gross_margin with a segment aggregate. start_year=0 means the segment already exists in Y0; start_year&gt;0 introduces a new revenue line at that projection year.</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="21" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="21" t="inlineStr">
         <is>
           <t>Segment name</t>
         </is>
       </c>
-      <c r="B191" s="21" t="inlineStr">
+      <c r="B192" s="21" t="inlineStr">
         <is>
           <t>Start year</t>
         </is>
       </c>
-      <c r="C191" s="21" t="inlineStr">
+      <c r="C192" s="21" t="inlineStr">
         <is>
           <t>Initial revenue</t>
         </is>
       </c>
-      <c r="D191" s="21" t="inlineStr">
+      <c r="D192" s="21" t="inlineStr">
         <is>
           <t>Growth Y1</t>
         </is>
       </c>
-      <c r="E191" s="21" t="inlineStr">
+      <c r="E192" s="21" t="inlineStr">
         <is>
           <t>Growth Y2</t>
         </is>
       </c>
-      <c r="F191" s="21" t="inlineStr">
+      <c r="F192" s="21" t="inlineStr">
         <is>
           <t>Growth Y3</t>
         </is>
       </c>
-      <c r="G191" s="21" t="inlineStr">
+      <c r="G192" s="21" t="inlineStr">
         <is>
           <t>Growth Y4</t>
         </is>
       </c>
-      <c r="H191" s="21" t="inlineStr">
+      <c r="H192" s="21" t="inlineStr">
         <is>
           <t>Growth Y5</t>
         </is>
       </c>
-      <c r="I191" s="21" t="inlineStr">
+      <c r="I192" s="21" t="inlineStr">
         <is>
           <t>GM Y1</t>
         </is>
       </c>
-      <c r="J191" s="21" t="inlineStr">
+      <c r="J192" s="21" t="inlineStr">
         <is>
           <t>GM Y2</t>
         </is>
       </c>
-      <c r="K191" s="21" t="inlineStr">
+      <c r="K192" s="21" t="inlineStr">
         <is>
           <t>GM Y3</t>
         </is>
       </c>
-      <c r="L191" s="21" t="inlineStr">
+      <c r="L192" s="21" t="inlineStr">
         <is>
           <t>GM Y4</t>
         </is>
       </c>
-      <c r="M191" s="21" t="inlineStr">
+      <c r="M192" s="21" t="inlineStr">
         <is>
           <t>GM Y5</t>
         </is>
       </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="33" t="n"/>
-      <c r="B192" s="33" t="n"/>
-      <c r="C192" s="33" t="n"/>
-      <c r="D192" s="33" t="n"/>
-      <c r="E192" s="33" t="n"/>
-      <c r="F192" s="33" t="n"/>
-      <c r="G192" s="33" t="n"/>
-      <c r="H192" s="33" t="n"/>
-      <c r="I192" s="33" t="n"/>
-      <c r="J192" s="33" t="n"/>
-      <c r="K192" s="33" t="n"/>
-      <c r="L192" s="33" t="n"/>
-      <c r="M192" s="33" t="n"/>
+      <c r="N192" s="21" t="inlineStr">
+        <is>
+          <t>Opex% Y1</t>
+        </is>
+      </c>
+      <c r="O192" s="21" t="inlineStr">
+        <is>
+          <t>Opex% Y2</t>
+        </is>
+      </c>
+      <c r="P192" s="21" t="inlineStr">
+        <is>
+          <t>Opex% Y3</t>
+        </is>
+      </c>
+      <c r="Q192" s="21" t="inlineStr">
+        <is>
+          <t>Opex% Y4</t>
+        </is>
+      </c>
+      <c r="R192" s="21" t="inlineStr">
+        <is>
+          <t>Opex% Y5</t>
+        </is>
+      </c>
+      <c r="S192" s="21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T192" s="21" t="inlineStr">
+        <is>
+          <t>Growth basis</t>
+        </is>
+      </c>
+      <c r="U192" s="21" t="inlineStr">
+        <is>
+          <t>Contractual support</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="33" t="n"/>
@@ -15888,6 +15941,14 @@
       <c r="K193" s="33" t="n"/>
       <c r="L193" s="33" t="n"/>
       <c r="M193" s="33" t="n"/>
+      <c r="N193" s="33" t="n"/>
+      <c r="O193" s="33" t="n"/>
+      <c r="P193" s="33" t="n"/>
+      <c r="Q193" s="33" t="n"/>
+      <c r="R193" s="33" t="n"/>
+      <c r="S193" s="33" t="n"/>
+      <c r="T193" s="33" t="n"/>
+      <c r="U193" s="33" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="33" t="n"/>
@@ -15903,6 +15964,14 @@
       <c r="K194" s="33" t="n"/>
       <c r="L194" s="33" t="n"/>
       <c r="M194" s="33" t="n"/>
+      <c r="N194" s="33" t="n"/>
+      <c r="O194" s="33" t="n"/>
+      <c r="P194" s="33" t="n"/>
+      <c r="Q194" s="33" t="n"/>
+      <c r="R194" s="33" t="n"/>
+      <c r="S194" s="33" t="n"/>
+      <c r="T194" s="33" t="n"/>
+      <c r="U194" s="33" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="33" t="n"/>
@@ -15918,6 +15987,14 @@
       <c r="K195" s="33" t="n"/>
       <c r="L195" s="33" t="n"/>
       <c r="M195" s="33" t="n"/>
+      <c r="N195" s="33" t="n"/>
+      <c r="O195" s="33" t="n"/>
+      <c r="P195" s="33" t="n"/>
+      <c r="Q195" s="33" t="n"/>
+      <c r="R195" s="33" t="n"/>
+      <c r="S195" s="33" t="n"/>
+      <c r="T195" s="33" t="n"/>
+      <c r="U195" s="33" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="33" t="n"/>
@@ -15933,31 +16010,62 @@
       <c r="K196" s="33" t="n"/>
       <c r="L196" s="33" t="n"/>
       <c r="M196" s="33" t="n"/>
+      <c r="N196" s="33" t="n"/>
+      <c r="O196" s="33" t="n"/>
+      <c r="P196" s="33" t="n"/>
+      <c r="Q196" s="33" t="n"/>
+      <c r="R196" s="33" t="n"/>
+      <c r="S196" s="33" t="n"/>
+      <c r="T196" s="33" t="n"/>
+      <c r="U196" s="33" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="33" t="n"/>
+      <c r="B197" s="33" t="n"/>
+      <c r="C197" s="33" t="n"/>
+      <c r="D197" s="33" t="n"/>
+      <c r="E197" s="33" t="n"/>
+      <c r="F197" s="33" t="n"/>
+      <c r="G197" s="33" t="n"/>
+      <c r="H197" s="33" t="n"/>
+      <c r="I197" s="33" t="n"/>
+      <c r="J197" s="33" t="n"/>
+      <c r="K197" s="33" t="n"/>
+      <c r="L197" s="33" t="n"/>
+      <c r="M197" s="33" t="n"/>
+      <c r="N197" s="33" t="n"/>
+      <c r="O197" s="33" t="n"/>
+      <c r="P197" s="33" t="n"/>
+      <c r="Q197" s="33" t="n"/>
+      <c r="R197" s="33" t="n"/>
+      <c r="S197" s="33" t="n"/>
+      <c r="T197" s="33" t="n"/>
+      <c r="U197" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A131:H131"/>
     <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A189:M189"/>
+    <mergeCell ref="A191:M191"/>
+    <mergeCell ref="A139:H139"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="A87:H87"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A171:H171"/>
+    <mergeCell ref="A172:H172"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="A115:H115"/>
+    <mergeCell ref="A104:H104"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A138:H138"/>
+    <mergeCell ref="A116:H116"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A190:M190"/>
     <mergeCell ref="A6:H6"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F81 F82 F83 F84 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F116 F117 F118 F119 F122 F123 F124 F125 F126 F127 F128 F131 F132 F133 F134 F135 F136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F81 F82 F83 F84 F85 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F117 F118 F119 F120 F123 F124 F125 F126 F127 F128 F129 F132 F133 F134 F135 F136 F137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Audited FS,Management Projections,Capital IQ,Bloomberg,Damodaran,Kroll,Mercer,Prospectus,Engagement Letter,Calculated,Manual"</formula1>
     </dataValidation>
-    <dataValidation sqref="D116 D118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D117 D119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16732,7 +16840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -17106,23 +17214,23 @@
         <v/>
       </c>
       <c r="D18" s="41">
-        <f>-D12*opex_pct_revenue_y1</f>
+        <f>-(D12-D64)*opex_pct_revenue_y1+D65</f>
         <v/>
       </c>
       <c r="E18" s="41">
-        <f>-E12*opex_pct_revenue_y2</f>
+        <f>-(E12-E64)*opex_pct_revenue_y2+E65</f>
         <v/>
       </c>
       <c r="F18" s="41">
-        <f>-F12*opex_pct_revenue_y3</f>
+        <f>-(F12-F64)*opex_pct_revenue_y3+F65</f>
         <v/>
       </c>
       <c r="G18" s="41">
-        <f>-G12*opex_pct_revenue_y4</f>
+        <f>-(G12-G64)*opex_pct_revenue_y4+G65</f>
         <v/>
       </c>
       <c r="H18" s="41">
-        <f>-H12*opex_pct_revenue_y5</f>
+        <f>-(H12-H64)*opex_pct_revenue_y5+H65</f>
         <v/>
       </c>
     </row>
@@ -17696,12 +17804,508 @@
         <v/>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Revenue streams — per-segment breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Driven by the Inputs 'Revenue segments' table. Unused slots stay blank. 'Related opex' uses the stream's own Opex% when provided (carved out of the top-level opex base), otherwise an allocation at the top-level ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4">
+        <f>IF(INDEX(segments_table,1,1)="","(segment slot 1 — unused)","Revenue — "&amp;INDEX(segments_table,1,1))</f>
+        <v/>
+      </c>
+      <c r="C44" s="41">
+        <f>IF(INDEX(segments_table,1,1)="",0,IF(N(INDEX(segments_table,1,2))=0,N(INDEX(segments_table,1,3)),0))</f>
+        <v/>
+      </c>
+      <c r="D44" s="41">
+        <f>IF(INDEX(segments_table,1,1)="",0,IF(1&lt;N(INDEX(segments_table,1,2)),0,IF(1=N(INDEX(segments_table,1,2)),N(INDEX(segments_table,1,3)),C44*(1+N(INDEX(segments_table,1,3+(1-N(INDEX(segments_table,1,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="E44" s="41">
+        <f>IF(INDEX(segments_table,1,1)="",0,IF(2&lt;N(INDEX(segments_table,1,2)),0,IF(2=N(INDEX(segments_table,1,2)),N(INDEX(segments_table,1,3)),D44*(1+N(INDEX(segments_table,1,3+(2-N(INDEX(segments_table,1,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="F44" s="41">
+        <f>IF(INDEX(segments_table,1,1)="",0,IF(3&lt;N(INDEX(segments_table,1,2)),0,IF(3=N(INDEX(segments_table,1,2)),N(INDEX(segments_table,1,3)),E44*(1+N(INDEX(segments_table,1,3+(3-N(INDEX(segments_table,1,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="G44" s="41">
+        <f>IF(INDEX(segments_table,1,1)="",0,IF(4&lt;N(INDEX(segments_table,1,2)),0,IF(4=N(INDEX(segments_table,1,2)),N(INDEX(segments_table,1,3)),F44*(1+N(INDEX(segments_table,1,3+(4-N(INDEX(segments_table,1,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="H44" s="41">
+        <f>IF(INDEX(segments_table,1,1)="",0,IF(5&lt;N(INDEX(segments_table,1,2)),0,IF(5=N(INDEX(segments_table,1,2)),N(INDEX(segments_table,1,3)),G44*(1+N(INDEX(segments_table,1,3+(5-N(INDEX(segments_table,1,2)))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4">
+        <f>IF(INDEX(segments_table,1,1)="","","COGS — "&amp;INDEX(segments_table,1,1))</f>
+        <v/>
+      </c>
+      <c r="C45" s="41" t="n"/>
+      <c r="D45" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",-D44*(1-N(INDEX(segments_table,1,MIN(9+(1-N(INDEX(segments_table,1,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",-E44*(1-N(INDEX(segments_table,1,MIN(9+(2-N(INDEX(segments_table,1,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="F45" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",-F44*(1-N(INDEX(segments_table,1,MIN(9+(3-N(INDEX(segments_table,1,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="G45" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",-G44*(1-N(INDEX(segments_table,1,MIN(9+(4-N(INDEX(segments_table,1,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="H45" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",-H44*(1-N(INDEX(segments_table,1,MIN(9+(5-N(INDEX(segments_table,1,2))),13)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4">
+        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,1,1),"Related opex (allocated) — "&amp;INDEX(segments_table,1,1)))</f>
+        <v/>
+      </c>
+      <c r="C46" s="41" t="n"/>
+      <c r="D46" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,-D44*N(INDEX(segments_table,1,MIN(14+(1-N(INDEX(segments_table,1,2))),18))),-D44*opex_pct_revenue_y1))</f>
+        <v/>
+      </c>
+      <c r="E46" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,-E44*N(INDEX(segments_table,1,MIN(14+(2-N(INDEX(segments_table,1,2))),18))),-E44*opex_pct_revenue_y2))</f>
+        <v/>
+      </c>
+      <c r="F46" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,-F44*N(INDEX(segments_table,1,MIN(14+(3-N(INDEX(segments_table,1,2))),18))),-F44*opex_pct_revenue_y3))</f>
+        <v/>
+      </c>
+      <c r="G46" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,-G44*N(INDEX(segments_table,1,MIN(14+(4-N(INDEX(segments_table,1,2))),18))),-G44*opex_pct_revenue_y4))</f>
+        <v/>
+      </c>
+      <c r="H46" s="41">
+        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,-H44*N(INDEX(segments_table,1,MIN(14+(5-N(INDEX(segments_table,1,2))),18))),-H44*opex_pct_revenue_y5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4">
+        <f>IF(INDEX(segments_table,2,1)="","(segment slot 2 — unused)","Revenue — "&amp;INDEX(segments_table,2,1))</f>
+        <v/>
+      </c>
+      <c r="C48" s="41">
+        <f>IF(INDEX(segments_table,2,1)="",0,IF(N(INDEX(segments_table,2,2))=0,N(INDEX(segments_table,2,3)),0))</f>
+        <v/>
+      </c>
+      <c r="D48" s="41">
+        <f>IF(INDEX(segments_table,2,1)="",0,IF(1&lt;N(INDEX(segments_table,2,2)),0,IF(1=N(INDEX(segments_table,2,2)),N(INDEX(segments_table,2,3)),C48*(1+N(INDEX(segments_table,2,3+(1-N(INDEX(segments_table,2,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="E48" s="41">
+        <f>IF(INDEX(segments_table,2,1)="",0,IF(2&lt;N(INDEX(segments_table,2,2)),0,IF(2=N(INDEX(segments_table,2,2)),N(INDEX(segments_table,2,3)),D48*(1+N(INDEX(segments_table,2,3+(2-N(INDEX(segments_table,2,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="F48" s="41">
+        <f>IF(INDEX(segments_table,2,1)="",0,IF(3&lt;N(INDEX(segments_table,2,2)),0,IF(3=N(INDEX(segments_table,2,2)),N(INDEX(segments_table,2,3)),E48*(1+N(INDEX(segments_table,2,3+(3-N(INDEX(segments_table,2,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="G48" s="41">
+        <f>IF(INDEX(segments_table,2,1)="",0,IF(4&lt;N(INDEX(segments_table,2,2)),0,IF(4=N(INDEX(segments_table,2,2)),N(INDEX(segments_table,2,3)),F48*(1+N(INDEX(segments_table,2,3+(4-N(INDEX(segments_table,2,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="H48" s="41">
+        <f>IF(INDEX(segments_table,2,1)="",0,IF(5&lt;N(INDEX(segments_table,2,2)),0,IF(5=N(INDEX(segments_table,2,2)),N(INDEX(segments_table,2,3)),G48*(1+N(INDEX(segments_table,2,3+(5-N(INDEX(segments_table,2,2)))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4">
+        <f>IF(INDEX(segments_table,2,1)="","","COGS — "&amp;INDEX(segments_table,2,1))</f>
+        <v/>
+      </c>
+      <c r="C49" s="41" t="n"/>
+      <c r="D49" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",-D48*(1-N(INDEX(segments_table,2,MIN(9+(1-N(INDEX(segments_table,2,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="E49" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",-E48*(1-N(INDEX(segments_table,2,MIN(9+(2-N(INDEX(segments_table,2,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="F49" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",-F48*(1-N(INDEX(segments_table,2,MIN(9+(3-N(INDEX(segments_table,2,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="G49" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",-G48*(1-N(INDEX(segments_table,2,MIN(9+(4-N(INDEX(segments_table,2,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="H49" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",-H48*(1-N(INDEX(segments_table,2,MIN(9+(5-N(INDEX(segments_table,2,2))),13)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4">
+        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,2,1),"Related opex (allocated) — "&amp;INDEX(segments_table,2,1)))</f>
+        <v/>
+      </c>
+      <c r="C50" s="41" t="n"/>
+      <c r="D50" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,-D48*N(INDEX(segments_table,2,MIN(14+(1-N(INDEX(segments_table,2,2))),18))),-D48*opex_pct_revenue_y1))</f>
+        <v/>
+      </c>
+      <c r="E50" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,-E48*N(INDEX(segments_table,2,MIN(14+(2-N(INDEX(segments_table,2,2))),18))),-E48*opex_pct_revenue_y2))</f>
+        <v/>
+      </c>
+      <c r="F50" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,-F48*N(INDEX(segments_table,2,MIN(14+(3-N(INDEX(segments_table,2,2))),18))),-F48*opex_pct_revenue_y3))</f>
+        <v/>
+      </c>
+      <c r="G50" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,-G48*N(INDEX(segments_table,2,MIN(14+(4-N(INDEX(segments_table,2,2))),18))),-G48*opex_pct_revenue_y4))</f>
+        <v/>
+      </c>
+      <c r="H50" s="41">
+        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,-H48*N(INDEX(segments_table,2,MIN(14+(5-N(INDEX(segments_table,2,2))),18))),-H48*opex_pct_revenue_y5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4">
+        <f>IF(INDEX(segments_table,3,1)="","(segment slot 3 — unused)","Revenue — "&amp;INDEX(segments_table,3,1))</f>
+        <v/>
+      </c>
+      <c r="C52" s="41">
+        <f>IF(INDEX(segments_table,3,1)="",0,IF(N(INDEX(segments_table,3,2))=0,N(INDEX(segments_table,3,3)),0))</f>
+        <v/>
+      </c>
+      <c r="D52" s="41">
+        <f>IF(INDEX(segments_table,3,1)="",0,IF(1&lt;N(INDEX(segments_table,3,2)),0,IF(1=N(INDEX(segments_table,3,2)),N(INDEX(segments_table,3,3)),C52*(1+N(INDEX(segments_table,3,3+(1-N(INDEX(segments_table,3,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="E52" s="41">
+        <f>IF(INDEX(segments_table,3,1)="",0,IF(2&lt;N(INDEX(segments_table,3,2)),0,IF(2=N(INDEX(segments_table,3,2)),N(INDEX(segments_table,3,3)),D52*(1+N(INDEX(segments_table,3,3+(2-N(INDEX(segments_table,3,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="F52" s="41">
+        <f>IF(INDEX(segments_table,3,1)="",0,IF(3&lt;N(INDEX(segments_table,3,2)),0,IF(3=N(INDEX(segments_table,3,2)),N(INDEX(segments_table,3,3)),E52*(1+N(INDEX(segments_table,3,3+(3-N(INDEX(segments_table,3,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="G52" s="41">
+        <f>IF(INDEX(segments_table,3,1)="",0,IF(4&lt;N(INDEX(segments_table,3,2)),0,IF(4=N(INDEX(segments_table,3,2)),N(INDEX(segments_table,3,3)),F52*(1+N(INDEX(segments_table,3,3+(4-N(INDEX(segments_table,3,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="H52" s="41">
+        <f>IF(INDEX(segments_table,3,1)="",0,IF(5&lt;N(INDEX(segments_table,3,2)),0,IF(5=N(INDEX(segments_table,3,2)),N(INDEX(segments_table,3,3)),G52*(1+N(INDEX(segments_table,3,3+(5-N(INDEX(segments_table,3,2)))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4">
+        <f>IF(INDEX(segments_table,3,1)="","","COGS — "&amp;INDEX(segments_table,3,1))</f>
+        <v/>
+      </c>
+      <c r="C53" s="41" t="n"/>
+      <c r="D53" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",-D52*(1-N(INDEX(segments_table,3,MIN(9+(1-N(INDEX(segments_table,3,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="E53" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",-E52*(1-N(INDEX(segments_table,3,MIN(9+(2-N(INDEX(segments_table,3,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="F53" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",-F52*(1-N(INDEX(segments_table,3,MIN(9+(3-N(INDEX(segments_table,3,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="G53" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",-G52*(1-N(INDEX(segments_table,3,MIN(9+(4-N(INDEX(segments_table,3,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="H53" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",-H52*(1-N(INDEX(segments_table,3,MIN(9+(5-N(INDEX(segments_table,3,2))),13)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4">
+        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,3,1),"Related opex (allocated) — "&amp;INDEX(segments_table,3,1)))</f>
+        <v/>
+      </c>
+      <c r="C54" s="41" t="n"/>
+      <c r="D54" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,-D52*N(INDEX(segments_table,3,MIN(14+(1-N(INDEX(segments_table,3,2))),18))),-D52*opex_pct_revenue_y1))</f>
+        <v/>
+      </c>
+      <c r="E54" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,-E52*N(INDEX(segments_table,3,MIN(14+(2-N(INDEX(segments_table,3,2))),18))),-E52*opex_pct_revenue_y2))</f>
+        <v/>
+      </c>
+      <c r="F54" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,-F52*N(INDEX(segments_table,3,MIN(14+(3-N(INDEX(segments_table,3,2))),18))),-F52*opex_pct_revenue_y3))</f>
+        <v/>
+      </c>
+      <c r="G54" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,-G52*N(INDEX(segments_table,3,MIN(14+(4-N(INDEX(segments_table,3,2))),18))),-G52*opex_pct_revenue_y4))</f>
+        <v/>
+      </c>
+      <c r="H54" s="41">
+        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,-H52*N(INDEX(segments_table,3,MIN(14+(5-N(INDEX(segments_table,3,2))),18))),-H52*opex_pct_revenue_y5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4">
+        <f>IF(INDEX(segments_table,4,1)="","(segment slot 4 — unused)","Revenue — "&amp;INDEX(segments_table,4,1))</f>
+        <v/>
+      </c>
+      <c r="C56" s="41">
+        <f>IF(INDEX(segments_table,4,1)="",0,IF(N(INDEX(segments_table,4,2))=0,N(INDEX(segments_table,4,3)),0))</f>
+        <v/>
+      </c>
+      <c r="D56" s="41">
+        <f>IF(INDEX(segments_table,4,1)="",0,IF(1&lt;N(INDEX(segments_table,4,2)),0,IF(1=N(INDEX(segments_table,4,2)),N(INDEX(segments_table,4,3)),C56*(1+N(INDEX(segments_table,4,3+(1-N(INDEX(segments_table,4,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="E56" s="41">
+        <f>IF(INDEX(segments_table,4,1)="",0,IF(2&lt;N(INDEX(segments_table,4,2)),0,IF(2=N(INDEX(segments_table,4,2)),N(INDEX(segments_table,4,3)),D56*(1+N(INDEX(segments_table,4,3+(2-N(INDEX(segments_table,4,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="F56" s="41">
+        <f>IF(INDEX(segments_table,4,1)="",0,IF(3&lt;N(INDEX(segments_table,4,2)),0,IF(3=N(INDEX(segments_table,4,2)),N(INDEX(segments_table,4,3)),E56*(1+N(INDEX(segments_table,4,3+(3-N(INDEX(segments_table,4,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="G56" s="41">
+        <f>IF(INDEX(segments_table,4,1)="",0,IF(4&lt;N(INDEX(segments_table,4,2)),0,IF(4=N(INDEX(segments_table,4,2)),N(INDEX(segments_table,4,3)),F56*(1+N(INDEX(segments_table,4,3+(4-N(INDEX(segments_table,4,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="H56" s="41">
+        <f>IF(INDEX(segments_table,4,1)="",0,IF(5&lt;N(INDEX(segments_table,4,2)),0,IF(5=N(INDEX(segments_table,4,2)),N(INDEX(segments_table,4,3)),G56*(1+N(INDEX(segments_table,4,3+(5-N(INDEX(segments_table,4,2)))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4">
+        <f>IF(INDEX(segments_table,4,1)="","","COGS — "&amp;INDEX(segments_table,4,1))</f>
+        <v/>
+      </c>
+      <c r="C57" s="41" t="n"/>
+      <c r="D57" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",-D56*(1-N(INDEX(segments_table,4,MIN(9+(1-N(INDEX(segments_table,4,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="E57" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",-E56*(1-N(INDEX(segments_table,4,MIN(9+(2-N(INDEX(segments_table,4,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="F57" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",-F56*(1-N(INDEX(segments_table,4,MIN(9+(3-N(INDEX(segments_table,4,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="G57" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",-G56*(1-N(INDEX(segments_table,4,MIN(9+(4-N(INDEX(segments_table,4,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="H57" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",-H56*(1-N(INDEX(segments_table,4,MIN(9+(5-N(INDEX(segments_table,4,2))),13)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4">
+        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,4,1),"Related opex (allocated) — "&amp;INDEX(segments_table,4,1)))</f>
+        <v/>
+      </c>
+      <c r="C58" s="41" t="n"/>
+      <c r="D58" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,-D56*N(INDEX(segments_table,4,MIN(14+(1-N(INDEX(segments_table,4,2))),18))),-D56*opex_pct_revenue_y1))</f>
+        <v/>
+      </c>
+      <c r="E58" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,-E56*N(INDEX(segments_table,4,MIN(14+(2-N(INDEX(segments_table,4,2))),18))),-E56*opex_pct_revenue_y2))</f>
+        <v/>
+      </c>
+      <c r="F58" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,-F56*N(INDEX(segments_table,4,MIN(14+(3-N(INDEX(segments_table,4,2))),18))),-F56*opex_pct_revenue_y3))</f>
+        <v/>
+      </c>
+      <c r="G58" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,-G56*N(INDEX(segments_table,4,MIN(14+(4-N(INDEX(segments_table,4,2))),18))),-G56*opex_pct_revenue_y4))</f>
+        <v/>
+      </c>
+      <c r="H58" s="41">
+        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,-H56*N(INDEX(segments_table,4,MIN(14+(5-N(INDEX(segments_table,4,2))),18))),-H56*opex_pct_revenue_y5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4">
+        <f>IF(INDEX(segments_table,5,1)="","(segment slot 5 — unused)","Revenue — "&amp;INDEX(segments_table,5,1))</f>
+        <v/>
+      </c>
+      <c r="C60" s="41">
+        <f>IF(INDEX(segments_table,5,1)="",0,IF(N(INDEX(segments_table,5,2))=0,N(INDEX(segments_table,5,3)),0))</f>
+        <v/>
+      </c>
+      <c r="D60" s="41">
+        <f>IF(INDEX(segments_table,5,1)="",0,IF(1&lt;N(INDEX(segments_table,5,2)),0,IF(1=N(INDEX(segments_table,5,2)),N(INDEX(segments_table,5,3)),C60*(1+N(INDEX(segments_table,5,3+(1-N(INDEX(segments_table,5,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="E60" s="41">
+        <f>IF(INDEX(segments_table,5,1)="",0,IF(2&lt;N(INDEX(segments_table,5,2)),0,IF(2=N(INDEX(segments_table,5,2)),N(INDEX(segments_table,5,3)),D60*(1+N(INDEX(segments_table,5,3+(2-N(INDEX(segments_table,5,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="F60" s="41">
+        <f>IF(INDEX(segments_table,5,1)="",0,IF(3&lt;N(INDEX(segments_table,5,2)),0,IF(3=N(INDEX(segments_table,5,2)),N(INDEX(segments_table,5,3)),E60*(1+N(INDEX(segments_table,5,3+(3-N(INDEX(segments_table,5,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="G60" s="41">
+        <f>IF(INDEX(segments_table,5,1)="",0,IF(4&lt;N(INDEX(segments_table,5,2)),0,IF(4=N(INDEX(segments_table,5,2)),N(INDEX(segments_table,5,3)),F60*(1+N(INDEX(segments_table,5,3+(4-N(INDEX(segments_table,5,2)))))))))</f>
+        <v/>
+      </c>
+      <c r="H60" s="41">
+        <f>IF(INDEX(segments_table,5,1)="",0,IF(5&lt;N(INDEX(segments_table,5,2)),0,IF(5=N(INDEX(segments_table,5,2)),N(INDEX(segments_table,5,3)),G60*(1+N(INDEX(segments_table,5,3+(5-N(INDEX(segments_table,5,2)))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4">
+        <f>IF(INDEX(segments_table,5,1)="","","COGS — "&amp;INDEX(segments_table,5,1))</f>
+        <v/>
+      </c>
+      <c r="C61" s="41" t="n"/>
+      <c r="D61" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",-D60*(1-N(INDEX(segments_table,5,MIN(9+(1-N(INDEX(segments_table,5,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="E61" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",-E60*(1-N(INDEX(segments_table,5,MIN(9+(2-N(INDEX(segments_table,5,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="F61" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",-F60*(1-N(INDEX(segments_table,5,MIN(9+(3-N(INDEX(segments_table,5,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="G61" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",-G60*(1-N(INDEX(segments_table,5,MIN(9+(4-N(INDEX(segments_table,5,2))),13)))))</f>
+        <v/>
+      </c>
+      <c r="H61" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",-H60*(1-N(INDEX(segments_table,5,MIN(9+(5-N(INDEX(segments_table,5,2))),13)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4">
+        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,5,1),"Related opex (allocated) — "&amp;INDEX(segments_table,5,1)))</f>
+        <v/>
+      </c>
+      <c r="C62" s="41" t="n"/>
+      <c r="D62" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,-D60*N(INDEX(segments_table,5,MIN(14+(1-N(INDEX(segments_table,5,2))),18))),-D60*opex_pct_revenue_y1))</f>
+        <v/>
+      </c>
+      <c r="E62" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,-E60*N(INDEX(segments_table,5,MIN(14+(2-N(INDEX(segments_table,5,2))),18))),-E60*opex_pct_revenue_y2))</f>
+        <v/>
+      </c>
+      <c r="F62" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,-F60*N(INDEX(segments_table,5,MIN(14+(3-N(INDEX(segments_table,5,2))),18))),-F60*opex_pct_revenue_y3))</f>
+        <v/>
+      </c>
+      <c r="G62" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,-G60*N(INDEX(segments_table,5,MIN(14+(4-N(INDEX(segments_table,5,2))),18))),-G60*opex_pct_revenue_y4))</f>
+        <v/>
+      </c>
+      <c r="H62" s="41">
+        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,-H60*N(INDEX(segments_table,5,MIN(14+(5-N(INDEX(segments_table,5,2))),18))),-H60*opex_pct_revenue_y5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Carved-out revenue (streams with own Opex%)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,D44,0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,D48,0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,D52,0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,D56,0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,D60,0)</f>
+        <v/>
+      </c>
+      <c r="E64" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,E44,0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,E48,0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,E52,0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,E56,0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,E60,0)</f>
+        <v/>
+      </c>
+      <c r="F64" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,F44,0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,F48,0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,F52,0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,F56,0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,F60,0)</f>
+        <v/>
+      </c>
+      <c r="G64" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,G44,0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,G48,0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,G52,0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,G56,0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,G60,0)</f>
+        <v/>
+      </c>
+      <c r="H64" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,H44,0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,H48,0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,H52,0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,H56,0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,H60,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Related opex — carved-out streams subtotal</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,N(D46),0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,N(D50),0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,N(D54),0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,N(D58),0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,N(D62),0)</f>
+        <v/>
+      </c>
+      <c r="E65" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,N(E46),0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,N(E50),0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,N(E54),0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,N(E58),0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,N(E62),0)</f>
+        <v/>
+      </c>
+      <c r="F65" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,N(F46),0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,N(F50),0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,N(F54),0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,N(F58),0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,N(F62),0)</f>
+        <v/>
+      </c>
+      <c r="G65" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,N(G46),0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,N(G50),0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,N(G54),0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,N(G58),0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,N(G62),0)</f>
+        <v/>
+      </c>
+      <c r="H65" s="41">
+        <f>IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,N(H46),0)+IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,N(H50),0)+IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,N(H54),0)+IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,N(H58),0)+IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,N(H62),0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A34:H34"/>
@@ -18808,7 +19412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -18823,14 +19427,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Football Field — methodology range reconciliation</t>
+          <t>Football Field — methodology ranges (DCF primary; others cross-checks)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Range chart input. DCF range comes from the two WACC scenarios. Comps range from CoCo Q1/Median/Q3. Precedent range from precedents_table (when populated). Apply football_field weights to compute weighted-average EV.</t>
+          <t>Range chart input. DCF range comes from the two WACC scenarios and is the primary methodology (weight_dcf = 1.0). Comps range from CoCo Q1/Median/Q3 and Precedent range from precedents_table are retained as cross-checks against the DCF EV (±10% band, see rows 22-26).</t>
         </is>
       </c>
     </row>
@@ -19055,7 +19659,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Weighted-average valuation</t>
+          <t>Concluded valuation (DCF primary)</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19677,7 @@
     <row r="16">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>Weighted-average EV (calculated)</t>
+          <t>Concluded EV (DCF primary)</t>
         </is>
       </c>
       <c r="F16" s="45">
@@ -19136,11 +19740,104 @@
       <c r="F20" s="33" t="n"/>
       <c r="G20" s="33" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Cross-checks vs DCF enterprise value (±10% band)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>Cross-check</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>Implied EV</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>Variance vs DCF</t>
+        </is>
+      </c>
+      <c r="D23" s="55" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="E23" s="55" t="inlineStr"/>
+      <c r="F23" s="55" t="inlineStr"/>
+      <c r="G23" s="55" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Market approach (Comps combined)</t>
+        </is>
+      </c>
+      <c r="B24" s="40">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="C24" s="54">
+        <f>IF(OR(C11=0,'DCF'!I27=0),"n/a",C11/'DCF'!I27-1)</f>
+        <v/>
+      </c>
+      <c r="D24" s="33">
+        <f>IF(OR(C11=0,'DCF'!I27=0),"Not available",IF(ABS(C11/'DCF'!I27-1)&lt;=0.1,"Within reasonable range","Outside cross-check range"))</f>
+        <v/>
+      </c>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Precedent transactions</t>
+        </is>
+      </c>
+      <c r="B25" s="40">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="C25" s="54">
+        <f>IF(OR(C12=0,'DCF'!I27=0),"n/a",C12/'DCF'!I27-1)</f>
+        <v/>
+      </c>
+      <c r="D25" s="33">
+        <f>IF(OR(C12=0,'DCF'!I27=0),"Not available",IF(ABS(C12/'DCF'!I27-1)&lt;=0.1,"Within reasonable range","Outside cross-check range"))</f>
+        <v/>
+      </c>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="33" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>Overall cross-check verdict</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="n"/>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="53">
+        <f>IF(AND(D24="Not available",D25="Not available"),"Not available",IF(OR(D24="Outside cross-check range",D25="Outside cross-check range"),"Outside cross-check range","Within reasonable range"))</f>
+        <v/>
+      </c>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/materials/templates/orionmano-valuation-template-v1.xlsx
+++ b/materials/templates/orionmano-valuation-template-v1.xlsx
@@ -17814,7 +17814,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Driven by the Inputs 'Revenue segments' table. Unused slots stay blank. 'Related opex' uses the stream's own Opex% when provided (carved out of the top-level opex base), otherwise an allocation at the top-level ratio.</t>
+          <t>Driven by the Inputs 'Revenue segments' table. Unused slots stay blank. 'Direct expenses' uses the stream's own Opex% when provided (carved out of the top-level opex base), otherwise an allocation at the top-level ratio.</t>
         </is>
       </c>
     </row>
@@ -17877,7 +17877,7 @@
     </row>
     <row r="46">
       <c r="A46" s="4">
-        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,1,1),"Related opex (allocated) — "&amp;INDEX(segments_table,1,1)))</f>
+        <f>IF(INDEX(segments_table,1,1)="","",IF(COUNT(INDEX(segments_table,1,14):INDEX(segments_table,1,18))&gt;0,"Direct expenses — "&amp;INDEX(segments_table,1,1),"Direct expenses (allocated) — "&amp;INDEX(segments_table,1,1)))</f>
         <v/>
       </c>
       <c r="C46" s="41" t="n"/>
@@ -17961,7 +17961,7 @@
     </row>
     <row r="50">
       <c r="A50" s="4">
-        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,2,1),"Related opex (allocated) — "&amp;INDEX(segments_table,2,1)))</f>
+        <f>IF(INDEX(segments_table,2,1)="","",IF(COUNT(INDEX(segments_table,2,14):INDEX(segments_table,2,18))&gt;0,"Direct expenses — "&amp;INDEX(segments_table,2,1),"Direct expenses (allocated) — "&amp;INDEX(segments_table,2,1)))</f>
         <v/>
       </c>
       <c r="C50" s="41" t="n"/>
@@ -18045,7 +18045,7 @@
     </row>
     <row r="54">
       <c r="A54" s="4">
-        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,3,1),"Related opex (allocated) — "&amp;INDEX(segments_table,3,1)))</f>
+        <f>IF(INDEX(segments_table,3,1)="","",IF(COUNT(INDEX(segments_table,3,14):INDEX(segments_table,3,18))&gt;0,"Direct expenses — "&amp;INDEX(segments_table,3,1),"Direct expenses (allocated) — "&amp;INDEX(segments_table,3,1)))</f>
         <v/>
       </c>
       <c r="C54" s="41" t="n"/>
@@ -18129,7 +18129,7 @@
     </row>
     <row r="58">
       <c r="A58" s="4">
-        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,4,1),"Related opex (allocated) — "&amp;INDEX(segments_table,4,1)))</f>
+        <f>IF(INDEX(segments_table,4,1)="","",IF(COUNT(INDEX(segments_table,4,14):INDEX(segments_table,4,18))&gt;0,"Direct expenses — "&amp;INDEX(segments_table,4,1),"Direct expenses (allocated) — "&amp;INDEX(segments_table,4,1)))</f>
         <v/>
       </c>
       <c r="C58" s="41" t="n"/>
@@ -18213,7 +18213,7 @@
     </row>
     <row r="62">
       <c r="A62" s="4">
-        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,"Related opex — "&amp;INDEX(segments_table,5,1),"Related opex (allocated) — "&amp;INDEX(segments_table,5,1)))</f>
+        <f>IF(INDEX(segments_table,5,1)="","",IF(COUNT(INDEX(segments_table,5,14):INDEX(segments_table,5,18))&gt;0,"Direct expenses — "&amp;INDEX(segments_table,5,1),"Direct expenses (allocated) — "&amp;INDEX(segments_table,5,1)))</f>
         <v/>
       </c>
       <c r="C62" s="41" t="n"/>
@@ -18271,7 +18271,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Related opex — carved-out streams subtotal</t>
+          <t>Direct expenses — carved-out streams subtotal</t>
         </is>
       </c>
       <c r="C65" t="n">

--- a/materials/templates/orionmano-valuation-template-v1.xlsx
+++ b/materials/templates/orionmano-valuation-template-v1.xlsx
@@ -16806,23 +16806,23 @@
         </is>
       </c>
       <c r="C47" s="39">
-        <f>C28-C39</f>
+        <f>ABS(C28)-ABS(C39)</f>
         <v/>
       </c>
       <c r="D47" s="39">
-        <f>D28-D39</f>
+        <f>ABS(D28)-ABS(D39)</f>
         <v/>
       </c>
       <c r="E47" s="39">
-        <f>E28-E39</f>
+        <f>ABS(E28)-ABS(E39)</f>
         <v/>
       </c>
       <c r="F47" s="39">
-        <f>F28-F39</f>
+        <f>ABS(F28)-ABS(F39)</f>
         <v/>
       </c>
       <c r="G47" s="39">
-        <f>G28-G39</f>
+        <f>ABS(G28)-ABS(G39)</f>
         <v/>
       </c>
     </row>
@@ -16838,23 +16838,23 @@
         </is>
       </c>
       <c r="C48" s="39">
-        <f>C37+C41-C24</f>
+        <f>ABS(C37)+ABS(C41)-ABS(C24)</f>
         <v/>
       </c>
       <c r="D48" s="39">
-        <f>D37+D41-D24</f>
+        <f>ABS(D37)+ABS(D41)-ABS(D24)</f>
         <v/>
       </c>
       <c r="E48" s="39">
-        <f>E37+E41-E24</f>
+        <f>ABS(E37)+ABS(E41)-ABS(E24)</f>
         <v/>
       </c>
       <c r="F48" s="39">
-        <f>F37+F41-F24</f>
+        <f>ABS(F37)+ABS(F41)-ABS(F24)</f>
         <v/>
       </c>
       <c r="G48" s="39">
-        <f>G37+G41-G24</f>
+        <f>ABS(G37)+ABS(G41)-ABS(G24)</f>
         <v/>
       </c>
     </row>
